--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BH22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,6 +727,4080 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Australian A-League Men</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>06:00:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Melbourne City</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Central Coast Mariners</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Turkish 1 Lig</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Hatayspor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Adana Demirspor</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K3" t="n">
+        <v>410</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Turkish 1 Lig</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Manisa FK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pendikspor</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Smouha</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ENPPI</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Swiss Challenge League</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Aarau</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Etoile Carouge</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Swedish Superettan</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Oddevold</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sandvikens</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Polish Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Arka Gdynia</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Zaglebie Lubin</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Aalesunds</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>KFUM Oslo</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Hodd</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sandnes Ulf</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cottbus</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1860 Munich</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Schweinfurt</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Rot-Weiss Essen</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>18</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>11</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Duisburg</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>VfL Osnabruck</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Jahn Regensburg</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Erzgebirge</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Danish Superliga</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FC Nordsjaelland</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Brondby</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Waldhof Mannheim</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Hoffenheim II</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Portuguese Segunda Liga</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>14:00:59</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Vizela</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Benfica B</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G18" t="n">
+        <v>120</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I18" t="n">
+        <v>120</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K18" t="n">
+        <v>120</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Swiss Challenge League</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FC Wil</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Neuchatel Xamax</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Swiss Challenge League</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FC Vaduz</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Bellinzona</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>50</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K20" t="n">
+        <v>12</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ceramica Cleopatra</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Al Ahly Cairo</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Aguilas Doradas</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:37:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH22"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Australian A-League Men</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,184 +743,184 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>06:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Melbourne City</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Central Coast Mariners</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1.48</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>410</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.38</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -937,36 +937,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Manisa FK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>410</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Manisa FK</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.85</v>
+        <v>2.48</v>
       </c>
       <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>4.6</v>
       </c>
-      <c r="H4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,42 +1325,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Etoile Carouge</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.48</v>
+        <v>1.45</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2</v>
+        <v>2.46</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>19.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>1.5</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1381,10 +1381,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1393,123 +1393,123 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Etoile Carouge</t>
+          <t>Sandvikens</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.77</v>
+        <v>2.78</v>
       </c>
       <c r="H6" t="n">
-        <v>2.28</v>
+        <v>2.76</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandvikens</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="G7" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="H7" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="I7" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,31 +1912,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Aalesunds</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.34</v>
+        <v>2.92</v>
       </c>
       <c r="G8" t="n">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="H8" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="I8" t="n">
-        <v>3.95</v>
+        <v>2.54</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aalesunds</t>
+          <t>KFUM Oslo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.92</v>
+        <v>2.12</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="H9" t="n">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.58</v>
+        <v>3.85</v>
       </c>
       <c r="J9" t="n">
         <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KFUM Oslo</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>2.26</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Cottbus</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>1860 Munich</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cottbus</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1860 Munich</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.77</v>
+        <v>4.8</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28</v>
+        <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>3.25</v>
+        <v>1.43</v>
       </c>
       <c r="I12" t="n">
-        <v>5.3</v>
+        <v>1.65</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.08</v>
+        <v>2.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>VfL Osnabruck</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>18</v>
+        <v>3.65</v>
       </c>
       <c r="H13" t="n">
-        <v>1.43</v>
+        <v>2.58</v>
       </c>
       <c r="I13" t="n">
-        <v>1.74</v>
+        <v>3.45</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>2.96</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.28</v>
+        <v>1.59</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.42</v>
+        <v>1.97</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VfL Osnabruck</t>
+          <t>Erzgebirge</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="G14" t="n">
-        <v>3.65</v>
+        <v>2.84</v>
       </c>
       <c r="H14" t="n">
-        <v>1.38</v>
+        <v>2.88</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.59</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.97</v>
+        <v>1.56</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,37 +3270,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>FC Nordsjaelland</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Erzgebirge</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.84</v>
+        <v>2.46</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="I15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K15" t="n">
         <v>4.1</v>
       </c>
-      <c r="J15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7</v>
-      </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3321,10 +3321,10 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3333,123 +3333,123 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,37 +3464,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FC Nordsjaelland</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="G16" t="n">
-        <v>2.46</v>
+        <v>2.98</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="I16" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3515,10 +3515,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3527,123 +3527,123 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>14:00:59</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Vizela</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Benfica B</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="G17" t="n">
-        <v>2.98</v>
+        <v>120</v>
       </c>
       <c r="H17" t="n">
-        <v>2.62</v>
+        <v>1.09</v>
       </c>
       <c r="I17" t="n">
-        <v>4.7</v>
+        <v>120</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>1.09</v>
       </c>
       <c r="K17" t="n">
-        <v>8.800000000000001</v>
+        <v>120</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,184 +3847,184 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14:00:59</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Vizela</t>
+          <t>FC Wil</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>Neuchatel Xamax</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="G18" t="n">
-        <v>120</v>
+        <v>2.58</v>
       </c>
       <c r="H18" t="n">
-        <v>1.09</v>
+        <v>2.86</v>
       </c>
       <c r="I18" t="n">
-        <v>120</v>
+        <v>3.35</v>
       </c>
       <c r="J18" t="n">
-        <v>1.09</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>120</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="R18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FC Wil</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neuchatel Xamax</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.3</v>
+        <v>1.29</v>
       </c>
       <c r="G19" t="n">
-        <v>2.58</v>
+        <v>1.43</v>
       </c>
       <c r="H19" t="n">
-        <v>2.86</v>
+        <v>7.2</v>
       </c>
       <c r="I19" t="n">
-        <v>3.35</v>
+        <v>50</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.08</v>
+        <v>2.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,42 +4235,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.29</v>
+        <v>4.8</v>
       </c>
       <c r="G20" t="n">
-        <v>1.49</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>7.2</v>
+        <v>1.57</v>
       </c>
       <c r="I20" t="n">
-        <v>50</v>
+        <v>1.85</v>
       </c>
       <c r="J20" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="K20" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>1.82</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.44</v>
+        <v>1.81</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4291,10 +4291,10 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4303,123 +4303,123 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,42 +4429,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Aguilas Doradas</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.8</v>
+        <v>2.54</v>
       </c>
       <c r="G21" t="n">
-        <v>8.6</v>
+        <v>3.1</v>
       </c>
       <c r="H21" t="n">
-        <v>1.56</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="K21" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4485,10 +4485,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4497,310 +4497,116 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>18:00:00</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Aguilas Doradas</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Atletico Bucaramanga</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="G22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Australian A-League Men</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,184 +743,184 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Melbourne City</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Central Coast Mariners</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>1.49</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="K2" t="n">
-        <v>410</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -937,36 +937,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Manisa FK</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>410</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,42 +1131,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Manisa FK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.48</v>
+        <v>3.85</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>1.89</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.38</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.88</v>
+        <v>1.77</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1187,10 +1187,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1199,123 +1199,123 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,42 +1325,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Etoile Carouge</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.45</v>
+        <v>2.48</v>
       </c>
       <c r="G5" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.46</v>
+        <v>3.2</v>
       </c>
       <c r="I5" t="n">
-        <v>19.5</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.5</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1381,10 +1381,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1393,123 +1393,123 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandvikens</t>
+          <t>Etoile Carouge</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78</v>
+        <v>1.68</v>
       </c>
       <c r="H6" t="n">
-        <v>2.76</v>
+        <v>2.54</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>19.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>2.46</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>410</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Sandvikens</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N7" t="n">
         <v>2.84</v>
       </c>
-      <c r="H7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,31 +1912,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Aalesunds</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.92</v>
+        <v>2.16</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="I8" t="n">
-        <v>2.54</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KFUM Oslo</t>
+          <t>Aalesunds</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.12</v>
+        <v>2.92</v>
       </c>
       <c r="G9" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4</v>
+        <v>2.32</v>
       </c>
       <c r="I9" t="n">
-        <v>3.85</v>
+        <v>2.58</v>
       </c>
       <c r="J9" t="n">
         <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>2.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>KFUM Oslo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.26</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cottbus</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1860 Munich</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.77</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.28</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Cottbus</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>1860 Munich</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.8</v>
+        <v>1.79</v>
       </c>
       <c r="G12" t="n">
-        <v>18</v>
+        <v>2.28</v>
       </c>
       <c r="H12" t="n">
-        <v>1.43</v>
+        <v>3.25</v>
       </c>
       <c r="I12" t="n">
-        <v>1.65</v>
+        <v>5.3</v>
       </c>
       <c r="J12" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VfL Osnabruck</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="G13" t="n">
-        <v>3.65</v>
+        <v>16.5</v>
       </c>
       <c r="H13" t="n">
-        <v>2.58</v>
+        <v>1.45</v>
       </c>
       <c r="I13" t="n">
-        <v>3.45</v>
+        <v>1.64</v>
       </c>
       <c r="J13" t="n">
-        <v>2.96</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.59</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.97</v>
+        <v>1.42</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erzgebirge</t>
+          <t>VfL Osnabruck</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>2.84</v>
+        <v>3.65</v>
       </c>
       <c r="H14" t="n">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="I14" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>1.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.56</v>
+        <v>1.97</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,37 +3270,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FC Nordsjaelland</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Erzgebirge</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="G15" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="I15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.25</v>
       </c>
-      <c r="J15" t="n">
-        <v>3.65</v>
-      </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3321,10 +3321,10 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3333,123 +3333,123 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,37 +3464,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>FC Nordsjaelland</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>2.98</v>
+        <v>2.46</v>
       </c>
       <c r="H16" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="I16" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3515,10 +3515,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3527,123 +3527,123 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14:00:59</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Vizela</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>120</v>
+        <v>2.96</v>
       </c>
       <c r="H17" t="n">
-        <v>1.09</v>
+        <v>2.62</v>
       </c>
       <c r="I17" t="n">
-        <v>120</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
-        <v>1.09</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>120</v>
+        <v>6.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,184 +3847,184 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:59</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FC Wil</t>
+          <t>Vizela</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neuchatel Xamax</t>
+          <t>Benfica B</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="G18" t="n">
-        <v>2.58</v>
+        <v>120</v>
       </c>
       <c r="H18" t="n">
-        <v>2.86</v>
+        <v>1.09</v>
       </c>
       <c r="I18" t="n">
-        <v>3.35</v>
+        <v>120</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>1.09</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>120</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P18" t="n">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>FC Wil</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchatel Xamax</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.29</v>
+        <v>2.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1.43</v>
+        <v>2.58</v>
       </c>
       <c r="H19" t="n">
-        <v>7.2</v>
+        <v>2.86</v>
       </c>
       <c r="I19" t="n">
-        <v>50</v>
+        <v>3.55</v>
       </c>
       <c r="J19" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>12</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,42 +4235,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.8</v>
+        <v>1.29</v>
       </c>
       <c r="G20" t="n">
-        <v>8.199999999999999</v>
+        <v>1.43</v>
       </c>
       <c r="H20" t="n">
-        <v>1.57</v>
+        <v>7.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.85</v>
+        <v>50</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="K20" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.82</v>
+        <v>2.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4291,10 +4291,10 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4303,310 +4303,504 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ceramica Cleopatra</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Al Ahly Cairo</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:37:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>18:00:00</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Aguilas Doradas</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Atletico Bucaramanga</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="F22" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H22" t="n">
         <v>3</v>
       </c>
-      <c r="I21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="I22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>1.46</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>2.34</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>2026-04-05 05:07:26</t>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -760,22 +760,22 @@
         <v>1.45</v>
       </c>
       <c r="G2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -790,7 +790,7 @@
         <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R2" t="n">
         <v>1.52</v>
@@ -802,13 +802,13 @@
         <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -865,7 +865,7 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ2" t="n">
         <v>21</v>
@@ -883,7 +883,7 @@
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
         <v>11.5</v>
@@ -907,7 +907,7 @@
         <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE2" t="n">
         <v>11.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -969,152 +969,152 @@
         <v>410</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
         <v>4.4</v>
@@ -1354,7 +1354,7 @@
         <v>2.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1462,13 +1462,13 @@
         <v>5.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AV5" t="n">
         <v>4.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
@@ -1477,10 +1477,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB5" t="n">
         <v>4.8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G7" t="n">
         <v>2.78</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I7" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
         <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,7 +1751,7 @@
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="O7" t="n">
         <v>1.28</v>
@@ -1760,13 +1760,13 @@
         <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R7" t="n">
         <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,7 +1775,7 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
         <v>1.56</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G10" t="n">
         <v>2.26</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.79</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H12" t="n">
         <v>3.25</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="G13" t="n">
-        <v>16.5</v>
+        <v>7.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="I13" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="K13" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -3476,19 +3476,19 @@
         <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H16" t="n">
         <v>3.1</v>
       </c>
       <c r="I16" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="J16" t="n">
         <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3515,7 +3515,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U16" t="n">
         <v>2.46</v>
@@ -3584,13 +3584,13 @@
         <v>5.3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR16" t="n">
         <v>18.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT16" t="n">
         <v>11</v>
@@ -3602,7 +3602,7 @@
         <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX16" t="n">
         <v>5.1</v>
@@ -3614,13 +3614,13 @@
         <v>11.5</v>
       </c>
       <c r="BA16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB16" t="n">
         <v>5.8</v>
       </c>
-      <c r="BB16" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BC16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD16" t="n">
         <v>5.7</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
         <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -4061,13 +4061,13 @@
         <v>2.58</v>
       </c>
       <c r="H19" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I19" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K19" t="n">
         <v>4.1</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J22" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-05 07:37:34</t>
+          <t>2026-04-05 10:07:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K2" t="n">
         <v>5.3</v>
@@ -778,7 +778,7 @@
         <v>1.28</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
         <v>4.9</v>
@@ -787,7 +787,7 @@
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q2" t="n">
         <v>1.67</v>
@@ -802,13 +802,13 @@
         <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V2" t="n">
         <v>1.12</v>
       </c>
       <c r="W2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         <v>130</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG2" t="n">
         <v>10.5</v>
@@ -847,7 +847,7 @@
         <v>110</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK2" t="n">
         <v>15</v>
@@ -865,16 +865,16 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
         <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
@@ -886,10 +886,10 @@
         <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
         <v>9.199999999999999</v>
@@ -898,7 +898,7 @@
         <v>19.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -910,17 +910,17 @@
         <v>10</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF2" t="n">
         <v>5.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -972,16 +972,16 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O3" t="n">
         <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q3" t="n">
         <v>1.21</v>
@@ -1059,52 +1059,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>3.85</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
         <v>1.89</v>
@@ -1163,16 +1163,16 @@
         <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
         <v>2.04</v>
@@ -1181,134 +1181,134 @@
         <v>1.77</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="J5" t="n">
         <v>2.5</v>
@@ -1357,40 +1357,40 @@
         <v>3.05</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
         <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" t="n">
         <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U5" t="n">
         <v>1.62</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X5" t="n">
         <v>7.6</v>
@@ -1447,16 +1447,16 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT5" t="n">
         <v>5.3</v>
@@ -1465,10 +1465,10 @@
         <v>3.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
@@ -1480,29 +1480,29 @@
         <v>4.6</v>
       </c>
       <c r="BA5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD5" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD5" t="n">
+      <c r="BE5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF5" t="n">
         <v>5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.9</v>
       </c>
       <c r="BG5" t="n">
         <v>5.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>2.78</v>
       </c>
       <c r="H7" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
@@ -1742,7 +1742,7 @@
         <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="H8" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J8" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.92</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H9" t="n">
         <v>2.32</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         <v>2.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
         <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB16" t="n">
         <v>15</v>
@@ -3554,7 +3554,7 @@
         <v>20</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
         <v>1000</v>
@@ -3581,16 +3581,16 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR16" t="n">
         <v>18.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT16" t="n">
         <v>11</v>
@@ -3602,10 +3602,10 @@
         <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AY16" t="n">
         <v>9.800000000000001</v>
@@ -3614,16 +3614,16 @@
         <v>11.5</v>
       </c>
       <c r="BA16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD16" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.7</v>
       </c>
       <c r="BE16" t="n">
         <v>48</v>
@@ -3632,11 +3632,11 @@
         <v>12</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
         <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>2.84</v>
       </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="J19" t="n">
         <v>3.45</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -4443,28 +4443,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="G21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="H21" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="I21" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4485,10 +4485,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4497,37 +4497,37 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF21" t="n">
         <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
@@ -4548,65 +4548,65 @@
         <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>2.54</v>
       </c>
       <c r="G22" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -4649,7 +4649,7 @@
         <v>3.5</v>
       </c>
       <c r="J22" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K22" t="n">
         <v>3.7</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-05 10:07:24</t>
+          <t>2026-04-05 12:33:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH22"/>
+  <dimension ref="A1:BH23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,7 +775,7 @@
         <v>5.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>410</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,13 +975,13 @@
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q3" t="n">
         <v>1.21</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G5" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="H5" t="n">
         <v>3.45</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J5" t="n">
         <v>2.5</v>
@@ -1372,7 +1372,7 @@
         <v>1.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="R5" t="n">
         <v>1.13</v>
@@ -1384,13 +1384,13 @@
         <v>2.38</v>
       </c>
       <c r="U5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V5" t="n">
         <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
         <v>7.6</v>
@@ -1447,28 +1447,28 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AQ5" t="n">
         <v>3.55</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="AT5" t="n">
         <v>5.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
@@ -1477,32 +1477,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="G6" t="n">
         <v>1.68</v>
       </c>
       <c r="H6" t="n">
-        <v>2.54</v>
+        <v>4.8</v>
       </c>
       <c r="I6" t="n">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="J6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W6" t="n">
         <v>2.46</v>
       </c>
-      <c r="K6" t="n">
-        <v>410</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>2.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="H7" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,13 +1751,13 @@
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
         <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
         <v>1.79</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H8" t="n">
         <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
@@ -1939,16 +1939,16 @@
         <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P8" t="n">
         <v>1.72</v>
@@ -1957,134 +1957,134 @@
         <v>2.18</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G9" t="n">
         <v>3.35</v>
@@ -2133,16 +2133,16 @@
         <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
         <v>2.06</v>
@@ -2151,134 +2151,134 @@
         <v>1.79</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
@@ -2327,16 +2327,16 @@
         <v>3.95</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P10" t="n">
         <v>2.06</v>
@@ -2345,134 +2345,134 @@
         <v>1.82</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P11" t="n">
         <v>2.18</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
       </c>
       <c r="Q11" t="n">
         <v>1.64</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cottbus</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1860 Munich</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.79</v>
+        <v>2.18</v>
       </c>
       <c r="G12" t="n">
-        <v>2.22</v>
+        <v>2.64</v>
       </c>
       <c r="H12" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="G13" t="n">
-        <v>7.6</v>
+        <v>2.68</v>
       </c>
       <c r="H13" t="n">
-        <v>1.52</v>
+        <v>2.62</v>
       </c>
       <c r="I13" t="n">
-        <v>1.61</v>
+        <v>3.85</v>
       </c>
       <c r="J13" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P13" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Cottbus</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VfL Osnabruck</t>
+          <t>1860 Munich</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="G14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H14" t="n">
         <v>3.65</v>
       </c>
-      <c r="H14" t="n">
-        <v>2.58</v>
-      </c>
       <c r="I14" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T14" t="n">
         <v>1.59</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Erzgebirge</t>
+          <t>VfL Osnabruck</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="K15" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FC Nordsjaelland</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="G16" t="n">
-        <v>2.44</v>
+        <v>7.6</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1</v>
+        <v>1.52</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>1.61</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="K16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X16" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BG16" t="n">
         <v>3.95</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="G17" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="H17" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="I17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>1.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,90 +3847,90 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14:00:59</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Vizela</t>
+          <t>FC Nordsjaelland</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="G18" t="n">
-        <v>120</v>
+        <v>2.44</v>
       </c>
       <c r="H18" t="n">
-        <v>1.09</v>
+        <v>3.1</v>
       </c>
       <c r="I18" t="n">
-        <v>120</v>
+        <v>3.4</v>
       </c>
       <c r="J18" t="n">
-        <v>1.09</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>120</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>1.02</v>
+        <v>4.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="T18" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="U18" t="n">
-        <v>1.84</v>
+        <v>2.46</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
@@ -3939,7 +3939,7 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG18" t="n">
         <v>1000</v>
@@ -3969,69 +3969,69 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,184 +4041,184 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:59</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FC Wil</t>
+          <t>Vizela</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neuchatel Xamax</t>
+          <t>Benfica B</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="G19" t="n">
-        <v>2.58</v>
+        <v>120</v>
       </c>
       <c r="H19" t="n">
-        <v>2.84</v>
+        <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>3.55</v>
+        <v>120</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>1.09</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>120</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P19" t="n">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>FC Wil</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchatel Xamax</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.29</v>
+        <v>2.3</v>
       </c>
       <c r="G20" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V20" t="n">
         <v>1.43</v>
       </c>
-      <c r="H20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>50</v>
-      </c>
-      <c r="J20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K20" t="n">
-        <v>12</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,105 +4429,105 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5.2</v>
+        <v>1.29</v>
       </c>
       <c r="G21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H21" t="n">
         <v>7.2</v>
       </c>
-      <c r="H21" t="n">
-        <v>1.67</v>
-      </c>
       <c r="I21" t="n">
-        <v>1.82</v>
+        <v>50</v>
       </c>
       <c r="J21" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="K21" t="n">
-        <v>4.4</v>
+        <v>12</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>2.44</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="T21" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X21" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
         <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
@@ -4548,259 +4548,453 @@
         <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-05 12:33:41</t>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ceramica Cleopatra</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Al Ahly Cairo</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-05 14:56:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>18:00:00</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Aguilas Doradas</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Atletico Bucaramanga</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>2.54</v>
       </c>
-      <c r="G22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="G23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H23" t="n">
         <v>3</v>
       </c>
-      <c r="I22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="I23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>1.46</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>2.34</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>2026-04-05 12:33:41</t>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-05 14:56:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH23"/>
+  <dimension ref="A1:BH26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H2" t="n">
         <v>8</v>
@@ -769,13 +769,13 @@
         <v>9</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
         <v>5.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
@@ -787,7 +787,7 @@
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
         <v>1.67</v>
@@ -808,7 +808,7 @@
         <v>1.12</v>
       </c>
       <c r="W2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -865,7 +865,7 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>21</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>3.85</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H4" t="n">
         <v>1.89</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>2.52</v>
       </c>
       <c r="G5" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="H5" t="n">
         <v>3.45</v>
       </c>
       <c r="I5" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="K5" t="n">
         <v>3.05</v>
@@ -1447,16 +1447,16 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AT5" t="n">
         <v>5.3</v>
@@ -1468,7 +1468,7 @@
         <v>4.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
@@ -1477,32 +1477,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA5" t="n">
         <v>3.5</v>
       </c>
       <c r="BB5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC5" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC5" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BD5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF5" t="n">
         <v>3.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>1.68</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="I6" t="n">
         <v>7.4</v>
@@ -1554,13 +1554,13 @@
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>2.32</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P6" t="n">
         <v>2.32</v>
@@ -1569,16 +1569,16 @@
         <v>1.59</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
         <v>1.15</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H8" t="n">
         <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
@@ -1939,10 +1939,10 @@
         <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
         <v>3.1</v>
@@ -1972,7 +1972,7 @@
         <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
@@ -2038,22 +2038,22 @@
         <v>4.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AU8" t="n">
         <v>3.45</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AW8" t="n">
         <v>5.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -2068,13 +2068,13 @@
         <v>5.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BD8" t="n">
         <v>5.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BF8" t="n">
         <v>20</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.96</v>
       </c>
       <c r="G9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H9" t="n">
         <v>2.32</v>
@@ -2133,13 +2133,13 @@
         <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
         <v>1.27</v>
@@ -2148,7 +2148,7 @@
         <v>2.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R9" t="n">
         <v>1.4</v>
@@ -2157,10 +2157,10 @@
         <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="U9" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="V9" t="n">
         <v>1.63</v>
@@ -2169,123 +2169,123 @@
         <v>1.43</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AB9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH9" t="n">
         <v>19.5</v>
       </c>
-      <c r="AC9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX9" t="n">
         <v>19</v>
       </c>
-      <c r="AH9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AY9" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.42</v>
+        <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.58</v>
+        <v>4.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.56</v>
+        <v>4.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.58</v>
+        <v>4.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.64</v>
+        <v>4.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BG9" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,163 +2300,163 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KFUM Oslo</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="G10" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="H10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.4</v>
       </c>
-      <c r="I10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.55</v>
-      </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>3.05</v>
+        <v>2.46</v>
       </c>
       <c r="T10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W10" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y10" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z10" t="n">
         <v>32</v>
       </c>
       <c r="AA10" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AF10" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AI10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL10" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM10" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AO10" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AP10" t="n">
-        <v>14.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS10" t="n">
         <v>4.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.6</v>
+        <v>3.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>13</v>
+        <v>3.95</v>
       </c>
       <c r="AW10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA10" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>32</v>
       </c>
       <c r="BB10" t="n">
         <v>4.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>19.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD10" t="n">
         <v>4.5</v>
@@ -2465,14 +2465,14 @@
         <v>4.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>11</v>
+        <v>3.75</v>
       </c>
       <c r="BG10" t="n">
-        <v>24</v>
+        <v>4.3</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="G11" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
         <v>1.64</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA11" t="n">
         <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AC11" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE11" t="n">
         <v>40</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI11" t="n">
         <v>46</v>
       </c>
       <c r="AJ11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO11" t="n">
         <v>32</v>
       </c>
-      <c r="AK11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>30</v>
-      </c>
       <c r="AP11" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.75</v>
+        <v>11.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>KFUM Oslo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
         <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>1.64</v>
+        <v>3.05</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V12" t="n">
         <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -2882,127 +2882,127 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Cottbus</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>1860 Munich</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="G13" t="n">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="H13" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="I13" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>2.48</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="P13" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="R13" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AR13" t="n">
         <v>1.03</v>
@@ -3011,50 +3011,50 @@
         <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
         <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA13" t="n">
         <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE13" t="n">
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -3076,127 +3076,127 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cottbus</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1860 Munich</t>
+          <t>VfL Osnabruck</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>2.08</v>
+        <v>3.85</v>
       </c>
       <c r="H14" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="I14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K14" t="n">
         <v>4.4</v>
       </c>
-      <c r="J14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>2.76</v>
       </c>
       <c r="O14" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="R14" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>2.34</v>
+        <v>1.86</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>1.92</v>
+        <v>1.47</v>
       </c>
       <c r="X14" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
         <v>1.03</v>
@@ -3205,50 +3205,50 @@
         <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
         <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
         <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -3270,157 +3270,157 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VfL Osnabruck</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P15" t="n">
         <v>2.6</v>
       </c>
-      <c r="G15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Q15" t="n">
-        <v>1.79</v>
+        <v>1.46</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3</v>
+        <v>2.28</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V15" t="n">
-        <v>1.41</v>
+        <v>2.62</v>
       </c>
       <c r="W15" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AX15" t="n">
         <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BB15" t="n">
         <v>1.03</v>
@@ -3435,14 +3435,14 @@
         <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -3464,157 +3464,157 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Erzgebirge</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5.8</v>
+        <v>1.99</v>
       </c>
       <c r="G16" t="n">
-        <v>7.6</v>
+        <v>2.38</v>
       </c>
       <c r="H16" t="n">
-        <v>1.52</v>
+        <v>2.9</v>
       </c>
       <c r="I16" t="n">
-        <v>1.61</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>5.3</v>
+        <v>950</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="O16" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>1.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="T16" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>2.62</v>
+        <v>1.32</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.72</v>
       </c>
       <c r="X16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
         <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
         <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
         <v>1.03</v>
@@ -3629,21 +3629,21 @@
         <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,73 +3658,73 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>FC Nordsjaelland</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Erzgebirge</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>1.41</v>
+        <v>4.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>1.41</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="V17" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -3733,10 +3733,10 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD17" t="n">
         <v>1000</v>
@@ -3745,7 +3745,7 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
         <v>1000</v>
@@ -3775,69 +3775,69 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,85 +3852,85 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FC Nordsjaelland</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G18" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="I18" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="J18" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>2.48</v>
       </c>
       <c r="O18" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="S18" t="n">
-        <v>2.58</v>
+        <v>1.76</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="W18" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
@@ -3939,7 +3939,7 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
         <v>1000</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -4258,25 +4258,25 @@
         <v>2.84</v>
       </c>
       <c r="I20" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="K20" t="n">
         <v>4.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
         <v>4.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P20" t="n">
         <v>2.08</v>
@@ -4285,134 +4285,134 @@
         <v>1.73</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
         <v>1.63</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="G21" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="H21" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I21" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="J21" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="K21" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4479,10 +4479,10 @@
         <v>1.44</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4491,10 +4491,10 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W21" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4551,52 +4551,52 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>5.2</v>
       </c>
       <c r="G22" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="H22" t="n">
         <v>1.67</v>
@@ -4649,49 +4649,49 @@
         <v>1.82</v>
       </c>
       <c r="J22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K22" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q22" t="n">
         <v>1.9</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U22" t="n">
         <v>1.94</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X22" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y22" t="n">
         <v>9.800000000000001</v>
@@ -4709,7 +4709,7 @@
         <v>10.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE22" t="n">
         <v>23</v>
@@ -4724,13 +4724,13 @@
         <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
         <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL22" t="n">
         <v>1000</v>
@@ -4778,223 +4778,805 @@
         <v>17.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG22" t="n">
         <v>9.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-05 14:56:54</t>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Scottish Championship</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ayr</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Dunfermline</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>27</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-05 17:18:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sporting Lisbon</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X24" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>46</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-05 17:18:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X25" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-05 17:18:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>18:00:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Aguilas Doradas</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Atletico Bucaramanga</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H23" t="n">
+      <c r="F26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H26" t="n">
         <v>3</v>
       </c>
-      <c r="I23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="I26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K26" t="n">
         <v>3.4</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L26" t="n">
         <v>0</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N26" t="n">
         <v>0</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P26" t="n">
         <v>1.46</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q26" t="n">
         <v>2.34</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S26" t="n">
         <v>0</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T26" t="n">
         <v>0</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U26" t="n">
         <v>0</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V26" t="n">
         <v>0</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W26" t="n">
         <v>0</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X26" t="n">
         <v>0</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Y26" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="Z26" t="n">
         <v>0</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AA26" t="n">
         <v>0</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AB26" t="n">
         <v>0</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AC26" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AD26" t="n">
         <v>0</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AE26" t="n">
         <v>0</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AF26" t="n">
         <v>0</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AG26" t="n">
         <v>0</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AH26" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AI26" t="n">
         <v>0</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AJ26" t="n">
         <v>0</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AK26" t="n">
         <v>0</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AL26" t="n">
         <v>0</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AM26" t="n">
         <v>0</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AN26" t="n">
         <v>0</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AO26" t="n">
         <v>0</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AP26" t="n">
         <v>0</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AQ26" t="n">
         <v>0</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AR26" t="n">
         <v>0</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AS26" t="n">
         <v>0</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AT26" t="n">
         <v>0</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AU26" t="n">
         <v>0</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AV26" t="n">
         <v>0</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="AW26" t="n">
         <v>0</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="AX26" t="n">
         <v>0</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="AY26" t="n">
         <v>0</v>
       </c>
-      <c r="AZ23" t="n">
+      <c r="AZ26" t="n">
         <v>0</v>
       </c>
-      <c r="BA23" t="n">
+      <c r="BA26" t="n">
         <v>0</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BB26" t="n">
         <v>0</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BC26" t="n">
         <v>0</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BD26" t="n">
         <v>0</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BE26" t="n">
         <v>0</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BF26" t="n">
         <v>0</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BG26" t="n">
         <v>0</v>
       </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>2026-04-05 14:56:54</t>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-05 17:18:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -766,13 +766,13 @@
         <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.31</v>
@@ -781,31 +781,31 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W2" t="n">
         <v>3.05</v>
@@ -823,7 +823,7 @@
         <v>280</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC2" t="n">
         <v>11.5</v>
@@ -841,13 +841,13 @@
         <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
         <v>110</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AK2" t="n">
         <v>15</v>
@@ -865,28 +865,28 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.6</v>
+        <v>17.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX2" t="n">
         <v>8.199999999999999</v>
@@ -898,7 +898,7 @@
         <v>19.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -907,20 +907,20 @@
         <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF2" t="n">
         <v>5.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>3.85</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
         <v>1.89</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="H5" t="n">
         <v>3.45</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
         <v>2.56</v>
@@ -1363,19 +1363,19 @@
         <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q5" t="n">
         <v>2.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S5" t="n">
         <v>6.4</v>
@@ -1390,7 +1390,7 @@
         <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="X5" t="n">
         <v>7.6</v>
@@ -1447,28 +1447,28 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AR5" t="n">
         <v>16.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AT5" t="n">
         <v>5.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
@@ -1477,32 +1477,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>1.68</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
         <v>7.4</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
         <v>2.78</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="U7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
         <v>3.25</v>
@@ -1969,10 +1969,10 @@
         <v>1.98</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W8" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
@@ -2348,7 +2348,7 @@
         <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
         <v>1.59</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
         <v>2.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="R15" t="n">
         <v>1.65</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ17" t="n">
         <v>5.2</v>
@@ -3796,10 +3796,10 @@
         <v>11.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY17" t="n">
         <v>9.800000000000001</v>
@@ -3817,7 +3817,7 @@
         <v>5.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE17" t="n">
         <v>6.6</v>
@@ -3826,11 +3826,11 @@
         <v>12</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -4258,10 +4258,10 @@
         <v>2.84</v>
       </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K20" t="n">
         <v>4.1</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R22" t="n">
         <v>1.34</v>
@@ -4679,7 +4679,7 @@
         <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U22" t="n">
         <v>1.94</v>
@@ -4712,7 +4712,7 @@
         <v>12.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF22" t="n">
         <v>48</v>
@@ -4724,13 +4724,13 @@
         <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ22" t="n">
         <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>12</v>
       </c>
       <c r="AP22" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR22" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AS22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AT22" t="n">
-        <v>15.5</v>
+        <v>4.3</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.6</v>
+        <v>3.55</v>
       </c>
       <c r="AV22" t="n">
         <v>8.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>15.5</v>
+        <v>4.3</v>
       </c>
       <c r="AX22" t="n">
-        <v>36</v>
+        <v>4.8</v>
       </c>
       <c r="AY22" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AZ22" t="n">
         <v>17.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC22" t="n">
         <v>5</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE22" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG22" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
         <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
         <v>1.8</v>
@@ -4885,116 +4885,116 @@
         <v>1.65</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD23" t="n">
         <v>17.5</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AE23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK23" t="n">
         <v>34</v>
       </c>
-      <c r="AA23" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AL23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BA23" t="n">
         <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF23" t="n">
         <v>16.5</v>
       </c>
-      <c r="BD23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>14</v>
-      </c>
       <c r="BG23" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="G24" t="n">
         <v>5.3</v>
       </c>
       <c r="H24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I24" t="n">
         <v>1.79</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.81</v>
       </c>
       <c r="J24" t="n">
         <v>4</v>
@@ -5043,19 +5043,19 @@
         <v>4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O24" t="n">
         <v>1.33</v>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
         <v>2</v>
@@ -5073,7 +5073,7 @@
         <v>2.02</v>
       </c>
       <c r="V24" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="W24" t="n">
         <v>1.23</v>
@@ -5100,7 +5100,7 @@
         <v>9.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF24" t="n">
         <v>40</v>
@@ -5130,7 +5130,7 @@
         <v>85</v>
       </c>
       <c r="AO24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP24" t="n">
         <v>13</v>
@@ -5142,10 +5142,10 @@
         <v>9.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AT24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU24" t="n">
         <v>8.199999999999999</v>
@@ -5160,7 +5160,7 @@
         <v>34</v>
       </c>
       <c r="AY24" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AZ24" t="n">
         <v>19.5</v>
@@ -5184,11 +5184,11 @@
         <v>46</v>
       </c>
       <c r="BG24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G25" t="n">
         <v>3.1</v>
@@ -5237,28 +5237,28 @@
         <v>4.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O25" t="n">
         <v>1.15</v>
       </c>
       <c r="P25" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="Q25" t="n">
         <v>1.48</v>
       </c>
       <c r="R25" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S25" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T25" t="n">
         <v>1.49</v>
@@ -5324,7 +5324,7 @@
         <v>15.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP25" t="n">
         <v>28</v>
@@ -5363,7 +5363,7 @@
         <v>24</v>
       </c>
       <c r="BB25" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BC25" t="n">
         <v>25</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>
@@ -5416,31 +5416,31 @@
         <v>2.6</v>
       </c>
       <c r="G26" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
         <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P26" t="n">
         <v>1.46</v>
@@ -5449,134 +5449,134 @@
         <v>2.34</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-05 17:18:16</t>
+          <t>2026-04-05 19:37:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -760,7 +760,7 @@
         <v>1.45</v>
       </c>
       <c r="G2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H2" t="n">
         <v>8</v>
@@ -769,13 +769,13 @@
         <v>8.6</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
@@ -787,16 +787,16 @@
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
         <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T2" t="n">
         <v>1.93</v>
@@ -808,19 +808,19 @@
         <v>1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="AB2" t="n">
         <v>9.4</v>
@@ -829,10 +829,10 @@
         <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AE2" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF2" t="n">
         <v>9.199999999999999</v>
@@ -841,22 +841,22 @@
         <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK2" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
         <v>6.2</v>
@@ -871,10 +871,10 @@
         <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT2" t="n">
         <v>8.4</v>
@@ -883,22 +883,22 @@
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AW2" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -907,20 +907,20 @@
         <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>1.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,22 +1169,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="O4" t="n">
         <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>1.24</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1193,10 +1193,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -1339,28 +1339,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H5" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="K5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N5" t="n">
         <v>2.24</v>
@@ -1372,31 +1372,31 @@
         <v>1.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1.14</v>
       </c>
       <c r="S5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T5" t="n">
         <v>2.38</v>
       </c>
       <c r="U5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z5" t="n">
         <v>1000</v>
@@ -1405,10 +1405,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>3.45</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AR5" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.3</v>
+        <v>3.15</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="AV5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW5" t="n">
         <v>4.9</v>
       </c>
-      <c r="AW5" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -1533,58 +1533,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="G6" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G7" t="n">
-        <v>2.54</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
         <v>4.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7</v>
+        <v>1.31</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>1.86</v>
       </c>
       <c r="O7" t="n">
         <v>1.28</v>
@@ -1760,16 +1760,16 @@
         <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>2.78</v>
+        <v>1.87</v>
       </c>
       <c r="T7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
         <v>1.01</v>
@@ -1778,7 +1778,7 @@
         <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="H8" t="n">
         <v>3.25</v>
@@ -1939,7 +1939,7 @@
         <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
@@ -1960,7 +1960,7 @@
         <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
         <v>1.87</v>
@@ -1969,10 +1969,10 @@
         <v>1.98</v>
       </c>
       <c r="V8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
@@ -2026,65 +2026,65 @@
         <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV8" t="n">
         <v>4</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AW8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX8" t="n">
         <v>4</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AY8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA8" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ8" t="n">
+      <c r="BB8" t="n">
         <v>4.6</v>
       </c>
-      <c r="BA8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BC8" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BF8" t="n">
         <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2115,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="G9" t="n">
         <v>3.3</v>
       </c>
       <c r="H9" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="I9" t="n">
         <v>2.58</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
         <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
@@ -2145,19 +2145,19 @@
         <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R9" t="n">
         <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U9" t="n">
         <v>2.26</v>
@@ -2172,7 +2172,7 @@
         <v>21</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
         <v>20</v>
@@ -2181,7 +2181,7 @@
         <v>40</v>
       </c>
       <c r="AB9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC9" t="n">
         <v>10.5</v>
@@ -2199,13 +2199,13 @@
         <v>16.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI9" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK9" t="n">
         <v>42</v>
@@ -2214,61 +2214,61 @@
         <v>50</v>
       </c>
       <c r="AM9" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AN9" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AO9" t="n">
         <v>22</v>
       </c>
       <c r="AP9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.2</v>
+        <v>23</v>
       </c>
       <c r="AT9" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AW9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE9" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.5</v>
       </c>
       <c r="BF9" t="n">
         <v>20</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>2.04</v>
       </c>
       <c r="O10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="X10" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -2503,46 +2503,46 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3.9</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
         <v>1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>1.24</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2551,64 +2551,64 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
         <v>1.03</v>
@@ -2659,14 +2659,14 @@
         <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="H12" t="n">
         <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
         <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2727,7 +2727,7 @@
         <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
         <v>1.82</v>
@@ -2742,13 +2742,13 @@
         <v>1.58</v>
       </c>
       <c r="U12" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="X12" t="n">
         <v>21</v>
@@ -2775,16 +2775,16 @@
         <v>50</v>
       </c>
       <c r="AF12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AJ12" t="n">
         <v>34</v>
@@ -2805,28 +2805,28 @@
         <v>44</v>
       </c>
       <c r="AP12" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AQ12" t="n">
         <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.4</v>
+        <v>19</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
         <v>7.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AX12" t="n">
         <v>10.5</v>
@@ -2835,32 +2835,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.4</v>
+        <v>19.5</v>
       </c>
       <c r="BC12" t="n">
         <v>19.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.5</v>
+        <v>24</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BF12" t="n">
         <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -2891,118 +2891,118 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.88</v>
+        <v>1.17</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>3.65</v>
+        <v>1.17</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8</v>
+        <v>1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>2.38</v>
+        <v>1.18</v>
       </c>
       <c r="T13" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
         <v>1.03</v>
@@ -3011,50 +3011,50 @@
         <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
         <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
         <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -3085,145 +3085,145 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="G14" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="H14" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="J14" t="n">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="Q14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U14" t="n">
         <v>2.02</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.86</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="W14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS14" t="n">
         <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW14" t="n">
         <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
         <v>1.03</v>
@@ -3241,14 +3241,14 @@
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -3279,148 +3279,148 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.8</v>
+        <v>1.11</v>
       </c>
       <c r="G15" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.52</v>
+        <v>1.11</v>
       </c>
       <c r="I15" t="n">
-        <v>1.61</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.7</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.6</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.52</v>
+        <v>1.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>2.28</v>
+        <v>1.15</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
         <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
         <v>1.03</v>
@@ -3435,14 +3435,14 @@
         <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.99</v>
+        <v>1.26</v>
       </c>
       <c r="G16" t="n">
-        <v>2.38</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9</v>
+        <v>1.25</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
         <v>950</v>
@@ -3497,22 +3497,22 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="O16" t="n">
         <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -3521,10 +3521,10 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J17" t="n">
         <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3706,25 +3706,25 @@
         <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="T17" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U17" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="V17" t="n">
         <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -3733,13 +3733,13 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC17" t="n">
         <v>10.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
@@ -3748,10 +3748,10 @@
         <v>20</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
@@ -3769,22 +3769,22 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="AR17" t="n">
-        <v>18.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT17" t="n">
         <v>11</v>
@@ -3793,44 +3793,44 @@
         <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="AY17" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB17" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.7</v>
+        <v>18</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>1.09</v>
       </c>
       <c r="G18" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>2.62</v>
+        <v>1.25</v>
       </c>
       <c r="I18" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="K18" t="n">
-        <v>5.1</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,22 +3885,22 @@
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="O18" t="n">
         <v>1.13</v>
       </c>
       <c r="P18" t="n">
-        <v>2.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="R18" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.76</v>
+        <v>1.13</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -4249,145 +4249,145 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G20" t="n">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="H20" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I20" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
         <v>4.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
         <v>1.73</v>
       </c>
       <c r="R20" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>2.84</v>
+        <v>2.08</v>
       </c>
       <c r="T20" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="X20" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
         <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW20" t="n">
         <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
         <v>1.03</v>
@@ -4396,7 +4396,7 @@
         <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
         <v>1.03</v>
@@ -4405,14 +4405,14 @@
         <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G21" t="n">
         <v>1.41</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="I21" t="n">
         <v>13</v>
       </c>
       <c r="J21" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="K21" t="n">
         <v>6.6</v>
@@ -4467,22 +4467,22 @@
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>2.44</v>
+        <v>1.6</v>
       </c>
       <c r="O21" t="n">
         <v>1.15</v>
       </c>
       <c r="P21" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4509,7 +4509,7 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC21" t="n">
         <v>1000</v>
@@ -4521,7 +4521,7 @@
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG21" t="n">
         <v>1000</v>
@@ -4536,7 +4536,7 @@
         <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="n">
         <v>1000</v>
@@ -4545,7 +4545,7 @@
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
@@ -4575,10 +4575,10 @@
         <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AZ21" t="n">
         <v>1.03</v>
@@ -4590,7 +4590,7 @@
         <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD21" t="n">
         <v>1.03</v>
@@ -4599,14 +4599,14 @@
         <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG21" t="n">
         <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -4640,19 +4640,19 @@
         <v>5.2</v>
       </c>
       <c r="G22" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H22" t="n">
         <v>1.67</v>
       </c>
       <c r="I22" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="J22" t="n">
         <v>3.7</v>
       </c>
       <c r="K22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4667,10 +4667,10 @@
         <v>1.31</v>
       </c>
       <c r="P22" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R22" t="n">
         <v>1.34</v>
@@ -4679,13 +4679,13 @@
         <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U22" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V22" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="W22" t="n">
         <v>1.18</v>
@@ -4694,28 +4694,28 @@
         <v>18</v>
       </c>
       <c r="Y22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC22" t="n">
         <v>11</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>10.5</v>
       </c>
       <c r="AD22" t="n">
         <v>12.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF22" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AG22" t="n">
         <v>27</v>
@@ -4724,7 +4724,7 @@
         <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AJ22" t="n">
         <v>1000</v>
@@ -4742,10 +4742,10 @@
         <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>7.2</v>
@@ -4757,19 +4757,19 @@
         <v>13</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.3</v>
+        <v>15.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.3</v>
+        <v>15.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>16</v>
@@ -4778,29 +4778,29 @@
         <v>17.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BD22" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="BG22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -4843,10 +4843,10 @@
         <v>3.75</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4879,7 +4879,7 @@
         <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
         <v>1.65</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
         <v>5.2</v>
       </c>
-      <c r="G24" t="n">
-        <v>5.3</v>
-      </c>
       <c r="H24" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="I24" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="J24" t="n">
         <v>4</v>
@@ -5043,13 +5043,13 @@
         <v>4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>1.33</v>
@@ -5067,16 +5067,16 @@
         <v>3.55</v>
       </c>
       <c r="T24" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U24" t="n">
         <v>2.02</v>
       </c>
       <c r="V24" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X24" t="n">
         <v>14</v>
@@ -5097,7 +5097,7 @@
         <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE24" t="n">
         <v>19</v>
@@ -5130,7 +5130,7 @@
         <v>85</v>
       </c>
       <c r="AO24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP24" t="n">
         <v>13</v>
@@ -5142,7 +5142,7 @@
         <v>9.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT24" t="n">
         <v>15.5</v>
@@ -5151,7 +5151,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW24" t="n">
         <v>17.5</v>
@@ -5160,7 +5160,7 @@
         <v>34</v>
       </c>
       <c r="AY24" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AZ24" t="n">
         <v>19.5</v>
@@ -5169,10 +5169,10 @@
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BC24" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BD24" t="n">
         <v>50</v>
@@ -5184,11 +5184,11 @@
         <v>46</v>
       </c>
       <c r="BG24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -5249,19 +5249,19 @@
         <v>1.15</v>
       </c>
       <c r="P25" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
         <v>1.48</v>
       </c>
       <c r="R25" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S25" t="n">
         <v>2.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="U25" t="n">
         <v>2.94</v>
@@ -5273,7 +5273,7 @@
         <v>1.47</v>
       </c>
       <c r="X25" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y25" t="n">
         <v>18.5</v>
@@ -5297,7 +5297,7 @@
         <v>19</v>
       </c>
       <c r="AF25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG25" t="n">
         <v>14</v>
@@ -5369,7 +5369,7 @@
         <v>25</v>
       </c>
       <c r="BD25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE25" t="n">
         <v>42</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="K26" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5437,22 +5437,22 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>2.32</v>
+        <v>1.25</v>
       </c>
       <c r="O26" t="n">
         <v>1.48</v>
       </c>
       <c r="P26" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.34</v>
+        <v>1.48</v>
       </c>
       <c r="R26" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S26" t="n">
-        <v>4.2</v>
+        <v>1.48</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -5461,10 +5461,10 @@
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-05 19:37:45</t>
+          <t>2026-04-05 21:56:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -796,7 +796,7 @@
         <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
         <v>1.93</v>
@@ -805,13 +805,13 @@
         <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W2" t="n">
         <v>3.15</v>
       </c>
       <c r="X2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="n">
         <v>34</v>
@@ -856,7 +856,7 @@
         <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN2" t="n">
         <v>6.2</v>
@@ -871,22 +871,22 @@
         <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
         <v>8</v>
@@ -898,7 +898,7 @@
         <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -907,20 +907,20 @@
         <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
         <v>5.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="G4" t="n">
         <v>5.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,22 +1169,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O4" t="n">
         <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.24</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1193,10 +1193,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="W4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>2.46</v>
       </c>
       <c r="G5" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H5" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
         <v>3.9</v>
@@ -1357,7 +1357,7 @@
         <v>3.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
         <v>1.16</v>
@@ -1366,7 +1366,7 @@
         <v>2.24</v>
       </c>
       <c r="O5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="P5" t="n">
         <v>1.41</v>
@@ -1390,7 +1390,7 @@
         <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="X5" t="n">
         <v>7.8</v>
@@ -1408,7 +1408,7 @@
         <v>8</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="AR5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX5" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4</v>
-      </c>
       <c r="AY5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB5" t="n">
         <v>3.95</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BC5" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="G6" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="H6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>4.2</v>
       </c>
-      <c r="I6" t="n">
-        <v>21</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K6" t="n">
-        <v>14</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>2.1</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="I7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
-        <v>1.31</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,22 +1751,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.86</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
         <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q7" t="n">
         <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>1.87</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G8" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="H8" t="n">
         <v>3.25</v>
@@ -1939,7 +1939,7 @@
         <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
@@ -1960,7 +1960,7 @@
         <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
         <v>1.87</v>
@@ -1972,13 +1972,13 @@
         <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
         <v>27</v>
@@ -2029,62 +2029,62 @@
         <v>60</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB8" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW8" t="n">
+      <c r="BC8" t="n">
         <v>4.8</v>
       </c>
-      <c r="AX8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA8" t="n">
+      <c r="BD8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>20</v>
-      </c>
       <c r="BG8" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>3.3</v>
       </c>
       <c r="H9" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="I9" t="n">
         <v>2.58</v>
@@ -2133,7 +2133,7 @@
         <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
@@ -2154,13 +2154,13 @@
         <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U9" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
         <v>1.63</v>
@@ -2232,7 +2232,7 @@
         <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>23</v>
+        <v>3.85</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -2309,61 +2309,61 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.89</v>
+        <v>2.12</v>
       </c>
       <c r="G10" t="n">
-        <v>2.64</v>
+        <v>2.36</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.04</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.9</v>
+        <v>2.46</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y10" t="n">
         <v>1000</v>
@@ -2375,10 +2375,10 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
@@ -2387,10 +2387,10 @@
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
         <v>1000</v>
@@ -2399,80 +2399,80 @@
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
         <v>1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>1.24</v>
+        <v>2.78</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>2.1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="H12" t="n">
         <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>3.55</v>
@@ -2739,16 +2739,16 @@
         <v>3.05</v>
       </c>
       <c r="T12" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="U12" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="X12" t="n">
         <v>21</v>
@@ -2766,10 +2766,10 @@
         <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
         <v>50</v>
@@ -2781,16 +2781,16 @@
         <v>13.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI12" t="n">
         <v>60</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
         <v>42</v>
@@ -2805,19 +2805,19 @@
         <v>44</v>
       </c>
       <c r="AP12" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>19</v>
+        <v>4.3</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AU12" t="n">
         <v>7.6</v>
@@ -2826,7 +2826,7 @@
         <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AX12" t="n">
         <v>10.5</v>
@@ -2835,10 +2835,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.95</v>
+        <v>32</v>
       </c>
       <c r="BB12" t="n">
         <v>19.5</v>
@@ -2847,20 +2847,20 @@
         <v>19.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>24</v>
+        <v>4.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BF12" t="n">
         <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -2891,118 +2891,118 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.17</v>
+        <v>1.89</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H13" t="n">
-        <v>1.17</v>
+        <v>3.65</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M13" t="n">
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>1.53</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="P13" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>1.18</v>
+        <v>2.38</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AR13" t="n">
         <v>1.03</v>
@@ -3011,50 +3011,50 @@
         <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
         <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA13" t="n">
         <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE13" t="n">
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G14" t="n">
         <v>3.1</v>
       </c>
       <c r="H14" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I14" t="n">
         <v>2.94</v>
       </c>
       <c r="J14" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3145,7 +3145,7 @@
         <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AA14" t="n">
         <v>55</v>
@@ -3157,28 +3157,28 @@
         <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
         <v>40</v>
       </c>
       <c r="AF14" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
         <v>60</v>
       </c>
       <c r="AK14" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL14" t="n">
         <v>60</v>
@@ -3190,7 +3190,7 @@
         <v>42</v>
       </c>
       <c r="AO14" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP14" t="n">
         <v>9</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -3279,94 +3279,94 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.11</v>
+        <v>5.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="H15" t="n">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>1.69</v>
       </c>
       <c r="J15" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>5.7</v>
       </c>
       <c r="O15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.15</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF15" t="n">
         <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ15" t="n">
         <v>1000</v>
@@ -3384,43 +3384,43 @@
         <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AX15" t="n">
         <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BB15" t="n">
         <v>1.03</v>
@@ -3435,14 +3435,14 @@
         <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.26</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="H16" t="n">
-        <v>1.25</v>
+        <v>2.88</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
         <v>950</v>
@@ -3497,22 +3497,22 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>1.43</v>
+        <v>2.04</v>
       </c>
       <c r="O16" t="n">
         <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.43</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -3521,10 +3521,10 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -3670,19 +3670,19 @@
         <v>2.28</v>
       </c>
       <c r="G17" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="I17" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
         <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3706,19 +3706,19 @@
         <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U17" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W17" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="X17" t="n">
         <v>23</v>
@@ -3778,13 +3778,13 @@
         <v>4.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT17" t="n">
         <v>11</v>
@@ -3796,10 +3796,10 @@
         <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AY17" t="n">
         <v>9.800000000000001</v>
@@ -3820,7 +3820,7 @@
         <v>4.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF17" t="n">
         <v>11</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.09</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="H18" t="n">
-        <v>1.25</v>
+        <v>2.62</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="J18" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
         <v>950</v>
@@ -3891,16 +3891,16 @@
         <v>1.13</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="S18" t="n">
-        <v>1.13</v>
+        <v>2.06</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G20" t="n">
         <v>2.88</v>
       </c>
       <c r="H20" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="I20" t="n">
         <v>3.9</v>
@@ -4264,7 +4264,7 @@
         <v>3.05</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -4273,22 +4273,22 @@
         <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>2.28</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="R20" t="n">
         <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>13</v>
       </c>
       <c r="J21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
         <v>6.6</v>
@@ -4467,28 +4467,28 @@
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.59</v>
       </c>
       <c r="S21" t="n">
-        <v>1.55</v>
+        <v>2.36</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V21" t="n">
         <v>1.08</v>
@@ -4497,7 +4497,7 @@
         <v>3.4</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y21" t="n">
         <v>1000</v>
@@ -4509,10 +4509,10 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD21" t="n">
         <v>1000</v>
@@ -4521,92 +4521,92 @@
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>13</v>
       </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
       <c r="AK21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
         <v>20</v>
       </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX21" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC21" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>5.2</v>
       </c>
       <c r="G22" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H22" t="n">
         <v>1.67</v>
@@ -4655,34 +4655,34 @@
         <v>4.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U22" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V22" t="n">
         <v>2.2</v>
@@ -4691,10 +4691,10 @@
         <v>1.18</v>
       </c>
       <c r="X22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z22" t="n">
         <v>12.5</v>
@@ -4712,7 +4712,7 @@
         <v>12.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AF22" t="n">
         <v>55</v>
@@ -4721,7 +4721,7 @@
         <v>27</v>
       </c>
       <c r="AH22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI22" t="n">
         <v>46</v>
@@ -4769,7 +4769,7 @@
         <v>15.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AY22" t="n">
         <v>16</v>
@@ -4778,29 +4778,29 @@
         <v>17.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BG22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -4834,28 +4834,28 @@
         <v>2.22</v>
       </c>
       <c r="G23" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I23" t="n">
         <v>3.75</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K23" t="n">
         <v>3.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
         <v>1.36</v>
@@ -4870,7 +4870,7 @@
         <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T23" t="n">
         <v>1.8</v>
@@ -4882,16 +4882,16 @@
         <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X23" t="n">
         <v>15.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA23" t="n">
         <v>80</v>
@@ -4903,7 +4903,7 @@
         <v>9.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE23" t="n">
         <v>55</v>
@@ -4933,7 +4933,7 @@
         <v>140</v>
       </c>
       <c r="AN23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO23" t="n">
         <v>60</v>
@@ -4942,13 +4942,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT23" t="n">
         <v>6.8</v>
@@ -4960,7 +4960,7 @@
         <v>10.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX23" t="n">
         <v>10.5</v>
@@ -4972,29 +4972,29 @@
         <v>13.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BC23" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG23" t="n">
-        <v>32</v>
+        <v>3.95</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
         <v>1.8</v>
       </c>
       <c r="I24" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="J24" t="n">
         <v>4</v>
@@ -5043,7 +5043,7 @@
         <v>4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
@@ -5067,7 +5067,7 @@
         <v>3.55</v>
       </c>
       <c r="T24" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U24" t="n">
         <v>2.02</v>
@@ -5172,7 +5172,7 @@
         <v>40</v>
       </c>
       <c r="BC24" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BD24" t="n">
         <v>50</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
         <v>19</v>
       </c>
       <c r="AA25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB25" t="n">
         <v>22</v>
@@ -5324,7 +5324,7 @@
         <v>15.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AP25" t="n">
         <v>28</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>
@@ -5413,170 +5413,170 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>2.74</v>
       </c>
       <c r="O26" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.48</v>
+        <v>2.52</v>
       </c>
       <c r="R26" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>1.48</v>
+        <v>4.3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-05 21:56:39</t>
+          <t>2026-04-06 00:14:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH26"/>
+  <dimension ref="A1:BH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>5.1</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -784,22 +784,22 @@
         <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S2" t="n">
         <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
         <v>2</v>
@@ -808,73 +808,73 @@
         <v>1.12</v>
       </c>
       <c r="W2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA2" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
         <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AE2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM2" t="n">
         <v>140</v>
       </c>
-      <c r="AF2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>150</v>
-      </c>
       <c r="AN2" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP2" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.4</v>
+        <v>15.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
@@ -883,22 +883,22 @@
         <v>10</v>
       </c>
       <c r="AV2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX2" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AW2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8</v>
-      </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -907,20 +907,20 @@
         <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>1.83</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="J4" t="n">
         <v>3.3</v>
@@ -1193,7 +1193,7 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W4" t="n">
         <v>1.23</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="H5" t="n">
         <v>3.5</v>
@@ -1354,10 +1354,10 @@
         <v>2.78</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
         <v>1.16</v>
@@ -1366,31 +1366,31 @@
         <v>2.24</v>
       </c>
       <c r="O5" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="P5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
         <v>1.14</v>
       </c>
       <c r="S5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V5" t="n">
         <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
         <v>7.8</v>
@@ -1405,10 +1405,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1447,69 +1447,69 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU5" t="n">
         <v>3.45</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BD5" t="n">
         <v>3.35</v>
       </c>
-      <c r="AV5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BE5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.6</v>
+        <v>2.66</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Araz Nakhchivan PFK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Etoile Carouge</t>
+          <t>FC Sabah</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1.68</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>1.41</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>1.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1611,10 +1611,10 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
         <v>1000</v>
@@ -1635,75 +1635,75 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,67 +1718,67 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandvikens</t>
+          <t>Etoile Carouge</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="H7" t="n">
-        <v>2.66</v>
+        <v>5.1</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.63</v>
+        <v>2.34</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1793,10 +1793,10 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1805,10 +1805,10 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
         <v>1000</v>
@@ -1829,75 +1829,75 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Sandvikens</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>3.25</v>
+        <v>2.44</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aalesunds</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.92</v>
+        <v>2.36</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="H9" t="n">
-        <v>2.32</v>
+        <v>3.25</v>
       </c>
       <c r="I9" t="n">
-        <v>2.58</v>
+        <v>3.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S9" t="n">
         <v>4.1</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.4</v>
       </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.63</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="X9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AA9" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AB9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD9" t="n">
         <v>17</v>
       </c>
-      <c r="AC9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>14</v>
-      </c>
       <c r="AE9" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AF9" t="n">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AK9" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO9" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AP9" t="n">
-        <v>12</v>
+        <v>3.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>3.65</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>5.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>16.5</v>
+        <v>4.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>12.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>KFUM Oslo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.12</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="H10" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="P10" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="X10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
         <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL10" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN10" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
         <v>4.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.8</v>
+        <v>9.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="AW10" t="n">
         <v>4.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.65</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.95</v>
+        <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.6</v>
+        <v>32</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.4</v>
+        <v>19.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.2</v>
+        <v>19.5</v>
       </c>
       <c r="BD10" t="n">
         <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.75</v>
+        <v>11</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
         <v>1.33</v>
@@ -2527,153 +2527,153 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X11" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR11" t="n">
         <v>4.4</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X11" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>18</v>
-      </c>
       <c r="AS11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW11" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW11" t="n">
+      <c r="AX11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB11" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA11" t="n">
+      <c r="BC11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG11" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>20</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KFUM Oslo</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="J12" t="n">
         <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.41</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.35</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA12" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AF12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG12" t="n">
         <v>13.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AJ12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO12" t="n">
         <v>32</v>
       </c>
-      <c r="AK12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN12" t="n">
+      <c r="AP12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR12" t="n">
         <v>18</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.3</v>
       </c>
       <c r="AS12" t="n">
         <v>4.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BA12" t="n">
-        <v>32</v>
+        <v>4.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>19.5</v>
+        <v>4.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cottbus</t>
+          <t>Aalesunds</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1860 Munich</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.89</v>
+        <v>2.84</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="H13" t="n">
-        <v>3.65</v>
+        <v>2.36</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4</v>
+        <v>2.66</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
         <v>1.3</v>
       </c>
       <c r="M13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="O13" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.6</v>
       </c>
-      <c r="U13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.29</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.92</v>
+        <v>1.45</v>
       </c>
       <c r="X13" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF13" t="n">
         <v>23</v>
       </c>
-      <c r="Z13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL13" t="n">
         <v>48</v>
       </c>
-      <c r="AF13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
+      <c r="AM13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN13" t="n">
         <v>27</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AO13" t="n">
         <v>22</v>
       </c>
-      <c r="AL13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>38</v>
-      </c>
       <c r="AP13" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
         <v>7.4</v>
       </c>
       <c r="AV13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG13" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>25</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Cottbus</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VfL Osnabruck</t>
+          <t>1860 Munich</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="H14" t="n">
-        <v>2.68</v>
+        <v>3.65</v>
       </c>
       <c r="I14" t="n">
-        <v>2.94</v>
+        <v>4.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.14</v>
+        <v>1.62</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9</v>
+        <v>2.54</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="V14" t="n">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="X14" t="n">
-        <v>13.5</v>
+        <v>26</v>
       </c>
       <c r="Y14" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>12</v>
       </c>
-      <c r="Z14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH14" t="n">
+      <c r="BA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD14" t="n">
         <v>21</v>
       </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ14" t="n">
+      <c r="BE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF14" t="n">
         <v>7.8</v>
       </c>
-      <c r="AR14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>27</v>
-      </c>
       <c r="BG14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
@@ -3270,157 +3270,157 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>VfL Osnabruck</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.8</v>
+        <v>2.92</v>
       </c>
       <c r="G15" t="n">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.52</v>
+        <v>2.58</v>
       </c>
       <c r="I15" t="n">
-        <v>1.69</v>
+        <v>2.82</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="P15" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.52</v>
+        <v>2.16</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="U15" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="V15" t="n">
-        <v>2.44</v>
+        <v>1.55</v>
       </c>
       <c r="W15" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="X15" t="n">
-        <v>32</v>
+        <v>13.5</v>
       </c>
       <c r="Y15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>14</v>
       </c>
-      <c r="Z15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA15" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
         <v>1.03</v>
@@ -3435,14 +3435,14 @@
         <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.6</v>
+        <v>25</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
@@ -3464,28 +3464,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Erzgebirge</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H16" t="n">
         <v>2.62</v>
       </c>
-      <c r="H16" t="n">
-        <v>2.88</v>
-      </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
         <v>950</v>
@@ -3494,25 +3494,25 @@
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="S16" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -3521,10 +3521,10 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W16" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FC Nordsjaelland</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.28</v>
+        <v>5.9</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42</v>
+        <v>7.6</v>
       </c>
       <c r="H17" t="n">
-        <v>3.15</v>
+        <v>1.52</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>1.66</v>
       </c>
       <c r="J17" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="T17" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="U17" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>2.48</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH17" t="n">
         <v>23</v>
       </c>
-      <c r="Y17" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
+      <c r="AI17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AP17" t="n">
         <v>20</v>
       </c>
-      <c r="AG17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.7</v>
+        <v>20</v>
       </c>
       <c r="BB17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>46</v>
+      </c>
+      <c r="BG17" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>18</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
@@ -3852,28 +3852,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H18" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="I18" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
         <v>950</v>
@@ -3882,37 +3882,37 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="O18" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="R18" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U18" t="n">
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,36 +4041,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14:00:59</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Vizela</t>
+          <t>FC Nordsjaelland</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="G19" t="n">
-        <v>120</v>
+        <v>2.42</v>
       </c>
       <c r="H19" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="I19" t="n">
-        <v>120</v>
+        <v>3.35</v>
       </c>
       <c r="J19" t="n">
-        <v>1.09</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,40 +4079,40 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>1.02</v>
+        <v>4.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="P19" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="T19" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="U19" t="n">
-        <v>1.84</v>
+        <v>2.46</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z19" t="n">
         <v>1000</v>
@@ -4121,25 +4121,25 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
@@ -4157,75 +4157,75 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,72 +4235,72 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:59</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FC Wil</t>
+          <t>Vizela</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neuchatel Xamax</t>
+          <t>Benfica B</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="G20" t="n">
-        <v>2.88</v>
+        <v>120</v>
       </c>
       <c r="H20" t="n">
-        <v>2.74</v>
+        <v>1.09</v>
       </c>
       <c r="I20" t="n">
-        <v>3.9</v>
+        <v>120</v>
       </c>
       <c r="J20" t="n">
-        <v>3.05</v>
+        <v>1.09</v>
       </c>
       <c r="K20" t="n">
-        <v>5.1</v>
+        <v>120</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>2.28</v>
+        <v>1.02</v>
       </c>
       <c r="O20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P20" t="n">
         <v>1.25</v>
       </c>
-      <c r="P20" t="n">
-        <v>1.94</v>
-      </c>
       <c r="Q20" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="S20" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4357,52 +4357,52 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,108 +4623,108 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>FC Wil</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Neuchatel Xamax</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5.2</v>
+        <v>2.28</v>
       </c>
       <c r="G22" t="n">
-        <v>6.4</v>
+        <v>2.96</v>
       </c>
       <c r="H22" t="n">
-        <v>1.67</v>
+        <v>2.74</v>
       </c>
       <c r="I22" t="n">
-        <v>1.83</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.65</v>
+        <v>2.28</v>
       </c>
       <c r="O22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="T22" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="X22" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
         <v>1000</v>
@@ -4742,72 +4742,72 @@
         <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.22</v>
+        <v>5.4</v>
       </c>
       <c r="G23" t="n">
-        <v>2.48</v>
+        <v>6.4</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2</v>
+        <v>1.67</v>
       </c>
       <c r="I23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J23" t="n">
         <v>3.75</v>
       </c>
-      <c r="J23" t="n">
-        <v>3.25</v>
-      </c>
       <c r="K23" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L23" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="P23" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="T23" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>2.24</v>
       </c>
       <c r="W23" t="n">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT23" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y23" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR23" t="n">
+      <c r="AU23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>17.5</v>
       </c>
-      <c r="AS23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY23" t="n">
+      <c r="BA23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG23" t="n">
         <v>8.4</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="G24" t="n">
-        <v>5.2</v>
+        <v>2.48</v>
       </c>
       <c r="H24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T24" t="n">
         <v>1.8</v>
       </c>
-      <c r="I24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="U24" t="n">
+        <v>2</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS24" t="n">
         <v>4</v>
       </c>
-      <c r="K24" t="n">
+      <c r="AT24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE24" t="n">
         <v>4.1</v>
       </c>
-      <c r="L24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V24" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X24" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>60</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>75</v>
-      </c>
       <c r="BF24" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="BG24" t="n">
-        <v>11</v>
+        <v>3.95</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Cove Rangers</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>2.26</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="K25" t="n">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L25" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="O25" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>1.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8</v>
+        <v>1.08</v>
       </c>
       <c r="S25" t="n">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="T25" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 00:14:41</t>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,184 +5399,960 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="G26" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>2.26</v>
       </c>
       <c r="J26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U26" t="n">
         <v>2.94</v>
       </c>
-      <c r="K26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.82</v>
-      </c>
       <c r="V26" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="W26" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="X26" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD26" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD26" t="n">
+      <c r="AE26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR26" t="n">
         <v>18</v>
       </c>
-      <c r="AE26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH26" t="n">
+      <c r="AS26" t="n">
         <v>26</v>
       </c>
-      <c r="AI26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AT26" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AU26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AV26" t="n">
         <v>10.5</v>
       </c>
       <c r="AW26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sporting Lisbon</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J27" t="n">
         <v>4</v>
       </c>
-      <c r="AX26" t="n">
+      <c r="K27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X27" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>60</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>48</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Aguilas Doradas</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X28" t="n">
         <v>11.5</v>
       </c>
-      <c r="AY26" t="n">
+      <c r="Y28" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY28" t="n">
         <v>9.6</v>
       </c>
-      <c r="AZ26" t="n">
+      <c r="AZ28" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Queretaro</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG29" t="n">
         <v>17</v>
       </c>
-      <c r="BA26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE26" t="n">
+      <c r="AH29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG29" t="n">
         <v>4.2</v>
       </c>
-      <c r="BF26" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH26" t="inlineStr">
-        <is>
-          <t>2026-04-06 00:14:41</t>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Real Santander</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K30" t="n">
+        <v>15</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH30"/>
+  <dimension ref="A1:BH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J2" t="n">
         <v>5.1</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -784,22 +784,22 @@
         <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
         <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U2" t="n">
         <v>2</v>
@@ -808,7 +808,7 @@
         <v>1.12</v>
       </c>
       <c r="W2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -817,10 +817,10 @@
         <v>32</v>
       </c>
       <c r="Z2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AB2" t="n">
         <v>9.6</v>
@@ -844,7 +844,7 @@
         <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ2" t="n">
         <v>12.5</v>
@@ -859,22 +859,22 @@
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
         <v>140</v>
       </c>
       <c r="AP2" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>26</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
@@ -883,22 +883,22 @@
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
         <v>22</v>
       </c>
       <c r="BA2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -907,20 +907,20 @@
         <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:15:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Manisa FK</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Shamakhi FK</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>2.26</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,22 +1169,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P4" t="n">
         <v>1.24</v>
       </c>
-      <c r="P4" t="n">
-        <v>1.87</v>
-      </c>
       <c r="Q4" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>1.46</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1193,10 +1193,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,78 +1325,78 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Manisa FK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="G5" t="n">
-        <v>2.72</v>
+        <v>5.4</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>2.26</v>
       </c>
       <c r="J5" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="O5" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>1.67</v>
       </c>
       <c r="R5" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.79</v>
       </c>
       <c r="W5" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="X5" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
         <v>1000</v>
@@ -1405,7 +1405,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
         <v>1000</v>
@@ -1447,69 +1447,69 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.54</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.72</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.98</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.82</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.58</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.32</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.64</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,78 +1519,78 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Araz Nakhchivan PFK</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Sabah</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N6" t="n">
-        <v>1.41</v>
+        <v>2.26</v>
       </c>
       <c r="O6" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="P6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.28</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1599,7 +1599,7 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC6" t="n">
         <v>1000</v>
@@ -1641,69 +1641,69 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>2.78</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>2.78</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>2.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>2.72</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,72 +1713,72 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Araz Nakhchivan PFK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Etoile Carouge</t>
+          <t>FC Sabah</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1.72</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>2.22</v>
+        <v>1.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1793,10 +1793,10 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1805,10 +1805,10 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
         <v>1000</v>
@@ -1829,75 +1829,75 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,67 +1912,67 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sandvikens</t>
+          <t>Etoile Carouge</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="H8" t="n">
-        <v>2.44</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -1987,10 +1987,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -1999,10 +1999,10 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
@@ -2023,75 +2023,75 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Sandvikens</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="G9" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="H9" t="n">
-        <v>3.25</v>
+        <v>2.66</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="P9" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KFUM Oslo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I10" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
         <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG10" t="n">
         <v>13.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO10" t="n">
         <v>60</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>44</v>
-      </c>
       <c r="AP10" t="n">
-        <v>14.5</v>
+        <v>3.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>3.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.6</v>
+        <v>3.65</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AW10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA10" t="n">
-        <v>32</v>
+        <v>5.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>19.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>19.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,25 +2494,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aalesunds</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.16</v>
+        <v>2.84</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6</v>
+        <v>2.64</v>
       </c>
       <c r="J11" t="n">
         <v>3.6</v>
@@ -2521,152 +2521,152 @@
         <v>4.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="U11" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="V11" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="W11" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AC11" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ11" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AK11" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN11" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AP11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW11" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR11" t="n">
+      <c r="AX11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA11" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BB11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC11" t="n">
         <v>4.3</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.85</v>
+        <v>20</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X12" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR12" t="n">
         <v>4.4</v>
       </c>
-      <c r="O12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X12" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>18</v>
-      </c>
       <c r="AS12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW12" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW12" t="n">
+      <c r="AX12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB12" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA12" t="n">
+      <c r="BC12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG12" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>20</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Aalesunds</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.84</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="H13" t="n">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="U13" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="X13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AA13" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AB13" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC13" t="n">
         <v>10.5</v>
       </c>
       <c r="AD13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP13" t="n">
         <v>14</v>
       </c>
-      <c r="AE13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP13" t="n">
+      <c r="AQ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>12</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13.5</v>
       </c>
       <c r="BA13" t="n">
         <v>4.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.2</v>
+        <v>17.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE13" t="n">
         <v>4.6</v>
       </c>
       <c r="BF13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG13" t="n">
         <v>20</v>
       </c>
-      <c r="BG13" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cottbus</t>
+          <t>KFUM Oslo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1860 Munich</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="H14" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="R14" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="U14" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="X14" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK14" t="n">
         <v>26</v>
       </c>
-      <c r="Y14" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AL14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP14" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT14" t="n">
         <v>9.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF14" t="n">
         <v>11</v>
       </c>
-      <c r="AY14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BG14" t="n">
-        <v>24</v>
+        <v>4.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Cottbus</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VfL Osnabruck</t>
+          <t>1860 Munich</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.92</v>
+        <v>1.9</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2</v>
+        <v>2.08</v>
       </c>
       <c r="H15" t="n">
-        <v>2.58</v>
+        <v>3.65</v>
       </c>
       <c r="I15" t="n">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="P15" t="n">
-        <v>1.75</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.16</v>
+        <v>1.62</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9</v>
+        <v>2.54</v>
       </c>
       <c r="T15" t="n">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="U15" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>1.45</v>
+        <v>1.92</v>
       </c>
       <c r="X15" t="n">
-        <v>13.5</v>
+        <v>26</v>
       </c>
       <c r="Y15" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC15" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO15" t="n">
         <v>38</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AP15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD15" t="n">
         <v>21</v>
       </c>
-      <c r="AG15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BE15" t="n">
         <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>27</v>
+        <v>7.6</v>
       </c>
       <c r="BG15" t="n">
         <v>25</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -3658,157 +3658,157 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>VfL Osnabruck</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU17" t="n">
         <v>5.9</v>
       </c>
-      <c r="G17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X17" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AV17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>14</v>
       </c>
-      <c r="Z17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA17" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
         <v>1.03</v>
@@ -3823,14 +3823,14 @@
         <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.6</v>
+        <v>25</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -3852,103 +3852,103 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Erzgebirge</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>2.62</v>
+        <v>7.4</v>
       </c>
       <c r="H18" t="n">
-        <v>2.88</v>
+        <v>1.52</v>
       </c>
       <c r="I18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J18" t="n">
         <v>4.3</v>
       </c>
-      <c r="J18" t="n">
-        <v>3.25</v>
-      </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>2.04</v>
+        <v>5.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>2.58</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="S18" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T18" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3</v>
+        <v>2.56</v>
       </c>
       <c r="W18" t="n">
-        <v>1.62</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF18" t="n">
         <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ18" t="n">
         <v>1000</v>
@@ -3966,72 +3966,72 @@
         <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,73 +4046,73 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FC Nordsjaelland</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Erzgebirge</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="H19" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="I19" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7</v>
+        <v>2.04</v>
       </c>
       <c r="O19" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="T19" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="U19" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="X19" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
         <v>1000</v>
@@ -4121,25 +4121,25 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
@@ -4157,75 +4157,75 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,36 +4235,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14:00:59</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Vizela</t>
+          <t>FC Nordsjaelland</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="G20" t="n">
-        <v>120</v>
+        <v>2.42</v>
       </c>
       <c r="H20" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="I20" t="n">
-        <v>120</v>
+        <v>3.35</v>
       </c>
       <c r="J20" t="n">
-        <v>1.09</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>120</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -4273,40 +4273,40 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="U20" t="n">
-        <v>1.84</v>
+        <v>2.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z20" t="n">
         <v>1000</v>
@@ -4315,25 +4315,25 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
@@ -4351,75 +4351,75 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,75 +4429,75 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:59</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>Vizela</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Benfica B</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.32</v>
+        <v>1.96</v>
       </c>
       <c r="G21" t="n">
-        <v>1.41</v>
+        <v>120</v>
       </c>
       <c r="H21" t="n">
-        <v>9.4</v>
+        <v>1.09</v>
       </c>
       <c r="I21" t="n">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>1.09</v>
       </c>
       <c r="K21" t="n">
-        <v>6.6</v>
+        <v>120</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>5.3</v>
+        <v>1.02</v>
       </c>
       <c r="O21" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="P21" t="n">
-        <v>2.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="R21" t="n">
-        <v>1.59</v>
+        <v>1.02</v>
       </c>
       <c r="S21" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="T21" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="U21" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="V21" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
         <v>1000</v>
@@ -4509,10 +4509,10 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
         <v>1000</v>
@@ -4521,22 +4521,22 @@
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
         <v>1000</v>
@@ -4545,68 +4545,68 @@
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FC Wil</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neuchatel Xamax</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.28</v>
+        <v>1.32</v>
       </c>
       <c r="G22" t="n">
-        <v>2.96</v>
+        <v>1.4</v>
       </c>
       <c r="H22" t="n">
-        <v>2.74</v>
+        <v>9.4</v>
       </c>
       <c r="I22" t="n">
+        <v>13</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF22" t="n">
         <v>3.9</v>
       </c>
-      <c r="J22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="BG22" t="n">
         <v>5.1</v>
       </c>
-      <c r="L22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>FC Wil</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Neuchatel Xamax</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.4</v>
+        <v>2.32</v>
       </c>
       <c r="G23" t="n">
-        <v>6.4</v>
+        <v>2.62</v>
       </c>
       <c r="H23" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N23" t="n">
         <v>3.75</v>
       </c>
-      <c r="K23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.7</v>
-      </c>
       <c r="O23" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="T23" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="U23" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="V23" t="n">
-        <v>2.24</v>
+        <v>1.38</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="X23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="AA23" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AB23" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AC23" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>19.5</v>
+        <v>38</v>
       </c>
       <c r="AF23" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="AG23" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AI23" t="n">
         <v>46</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="AP23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AS23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX23" t="n">
         <v>13</v>
       </c>
-      <c r="AT23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AY23" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.5</v>
+        <v>19</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="BG23" t="n">
-        <v>8.4</v>
+        <v>19.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="G24" t="n">
-        <v>2.48</v>
+        <v>6.4</v>
       </c>
       <c r="H24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
         <v>3.2</v>
       </c>
-      <c r="I24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.7</v>
-      </c>
       <c r="T24" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V24" t="n">
-        <v>1.36</v>
+        <v>2.26</v>
       </c>
       <c r="W24" t="n">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="X24" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT24" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y24" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR24" t="n">
+      <c r="AU24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>17.5</v>
       </c>
-      <c r="AS24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY24" t="n">
+      <c r="BA24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG24" t="n">
         <v>8.4</v>
       </c>
-      <c r="AZ24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cove Rangers</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="P25" t="n">
-        <v>1.08</v>
+        <v>1.78</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="R25" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>1.24</v>
+        <v>3.35</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,184 +5399,184 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Cove Rangers</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>2.26</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="K26" t="n">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L26" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="O26" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="P26" t="n">
-        <v>2.98</v>
+        <v>1.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="R26" t="n">
-        <v>1.8</v>
+        <v>1.08</v>
       </c>
       <c r="S26" t="n">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="T26" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR26" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AS26" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AT26" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AU26" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AV26" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW26" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AX26" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AY26" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA26" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BB26" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BC26" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BD26" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BE26" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BF26" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="H27" t="n">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="I27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R27" t="n">
         <v>1.8</v>
       </c>
-      <c r="J27" t="n">
-        <v>4</v>
-      </c>
-      <c r="K27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.37</v>
-      </c>
       <c r="S27" t="n">
-        <v>3.55</v>
+        <v>2.18</v>
       </c>
       <c r="T27" t="n">
-        <v>1.92</v>
+        <v>1.48</v>
       </c>
       <c r="U27" t="n">
-        <v>2.02</v>
+        <v>2.94</v>
       </c>
       <c r="V27" t="n">
-        <v>2.24</v>
+        <v>1.79</v>
       </c>
       <c r="W27" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="X27" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="Z27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC27" t="n">
         <v>10.5</v>
       </c>
-      <c r="AA27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AD27" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AE27" t="n">
         <v>19</v>
       </c>
       <c r="AF27" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AG27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT27" t="n">
         <v>20</v>
       </c>
-      <c r="AH27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP27" t="n">
+      <c r="AU27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY27" t="n">
         <v>13</v>
       </c>
-      <c r="AQ27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AZ27" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BB27" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BC27" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="BD27" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="BE27" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="BF27" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="BG27" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.58</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>2.86</v>
+        <v>5.1</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>1.81</v>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>1.83</v>
       </c>
       <c r="J28" t="n">
-        <v>2.94</v>
+        <v>3.95</v>
       </c>
       <c r="K28" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M28" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>2.74</v>
+        <v>3.85</v>
       </c>
       <c r="O28" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="P28" t="n">
-        <v>1.58</v>
+        <v>1.96</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.52</v>
+        <v>2.02</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="S28" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="U28" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="V28" t="n">
-        <v>1.39</v>
+        <v>2.2</v>
       </c>
       <c r="W28" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="X28" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO28" t="n">
         <v>12</v>
       </c>
-      <c r="Z28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE28" t="n">
+      <c r="AP28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC28" t="n">
         <v>60</v>
       </c>
-      <c r="AF28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BD28" t="n">
-        <v>4.1</v>
+        <v>60</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.2</v>
+        <v>95</v>
       </c>
       <c r="BF28" t="n">
-        <v>3.95</v>
+        <v>65</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,378 +5981,572 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Aguilas Doradas</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="G29" t="n">
-        <v>3.9</v>
+        <v>2.86</v>
       </c>
       <c r="H29" t="n">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q29" t="n">
         <v>2.52</v>
       </c>
-      <c r="J29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.88</v>
-      </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="T29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="V29" t="n">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="W29" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="X29" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="Y29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AA29" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AB29" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE29" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AF29" t="n">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH29" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AI29" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK29" t="n">
         <v>46</v>
       </c>
       <c r="AL29" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AO29" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="AP29" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AT29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX29" t="n">
         <v>11.5</v>
       </c>
-      <c r="AU29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AY29" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BG29" t="n">
         <v>4.2</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Queretaro</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-06 04:52:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Real Santander</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="F31" t="n">
         <v>1.69</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G31" t="n">
         <v>2.34</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H31" t="n">
         <v>3.15</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I31" t="n">
         <v>6.2</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J31" t="n">
         <v>2.84</v>
       </c>
-      <c r="K30" t="n">
-        <v>15</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="K31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N31" t="n">
         <v>2.48</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O31" t="n">
         <v>1.42</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P31" t="n">
         <v>1.55</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q31" t="n">
         <v>2.14</v>
       </c>
-      <c r="R30" t="n">
+      <c r="R31" t="n">
         <v>1.14</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S31" t="n">
         <v>3.2</v>
       </c>
-      <c r="T30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V30" t="n">
+      <c r="T31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V31" t="n">
         <v>1.2</v>
       </c>
-      <c r="W30" t="n">
+      <c r="W31" t="n">
         <v>1.74</v>
       </c>
-      <c r="X30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH30" t="inlineStr">
-        <is>
-          <t>2026-04-06 02:33:27</t>
+      <c r="X31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH31"/>
+  <dimension ref="A1:BH35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G2" t="n">
         <v>1.46</v>
@@ -766,13 +766,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2" t="n">
         <v>5.1</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -784,13 +784,13 @@
         <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
         <v>1.53</v>
@@ -799,7 +799,7 @@
         <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
         <v>2</v>
@@ -820,10 +820,10 @@
         <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC2" t="n">
         <v>11.5</v>
@@ -844,7 +844,7 @@
         <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ2" t="n">
         <v>12.5</v>
@@ -856,13 +856,13 @@
         <v>34</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AO2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP2" t="n">
         <v>19.5</v>
@@ -871,10 +871,10 @@
         <v>26</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS2" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
@@ -883,7 +883,7 @@
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="AW2" t="n">
         <v>16</v>
@@ -892,13 +892,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -913,21 +913,21 @@
         <v>16</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,17 +937,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Imisli FK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>PFK Turan Tovuz</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -966,31 +966,31 @@
         <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1059,52 +1059,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Azerbaijan Premier League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,17 +1131,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10:15:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shamakhi FK</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1157,7 +1157,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1166,25 +1166,25 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -1325,168 +1325,168 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Manisa FK</t>
+          <t>Bandirmaspor</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Sariyer G.K.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.35</v>
+        <v>2.08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.4</v>
+        <v>2.38</v>
       </c>
       <c r="H5" t="n">
-        <v>1.83</v>
+        <v>3.55</v>
       </c>
       <c r="I5" t="n">
-        <v>2.26</v>
+        <v>4.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="R5" t="n">
         <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V5" t="n">
-        <v>1.79</v>
+        <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>1.23</v>
+        <v>1.74</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AS5" t="n">
         <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW5" t="n">
         <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
         <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>1.03</v>
@@ -1495,21 +1495,21 @@
         <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,78 +1519,78 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>10:15:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Shamakhi FK</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.26</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.68</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>1.46</v>
       </c>
       <c r="R6" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>6.4</v>
+        <v>1.46</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1599,7 +1599,7 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
         <v>1000</v>
@@ -1641,69 +1641,69 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.78</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.78</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.9</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.88</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.66</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.7</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.72</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premier League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,60 +1713,60 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Araz Nakhchivan PFK</t>
+          <t>Manisa FK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Sabah</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>1.41</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.28</v>
+        <v>1.72</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,78 +1907,78 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Etoile Carouge</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.54</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.66</v>
+        <v>2.72</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X8" t="n">
         <v>7.6</v>
       </c>
-      <c r="J8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1987,10 +1987,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -1999,10 +1999,10 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
@@ -2023,75 +2023,75 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AQ8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR8" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>4.7</v>
       </c>
       <c r="AS8" t="n">
         <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.4</v>
+        <v>3.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.9</v>
+        <v>3.05</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.6</v>
+        <v>3.95</v>
       </c>
       <c r="AY8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA8" t="n">
         <v>8</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA8" t="n">
+      <c r="BB8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,33 +2101,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Araz Nakhchivan PFK</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sandvikens</t>
+          <t>FC Sabah</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2139,34 +2139,34 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
         <v>1.28</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.74</v>
+        <v>1.28</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2223,52 +2223,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="n">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="H10" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.6</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.2</v>
-      </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>1.73</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="T10" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="U10" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
         <v>75</v>
       </c>
       <c r="AB10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC10" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC10" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF10" t="n">
         <v>17.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AJ10" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AK10" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AM10" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="AN10" t="n">
-        <v>32</v>
+        <v>14.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.9</v>
+        <v>14.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.8</v>
+        <v>12.5</v>
       </c>
       <c r="AR10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW10" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AX10" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD10" t="n">
         <v>4.5</v>
       </c>
-      <c r="BA10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC10" t="n">
+      <c r="BE10" t="n">
         <v>4.8</v>
       </c>
-      <c r="BD10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BF10" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Aalesunds</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Bodrum Belediyesi Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>1.96</v>
       </c>
       <c r="H11" t="n">
-        <v>2.44</v>
+        <v>3.85</v>
       </c>
       <c r="I11" t="n">
-        <v>2.64</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>1.83</v>
       </c>
       <c r="O11" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W11" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.47</v>
-      </c>
       <c r="X11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,70 +2688,70 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Etoile Carouge</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.18</v>
+        <v>1.54</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="I12" t="n">
-        <v>3.55</v>
+        <v>7.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="R12" t="n">
         <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="U12" t="n">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="W12" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="X12" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
         <v>1000</v>
@@ -2763,10 +2763,10 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2775,10 +2775,10 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
         <v>1000</v>
@@ -2787,87 +2787,87 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4</v>
-      </c>
       <c r="BA12" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="BD12" t="n">
         <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sandvikens</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G13" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="I13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.6</v>
       </c>
-      <c r="J13" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="P13" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y13" t="n">
         <v>17.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG13" t="n">
         <v>13.5</v>
       </c>
       <c r="AH13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR13" t="n">
         <v>18.5</v>
       </c>
-      <c r="AI13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>18</v>
-      </c>
       <c r="AS13" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AT13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY13" t="n">
         <v>9.4</v>
       </c>
-      <c r="AU13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>3.55</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="BC13" t="n">
-        <v>17.5</v>
+        <v>3.75</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BF13" t="n">
         <v>11.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>20</v>
+        <v>3.95</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KFUM Oslo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="G14" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I14" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S14" t="n">
         <v>4.1</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="U14" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W14" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y14" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
         <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF14" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG14" t="n">
         <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO14" t="n">
         <v>60</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>44</v>
-      </c>
       <c r="AP14" t="n">
-        <v>14.5</v>
+        <v>3.9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11</v>
+        <v>3.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.6</v>
+        <v>3.65</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AW14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA14" t="n">
-        <v>32</v>
+        <v>5.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>19.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC14" t="n">
-        <v>19.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cottbus</t>
+          <t>Aalesunds</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1860 Munich</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.9</v>
+        <v>2.84</v>
       </c>
       <c r="G15" t="n">
-        <v>2.08</v>
+        <v>3.1</v>
       </c>
       <c r="H15" t="n">
-        <v>3.65</v>
+        <v>2.44</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>2.64</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O15" t="n">
         <v>1.27</v>
       </c>
-      <c r="M15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.21</v>
-      </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="U15" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="W15" t="n">
-        <v>1.92</v>
+        <v>1.47</v>
       </c>
       <c r="X15" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Z15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI15" t="n">
         <v>38</v>
       </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE15" t="n">
+      <c r="AJ15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL15" t="n">
         <v>48</v>
       </c>
-      <c r="AF15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="AM15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN15" t="n">
         <v>27</v>
       </c>
-      <c r="AK15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AO15" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AP15" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU15" t="n">
         <v>7.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AX15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY15" t="n">
         <v>11</v>
       </c>
-      <c r="AY15" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>17.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>14</v>
+        <v>5.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>21</v>
+        <v>5.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BG15" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>KFUM Oslo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="G16" t="n">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="H16" t="n">
-        <v>2.62</v>
+        <v>3.35</v>
       </c>
       <c r="I16" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="P16" t="n">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="R16" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.06</v>
+        <v>3.05</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VfL Osnabruck</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H17" t="n">
         <v>2.92</v>
       </c>
-      <c r="G17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2.58</v>
-      </c>
       <c r="I17" t="n">
-        <v>2.82</v>
+        <v>3.95</v>
       </c>
       <c r="J17" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5</v>
+        <v>500</v>
       </c>
       <c r="L17" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.76</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.16</v>
+        <v>1.59</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X17" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY17" t="n">
         <v>3.9</v>
       </c>
-      <c r="T17" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>4.3</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF17" t="n">
-        <v>27</v>
+        <v>4.1</v>
       </c>
       <c r="BG17" t="n">
-        <v>25</v>
+        <v>4.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -3852,103 +3852,103 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>2.06</v>
       </c>
       <c r="G18" t="n">
-        <v>7.4</v>
+        <v>2.66</v>
       </c>
       <c r="H18" t="n">
-        <v>1.52</v>
+        <v>2.62</v>
       </c>
       <c r="I18" t="n">
-        <v>1.67</v>
+        <v>3.75</v>
       </c>
       <c r="J18" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>5.3</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="O18" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="P18" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="R18" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="S18" t="n">
-        <v>2.34</v>
+        <v>1.76</v>
       </c>
       <c r="T18" t="n">
-        <v>1.69</v>
+        <v>1.35</v>
       </c>
       <c r="U18" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>2.56</v>
+        <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="X18" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
         <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
         <v>1000</v>
@@ -3966,65 +3966,65 @@
         <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -4046,127 +4046,127 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Cottbus</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Erzgebirge</t>
+          <t>1860 Munich</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="G19" t="n">
-        <v>2.56</v>
+        <v>2.06</v>
       </c>
       <c r="H19" t="n">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="I19" t="n">
         <v>4.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T19" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V19" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W19" t="n">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AR19" t="n">
         <v>1.03</v>
@@ -4175,57 +4175,57 @@
         <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW19" t="n">
         <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA19" t="n">
         <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE19" t="n">
         <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FC Nordsjaelland</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>VfL Osnabruck</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.28</v>
+        <v>2.92</v>
       </c>
       <c r="G20" t="n">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="H20" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J20" t="n">
         <v>3.15</v>
       </c>
-      <c r="I20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.7</v>
-      </c>
       <c r="K20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.9</v>
       </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T20" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="U20" t="n">
-        <v>2.44</v>
+        <v>2.04</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="X20" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="Y20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z20" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF20" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG20" t="n">
         <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP20" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV20" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="BG20" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,108 +4429,108 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14:00:59</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Vizela</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.96</v>
+        <v>5.9</v>
       </c>
       <c r="G21" t="n">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="I21" t="n">
-        <v>120</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>1.09</v>
+        <v>4.7</v>
       </c>
       <c r="K21" t="n">
-        <v>120</v>
+        <v>5.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>1.02</v>
+        <v>5.7</v>
       </c>
       <c r="O21" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R21" t="n">
-        <v>1.02</v>
+        <v>1.64</v>
       </c>
       <c r="S21" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="T21" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="U21" t="n">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF21" t="n">
         <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
@@ -4548,72 +4548,72 @@
         <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,33 +4623,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Erzgebirge</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.32</v>
+        <v>1.97</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="H22" t="n">
-        <v>9.4</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
         <v>6.4</v>
@@ -4658,40 +4658,40 @@
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>5.3</v>
+        <v>2.04</v>
       </c>
       <c r="O22" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="R22" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="T22" t="n">
-        <v>1.89</v>
+        <v>1.49</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="W22" t="n">
-        <v>3.5</v>
+        <v>1.66</v>
       </c>
       <c r="X22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
         <v>1000</v>
@@ -4703,10 +4703,10 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4715,22 +4715,22 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
         <v>1000</v>
@@ -4739,75 +4739,75 @@
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FC Wil</t>
+          <t>FC Nordsjaelland</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neuchatel Xamax</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G23" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="H23" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="K23" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="R23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.42</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.38</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="X23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Y23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD23" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AE23" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG23" t="n">
         <v>13.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="AQ23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV23" t="n">
         <v>12</v>
       </c>
-      <c r="AR23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS23" t="n">
+      <c r="AW23" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW23" t="n">
+      <c r="AX23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC23" t="n">
         <v>4.6</v>
       </c>
-      <c r="AX23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>19</v>
-      </c>
       <c r="BD23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BG23" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5.4</v>
+        <v>2.22</v>
       </c>
       <c r="G24" t="n">
-        <v>6.4</v>
+        <v>2.44</v>
       </c>
       <c r="H24" t="n">
-        <v>1.66</v>
+        <v>3.05</v>
       </c>
       <c r="I24" t="n">
-        <v>1.79</v>
+        <v>3.45</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="K24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X24" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB24" t="n">
         <v>4.3</v>
       </c>
-      <c r="L24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V24" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X24" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX24" t="n">
+      <c r="BC24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE24" t="n">
         <v>4.6</v>
       </c>
-      <c r="AY24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BF24" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:59</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>Vizela</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Benfica B</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="G25" t="n">
-        <v>2.48</v>
+        <v>120</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2</v>
+        <v>1.09</v>
       </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>120</v>
       </c>
       <c r="J25" t="n">
-        <v>3.25</v>
+        <v>1.09</v>
       </c>
       <c r="K25" t="n">
-        <v>3.8</v>
+        <v>120</v>
       </c>
       <c r="L25" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="O25" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="P25" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R25" t="n">
-        <v>1.29</v>
+        <v>1.02</v>
       </c>
       <c r="S25" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="T25" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="V25" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>FC Wil</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cove Rangers</t>
+          <t>Neuchatel Xamax</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="J26" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="O26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P26" t="n">
-        <v>1.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.08</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>1.24</v>
+        <v>2.9</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>1.32</v>
       </c>
       <c r="G27" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="H27" t="n">
-        <v>2.24</v>
+        <v>8.6</v>
       </c>
       <c r="I27" t="n">
-        <v>2.26</v>
+        <v>12.5</v>
       </c>
       <c r="J27" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
         <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="R27" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="S27" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="T27" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="U27" t="n">
-        <v>2.94</v>
+        <v>1.9</v>
       </c>
       <c r="V27" t="n">
-        <v>1.79</v>
+        <v>1.08</v>
       </c>
       <c r="W27" t="n">
-        <v>1.47</v>
+        <v>3.5</v>
       </c>
       <c r="X27" t="n">
         <v>32</v>
       </c>
       <c r="Y27" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AC27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>27</v>
-      </c>
       <c r="AG27" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="AI27" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>28</v>
+        <v>16.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AQ27" t="n">
-        <v>17.5</v>
+        <v>4.8</v>
       </c>
       <c r="AR27" t="n">
-        <v>18</v>
+        <v>5.1</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>5.3</v>
       </c>
       <c r="AT27" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AU27" t="n">
         <v>10</v>
       </c>
       <c r="AV27" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="AW27" t="n">
-        <v>18</v>
+        <v>5.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>26</v>
+        <v>7.2</v>
       </c>
       <c r="AY27" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>23</v>
+        <v>5.1</v>
       </c>
       <c r="BB27" t="n">
-        <v>44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC27" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="BD27" t="n">
-        <v>27</v>
+        <v>4.7</v>
       </c>
       <c r="BE27" t="n">
-        <v>42</v>
+        <v>5.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>14</v>
+        <v>3.9</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="G28" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="I28" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L28" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
         <v>3.85</v>
       </c>
       <c r="O28" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.96</v>
       </c>
-      <c r="Q28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.02</v>
-      </c>
       <c r="V28" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="W28" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Y28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z28" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AB28" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AD28" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AG28" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AH28" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI28" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AJ28" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AP28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS28" t="n">
         <v>13</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>17.5</v>
       </c>
       <c r="AT28" t="n">
         <v>15.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="AW28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>17.5</v>
       </c>
-      <c r="AX28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BA28" t="n">
-        <v>32</v>
+        <v>4.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>40</v>
+        <v>4.9</v>
       </c>
       <c r="BC28" t="n">
-        <v>60</v>
+        <v>4.8</v>
       </c>
       <c r="BD28" t="n">
-        <v>60</v>
+        <v>4.8</v>
       </c>
       <c r="BE28" t="n">
-        <v>95</v>
+        <v>4.9</v>
       </c>
       <c r="BF28" t="n">
-        <v>65</v>
+        <v>4.9</v>
       </c>
       <c r="BG28" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.58</v>
+        <v>2.28</v>
       </c>
       <c r="G29" t="n">
-        <v>2.86</v>
+        <v>2.54</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="I29" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="J29" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="K29" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M29" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="O29" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="P29" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X29" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE29" t="n">
         <v>4.9</v>
       </c>
-      <c r="T29" t="n">
-        <v>2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X29" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BF29" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,378 +6175,1154 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Cove Rangers</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.25</v>
+        <v>1.09</v>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>2.22</v>
+        <v>1.09</v>
       </c>
       <c r="I30" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="K30" t="n">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L30" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="O30" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="P30" t="n">
-        <v>1.91</v>
+        <v>1.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="S30" t="n">
-        <v>3.35</v>
+        <v>1.24</v>
       </c>
       <c r="T30" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ30" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR30" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT30" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV30" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW30" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AX30" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY30" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ30" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF30" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X31" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-06 07:11:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sporting Lisbon</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X32" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>70</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-06 07:11:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Aguilas Doradas</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X33" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-06 07:11:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Queretaro</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-06 07:11:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Real Santander</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="F35" t="n">
         <v>1.69</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G35" t="n">
         <v>2.34</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H35" t="n">
         <v>3.15</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I35" t="n">
         <v>6.2</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J35" t="n">
         <v>2.84</v>
       </c>
-      <c r="K31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="K35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N35" t="n">
         <v>2.48</v>
       </c>
-      <c r="O31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="O35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P35" t="n">
         <v>1.55</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q35" t="n">
         <v>2.14</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R35" t="n">
         <v>1.14</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S35" t="n">
         <v>3.2</v>
       </c>
-      <c r="T31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V31" t="n">
+      <c r="T35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V35" t="n">
         <v>1.2</v>
       </c>
-      <c r="W31" t="n">
+      <c r="W35" t="n">
         <v>1.74</v>
       </c>
-      <c r="X31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>2026-04-06 04:52:09</t>
+      <c r="X35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH35"/>
+  <dimension ref="A1:BH37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G2" t="n">
         <v>1.45</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.46</v>
-      </c>
       <c r="H2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J2" t="n">
         <v>5.1</v>
@@ -781,7 +781,7 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.22</v>
@@ -790,25 +790,25 @@
         <v>2.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
         <v>1.12</v>
       </c>
       <c r="W2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -817,10 +817,10 @@
         <v>32</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA2" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AB2" t="n">
         <v>9.800000000000001</v>
@@ -859,7 +859,7 @@
         <v>130</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AO2" t="n">
         <v>130</v>
@@ -874,7 +874,7 @@
         <v>15</v>
       </c>
       <c r="AS2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
@@ -886,13 +886,13 @@
         <v>27</v>
       </c>
       <c r="AW2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
         <v>21</v>
@@ -907,20 +907,20 @@
         <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BE2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BG2" t="n">
         <v>16</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>1.87</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.4</v>
+        <v>2.18</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -1169,16 +1169,16 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1244,7 +1244,7 @@
         <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -1342,37 +1342,37 @@
         <v>2.08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I5" t="n">
         <v>4.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R5" t="n">
         <v>1.3</v>
@@ -1381,16 +1381,16 @@
         <v>3.6</v>
       </c>
       <c r="T5" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X5" t="n">
         <v>15.5</v>
@@ -1402,7 +1402,7 @@
         <v>34</v>
       </c>
       <c r="AA5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB5" t="n">
         <v>11</v>
@@ -1429,7 +1429,7 @@
         <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1450,10 +1450,10 @@
         <v>9.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS5" t="n">
         <v>1.03</v>
@@ -1471,7 +1471,7 @@
         <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY5" t="n">
         <v>8</v>
@@ -1498,11 +1498,11 @@
         <v>14</v>
       </c>
       <c r="BG5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -1533,46 +1533,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1.96</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>5.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.46</v>
+        <v>2.24</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.46</v>
+        <v>2.66</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1581,10 +1581,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>3.85</v>
       </c>
       <c r="G7" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="n">
         <v>1.89</v>
@@ -1745,7 +1745,7 @@
         <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
@@ -1757,7 +1757,7 @@
         <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q7" t="n">
         <v>1.72</v>
@@ -1775,7 +1775,7 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W7" t="n">
         <v>1.25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H8" t="n">
         <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J8" t="n">
         <v>2.84</v>
@@ -1945,7 +1945,7 @@
         <v>1.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O8" t="n">
         <v>1.63</v>
@@ -1954,7 +1954,7 @@
         <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R8" t="n">
         <v>1.16</v>
@@ -1963,13 +1963,13 @@
         <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
         <v>1.59</v>
@@ -2038,22 +2038,22 @@
         <v>4.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AX8" t="n">
         <v>4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.95</v>
       </c>
       <c r="AY8" t="n">
         <v>5.4</v>
@@ -2065,7 +2065,7 @@
         <v>8</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
         <v>3.2</v>
@@ -2077,14 +2077,14 @@
         <v>5.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -2118,55 +2118,55 @@
         <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>1.66</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.28</v>
+        <v>1.71</v>
       </c>
       <c r="R9" t="n">
         <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2274,11 +2274,11 @@
         <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
         <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X10" t="n">
         <v>22</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bodrum Belediyesi Bodrumspor</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>1.96</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>8.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2527,22 +2527,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.64</v>
+        <v>1.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>2.56</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2551,10 +2551,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,72 +2683,72 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Etoile Carouge</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="G12" t="n">
-        <v>1.66</v>
+        <v>1.32</v>
       </c>
       <c r="H12" t="n">
-        <v>5.2</v>
+        <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="J12" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="M12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="P12" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="R12" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="U12" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="V12" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2763,10 +2763,10 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2775,10 +2775,10 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
         <v>1000</v>
@@ -2799,75 +2799,75 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>7.8</v>
+        <v>3.85</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.4</v>
+        <v>2.86</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,91 +2882,91 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>KFUM Oslo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sandvikens</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G13" t="n">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="H13" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="I13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N13" t="n">
         <v>4.1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.75</v>
       </c>
       <c r="O13" t="n">
         <v>1.28</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U13" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="X13" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB13" t="n">
         <v>13</v>
       </c>
       <c r="AC13" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AD13" t="n">
         <v>18</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF13" t="n">
         <v>18</v>
@@ -2975,93 +2975,93 @@
         <v>13.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN13" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AR13" t="n">
-        <v>18.5</v>
+        <v>4.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="AX13" t="n">
         <v>10.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.55</v>
+        <v>14.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.75</v>
+        <v>19.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Bodrum Belediyesi Bodrumspor</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.36</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.56</v>
       </c>
-      <c r="H14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4.1</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="W14" t="n">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aalesunds</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Etoile Carouge</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.84</v>
+        <v>1.55</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="H15" t="n">
-        <v>2.44</v>
+        <v>5.4</v>
       </c>
       <c r="I15" t="n">
-        <v>2.64</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>1.47</v>
+        <v>2.42</v>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AG15" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="AO15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>4.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="AR15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB15" t="n">
         <v>12</v>
       </c>
-      <c r="AS15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BC15" t="n">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>16</v>
+        <v>4.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KFUM Oslo</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandvikens</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
-        <v>2.26</v>
+        <v>2.58</v>
       </c>
       <c r="H16" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="I16" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,58 +3497,58 @@
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
         <v>1.28</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="T16" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U16" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
         <v>13</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
         <v>18</v>
       </c>
       <c r="AE16" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
         <v>18</v>
@@ -3557,93 +3557,93 @@
         <v>13.5</v>
       </c>
       <c r="AH16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
         <v>19.5</v>
       </c>
-      <c r="AI16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AO16" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BB16" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC16" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BF16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="H17" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="I17" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K17" t="n">
-        <v>500</v>
+        <v>3.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>2.16</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.59</v>
+        <v>2.18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>2.06</v>
+        <v>4.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="V17" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="X17" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF17" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN17" t="n">
         <v>32</v>
       </c>
-      <c r="AK17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>970</v>
-      </c>
       <c r="AO17" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AP17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR17" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>4.8</v>
       </c>
       <c r="AS17" t="n">
         <v>5.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB17" t="n">
         <v>4.9</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Aalesunds</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.06</v>
+        <v>2.82</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="H18" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="I18" t="n">
-        <v>3.75</v>
+        <v>2.64</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="P18" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>1.76</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cottbus</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1860 Munich</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="G19" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="H19" t="n">
-        <v>3.65</v>
+        <v>2.98</v>
       </c>
       <c r="I19" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="U19" t="n">
         <v>2.34</v>
       </c>
       <c r="V19" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W19" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="X19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y19" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AO19" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AP19" t="n">
-        <v>16.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14.5</v>
+        <v>4.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.4</v>
+        <v>3.75</v>
       </c>
       <c r="AV19" t="n">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX19" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.4</v>
+        <v>3.95</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12</v>
+        <v>4.3</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>17.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC19" t="n">
-        <v>14.5</v>
+        <v>4.7</v>
       </c>
       <c r="BD19" t="n">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>24</v>
+        <v>4.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>VfL Osnabruck</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.92</v>
+        <v>2.22</v>
       </c>
       <c r="G20" t="n">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="H20" t="n">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="I20" t="n">
-        <v>2.82</v>
+        <v>3.45</v>
       </c>
       <c r="J20" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.46</v>
       </c>
-      <c r="M20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.29</v>
-      </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>2.66</v>
       </c>
       <c r="T20" t="n">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="U20" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="V20" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="W20" t="n">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="X20" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="AA20" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AB20" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG20" t="n">
         <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ20" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AK20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL20" t="n">
         <v>38</v>
       </c>
-      <c r="AL20" t="n">
-        <v>60</v>
-      </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>42</v>
+        <v>17.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP20" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>27</v>
+        <v>11.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -4434,103 +4434,103 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5.9</v>
+        <v>2.12</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="H21" t="n">
-        <v>1.52</v>
+        <v>2.82</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>3.75</v>
       </c>
       <c r="J21" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="O21" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="P21" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="R21" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="S21" t="n">
-        <v>2.32</v>
+        <v>1.76</v>
       </c>
       <c r="T21" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="U21" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>2.66</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>1.17</v>
+        <v>1.66</v>
       </c>
       <c r="X21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
         <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
@@ -4548,65 +4548,65 @@
         <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -4628,127 +4628,127 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Cottbus</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Erzgebirge</t>
+          <t>1860 Munich</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="I22" t="n">
         <v>4.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="K22" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M22" t="n">
         <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P22" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="S22" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="T22" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W22" t="n">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AR22" t="n">
         <v>1.03</v>
@@ -4757,57 +4757,57 @@
         <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW22" t="n">
         <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA22" t="n">
         <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE22" t="n">
         <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FC Nordsjaelland</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>VfL Osnabruck</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.28</v>
+        <v>2.92</v>
       </c>
       <c r="G23" t="n">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="H23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J23" t="n">
         <v>3.15</v>
       </c>
-      <c r="I23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.7</v>
-      </c>
       <c r="K23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S23" t="n">
         <v>3.9</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T23" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="U23" t="n">
-        <v>2.46</v>
+        <v>2.04</v>
       </c>
       <c r="V23" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W23" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="X23" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="Y23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z23" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB23" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC23" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF23" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG23" t="n">
         <v>13.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="BG23" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.22</v>
+        <v>5.9</v>
       </c>
       <c r="G24" t="n">
-        <v>2.44</v>
+        <v>7</v>
       </c>
       <c r="H24" t="n">
-        <v>3.05</v>
+        <v>1.52</v>
       </c>
       <c r="I24" t="n">
-        <v>3.45</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="O24" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="S24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V24" t="n">
         <v>2.66</v>
       </c>
-      <c r="T24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.41</v>
-      </c>
       <c r="W24" t="n">
-        <v>1.69</v>
+        <v>1.17</v>
       </c>
       <c r="X24" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="Y24" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA24" t="n">
         <v>17.5</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
         <v>28</v>
       </c>
-      <c r="AA24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="AH24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS24" t="n">
+      <c r="BA24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG24" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>20</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,72 +5205,72 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14:00:59</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Vizela</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>Erzgebirge</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G25" t="n">
-        <v>120</v>
+        <v>2.5</v>
       </c>
       <c r="H25" t="n">
-        <v>1.09</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>120</v>
+        <v>4.2</v>
       </c>
       <c r="J25" t="n">
-        <v>1.09</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>120</v>
+        <v>6.4</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="O25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.01</v>
       </c>
-      <c r="P25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.84</v>
-      </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5327,52 +5327,52 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FC Wil</t>
+          <t>FC Nordsjaelland</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neuchatel Xamax</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="G26" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="H26" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="I26" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="J26" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="K26" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L26" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P26" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="T26" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U26" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="V26" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W26" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="X26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD26" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AE26" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG26" t="n">
         <v>13.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL26" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="AR26" t="n">
-        <v>17</v>
+        <v>4.7</v>
       </c>
       <c r="AS26" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX26" t="n">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB26" t="n">
         <v>4.8</v>
       </c>
       <c r="BC26" t="n">
-        <v>19</v>
+        <v>4.6</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BG26" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,75 +5593,75 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:59</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>Vizela</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Benfica B</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.32</v>
+        <v>1.96</v>
       </c>
       <c r="G27" t="n">
-        <v>1.4</v>
+        <v>120</v>
       </c>
       <c r="H27" t="n">
-        <v>8.6</v>
+        <v>1.09</v>
       </c>
       <c r="I27" t="n">
-        <v>12.5</v>
+        <v>120</v>
       </c>
       <c r="J27" t="n">
-        <v>5</v>
+        <v>1.09</v>
       </c>
       <c r="K27" t="n">
-        <v>6.4</v>
+        <v>120</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>5.3</v>
+        <v>1.02</v>
       </c>
       <c r="O27" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="P27" t="n">
-        <v>2.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="R27" t="n">
-        <v>1.59</v>
+        <v>1.02</v>
       </c>
       <c r="S27" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="T27" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="U27" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="V27" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
         <v>1000</v>
@@ -5673,10 +5673,10 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
         <v>1000</v>
@@ -5685,22 +5685,22 @@
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
         <v>1000</v>
@@ -5709,75 +5709,75 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="G28" t="n">
-        <v>6.4</v>
+        <v>1.37</v>
       </c>
       <c r="H28" t="n">
-        <v>1.67</v>
+        <v>10</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>12.5</v>
       </c>
       <c r="J28" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="K28" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="L28" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N28" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="P28" t="n">
-        <v>1.97</v>
+        <v>2.52</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="S28" t="n">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="T28" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="V28" t="n">
-        <v>2.24</v>
+        <v>1.09</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>3.7</v>
       </c>
       <c r="X28" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB28" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Z28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC28" t="n">
+      <c r="BC28" t="n">
         <v>11</v>
       </c>
-      <c r="AD28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD28" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>FC Wil</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Neuchatel Xamax</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G29" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="H29" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="I29" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="J29" t="n">
         <v>3.2</v>
       </c>
       <c r="K29" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="P29" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.28</v>
+        <v>1.75</v>
       </c>
       <c r="R29" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="S29" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="T29" t="n">
-        <v>1.96</v>
+        <v>1.64</v>
       </c>
       <c r="U29" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="V29" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W29" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="X29" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Y29" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA29" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AC29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH29" t="n">
         <v>18.5</v>
       </c>
-      <c r="AE29" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>25</v>
-      </c>
       <c r="AI29" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="AJ29" t="n">
         <v>40</v>
       </c>
       <c r="AK29" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AL29" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO29" t="n">
         <v>30</v>
       </c>
-      <c r="AO29" t="n">
-        <v>60</v>
-      </c>
       <c r="AP29" t="n">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AR29" t="n">
         <v>17</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT29" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW29" t="n">
         <v>4.7</v>
       </c>
       <c r="AX29" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AY29" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA29" t="n">
         <v>4.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.5</v>
+        <v>19</v>
       </c>
       <c r="BD29" t="n">
-        <v>30</v>
+        <v>4.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.7</v>
+        <v>19.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,108 +6175,108 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cove Rangers</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.09</v>
+        <v>5.2</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="H30" t="n">
-        <v>1.09</v>
+        <v>1.67</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="O30" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="P30" t="n">
-        <v>1.08</v>
+        <v>1.97</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="R30" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>1.24</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ30" t="n">
         <v>1000</v>
@@ -6294,72 +6294,72 @@
         <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="G31" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="H31" t="n">
-        <v>2.24</v>
+        <v>3.25</v>
       </c>
       <c r="I31" t="n">
-        <v>2.26</v>
+        <v>3.75</v>
       </c>
       <c r="J31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S31" t="n">
         <v>4.3</v>
       </c>
-      <c r="K31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P31" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.18</v>
-      </c>
       <c r="T31" t="n">
-        <v>1.48</v>
+        <v>1.98</v>
       </c>
       <c r="U31" t="n">
-        <v>2.96</v>
+        <v>1.84</v>
       </c>
       <c r="V31" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="X31" t="n">
-        <v>32</v>
+        <v>12.5</v>
       </c>
       <c r="Y31" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD31" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z31" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>29</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX31" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>46</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>26</v>
-      </c>
       <c r="AY31" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA31" t="n">
-        <v>23</v>
+        <v>5.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>44</v>
+        <v>5.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>25</v>
+        <v>5.1</v>
       </c>
       <c r="BD31" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE31" t="n">
-        <v>40</v>
+        <v>5.7</v>
       </c>
       <c r="BF31" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="BG31" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,191 +6563,191 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Cove Rangers</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="G32" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="H32" t="n">
-        <v>1.79</v>
+        <v>2.92</v>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K32" t="n">
         <v>4</v>
       </c>
-      <c r="K32" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L32" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="M32" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="O32" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="P32" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="R32" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>3.55</v>
+        <v>2.72</v>
       </c>
       <c r="T32" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="U32" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="V32" t="n">
-        <v>2.24</v>
+        <v>1.41</v>
       </c>
       <c r="W32" t="n">
-        <v>1.23</v>
+        <v>1.66</v>
       </c>
       <c r="X32" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Y32" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="Z32" t="n">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="AA32" t="n">
-        <v>18.5</v>
+        <v>60</v>
       </c>
       <c r="AB32" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD32" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AE32" t="n">
-        <v>18.5</v>
+        <v>38</v>
       </c>
       <c r="AF32" t="n">
-        <v>38</v>
+        <v>16.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AH32" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI32" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL32" t="n">
         <v>36</v>
       </c>
-      <c r="AJ32" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>75</v>
-      </c>
       <c r="AM32" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AN32" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="AO32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF32" t="n">
         <v>12</v>
       </c>
-      <c r="AP32" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>36</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>42</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>55</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>65</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>70</v>
-      </c>
       <c r="BG32" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="G33" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="H33" t="n">
-        <v>3.1</v>
+        <v>2.24</v>
       </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>2.26</v>
       </c>
       <c r="J33" t="n">
-        <v>2.94</v>
+        <v>4.3</v>
       </c>
       <c r="K33" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>2.74</v>
+        <v>7.2</v>
       </c>
       <c r="O33" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="P33" t="n">
-        <v>1.58</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.52</v>
+        <v>1.48</v>
       </c>
       <c r="R33" t="n">
-        <v>1.2</v>
+        <v>1.81</v>
       </c>
       <c r="S33" t="n">
-        <v>4.9</v>
+        <v>2.18</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="U33" t="n">
-        <v>1.82</v>
+        <v>2.96</v>
       </c>
       <c r="V33" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="W33" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="X33" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="Y33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD33" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AE33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI33" t="n">
         <v>25</v>
       </c>
-      <c r="AA33" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="AJ33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU33" t="n">
         <v>10</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>6</v>
       </c>
       <c r="AV33" t="n">
         <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.1</v>
+        <v>18</v>
       </c>
       <c r="AX33" t="n">
-        <v>11.5</v>
+        <v>25</v>
       </c>
       <c r="AY33" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="AZ33" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.2</v>
+        <v>23</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.1</v>
+        <v>44</v>
       </c>
       <c r="BC33" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.2</v>
+        <v>27</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.3</v>
+        <v>40</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,378 +6951,766 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="G34" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="H34" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="I34" t="n">
-        <v>2.44</v>
+        <v>1.81</v>
       </c>
       <c r="J34" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="K34" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M34" t="n">
         <v>1.07</v>
       </c>
       <c r="N34" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="O34" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P34" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T34" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q34" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.75</v>
-      </c>
       <c r="U34" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="V34" t="n">
-        <v>1.69</v>
+        <v>2.24</v>
       </c>
       <c r="W34" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="X34" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Y34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO34" t="n">
         <v>12</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AP34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS34" t="n">
         <v>17.5</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AT34" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX34" t="n">
         <v>36</v>
       </c>
-      <c r="AB34" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL34" t="n">
+      <c r="AY34" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>110</v>
+      </c>
+      <c r="BC34" t="n">
         <v>60</v>
       </c>
-      <c r="AM34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP34" t="n">
+      <c r="BD34" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>70</v>
+      </c>
+      <c r="BG34" t="n">
         <v>11</v>
       </c>
-      <c r="AQ34" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Aguilas Doradas</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X35" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-04-06 09:33:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Queretaro</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X36" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-04-06 09:33:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Real Santander</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="F37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G37" t="n">
         <v>2.34</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H37" t="n">
         <v>3.15</v>
       </c>
-      <c r="I35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M35" t="n">
+      <c r="I37" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M37" t="n">
         <v>1.01</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N37" t="n">
         <v>2.48</v>
       </c>
-      <c r="O35" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P35" t="n">
+      <c r="O37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P37" t="n">
         <v>1.55</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q37" t="n">
         <v>2.14</v>
       </c>
-      <c r="R35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S35" t="n">
+      <c r="R37" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S37" t="n">
         <v>3.2</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T37" t="n">
         <v>1.01</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U37" t="n">
         <v>1.01</v>
       </c>
-      <c r="V35" t="n">
+      <c r="V37" t="n">
         <v>1.2</v>
       </c>
-      <c r="W35" t="n">
+      <c r="W37" t="n">
         <v>1.74</v>
       </c>
-      <c r="X35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF35" t="n">
+      <c r="X37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF37" t="n">
         <v>1.01</v>
       </c>
-      <c r="BG35" t="n">
+      <c r="BG37" t="n">
         <v>1.01</v>
       </c>
-      <c r="BH35" t="inlineStr">
-        <is>
-          <t>2026-04-06 07:11:44</t>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH37"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,28 +781,28 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="R2" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
         <v>1.12</v>
@@ -811,61 +811,61 @@
         <v>3.2</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z2" t="n">
         <v>80</v>
       </c>
       <c r="AA2" t="n">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC2" t="n">
         <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE2" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG2" t="n">
         <v>10</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK2" t="n">
         <v>14.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AP2" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>26</v>
@@ -874,10 +874,10 @@
         <v>15</v>
       </c>
       <c r="AS2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
         <v>16.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY2" t="n">
         <v>9.199999999999999</v>
@@ -913,14 +913,14 @@
         <v>16.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>1.65</v>
       </c>
       <c r="I3" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="J3" t="n">
         <v>3.15</v>
@@ -975,13 +975,13 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O3" t="n">
         <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q3" t="n">
         <v>2.18</v>
@@ -990,7 +990,7 @@
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T3" t="n">
         <v>2.16</v>
@@ -999,7 +999,7 @@
         <v>1.69</v>
       </c>
       <c r="V3" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="W3" t="n">
         <v>1.13</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>2.46</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>2.46</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="BG3" t="n">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
@@ -1166,16 +1166,16 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Q4" t="n">
         <v>1.5</v>
@@ -1187,10 +1187,10 @@
         <v>1.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G5" t="n">
         <v>2.32</v>
@@ -1372,7 +1372,7 @@
         <v>1.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R5" t="n">
         <v>1.3</v>
@@ -1402,7 +1402,7 @@
         <v>34</v>
       </c>
       <c r="AA5" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB5" t="n">
         <v>11</v>
@@ -1414,7 +1414,7 @@
         <v>19.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF5" t="n">
         <v>16.5</v>
@@ -1426,10 +1426,10 @@
         <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1450,13 +1450,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT5" t="n">
         <v>6.6</v>
@@ -1468,19 +1468,19 @@
         <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB5" t="n">
         <v>20</v>
@@ -1489,20 +1489,20 @@
         <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
         <v>14</v>
       </c>
       <c r="BG5" t="n">
-        <v>40</v>
+        <v>4.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G6" t="n">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T6" t="n">
         <v>2.18</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V6" t="n">
         <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>3.85</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H7" t="n">
         <v>1.89</v>
@@ -1739,13 +1739,13 @@
         <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
         <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
@@ -1757,7 +1757,7 @@
         <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
         <v>1.72</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
         <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="R8" t="n">
         <v>1.16</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="I9" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>1.09</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="R9" t="n">
         <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="T9" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="U9" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="V9" t="n">
-        <v>2.52</v>
+        <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2271,21 +2271,21 @@
         <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:40:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Miedz Legnica</t>
+          <t>Al Jubail</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Al-Jndal</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="G10" t="n">
-        <v>2.26</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="I10" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>3.45</v>
       </c>
       <c r="T10" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="X10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
         <v>22</v>
       </c>
-      <c r="Y10" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG10" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,67 +2494,67 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Trans Narva</t>
+          <t>Al-Arabi Al-Saudi</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>Al-Zulfi SC</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>1.85</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>1.99</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>1.32</v>
+        <v>2.26</v>
       </c>
       <c r="H12" t="n">
-        <v>1.09</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X12" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC12" t="n">
         <v>16</v>
       </c>
-      <c r="J12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>950</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.86</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KFUM Oslo</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.26</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="O13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P13" t="n">
         <v>1.28</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.08</v>
-      </c>
       <c r="Q13" t="n">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>3.05</v>
+        <v>1.15</v>
       </c>
       <c r="T13" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,72 +3071,72 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bodrum Belediyesi Bodrumspor</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="G14" t="n">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="H14" t="n">
-        <v>3.85</v>
+        <v>1.09</v>
       </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>1.09</v>
       </c>
       <c r="K14" t="n">
-        <v>8.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M14" t="n">
         <v>1.01</v>
       </c>
-      <c r="M14" t="n">
-        <v>1.03</v>
-      </c>
       <c r="N14" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="O14" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>1.98</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V14" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="W14" t="n">
-        <v>2.08</v>
+        <v>4</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3187,7 +3187,7 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
@@ -3241,21 +3241,21 @@
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BG14" t="n">
         <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>KFUM Oslo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Etoile Carouge</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7</v>
+        <v>2.26</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4</v>
+        <v>3.45</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
         <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>2.42</v>
+        <v>1.79</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC15" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>13</v>
       </c>
-      <c r="AG15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AR15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW15" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AX15" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
         <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE15" t="n">
         <v>4.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,73 +3464,73 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sandvikens</t>
+          <t>Bodrum Belediyesi Bodrumspor</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="G16" t="n">
-        <v>2.58</v>
+        <v>1.91</v>
       </c>
       <c r="H16" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="J16" t="n">
         <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>1.94</v>
       </c>
       <c r="O16" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="W16" t="n">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="X16" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3539,25 +3539,25 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
@@ -3566,7 +3566,7 @@
         <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
         <v>1000</v>
@@ -3575,75 +3575,75 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Etoile Carouge</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.36</v>
+        <v>1.55</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56</v>
+        <v>1.7</v>
       </c>
       <c r="H17" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="I17" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.73</v>
+        <v>2.32</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.18</v>
+        <v>1.56</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="U17" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="W17" t="n">
-        <v>1.64</v>
+        <v>2.42</v>
       </c>
       <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
         <v>13</v>
       </c>
-      <c r="Y17" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AG17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX17" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AY17" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="AZ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD17" t="n">
         <v>4.5</v>
       </c>
-      <c r="BA17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB17" t="n">
+      <c r="BE17" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BF17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG17" t="n">
         <v>4.8</v>
       </c>
-      <c r="BD17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aalesunds</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Sandvikens</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.82</v>
+        <v>2.1</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="H18" t="n">
-        <v>2.44</v>
+        <v>2.96</v>
       </c>
       <c r="I18" t="n">
-        <v>2.64</v>
+        <v>4.1</v>
       </c>
       <c r="J18" t="n">
         <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA18" t="n">
         <v>4</v>
       </c>
-      <c r="O18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X18" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BB18" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF18" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>16</v>
+        <v>3.95</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="G19" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="H19" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="I19" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.24</v>
+        <v>1.73</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.6</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="V19" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="X19" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN19" t="n">
         <v>32</v>
       </c>
-      <c r="AK19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>970</v>
-      </c>
       <c r="AO19" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AP19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR19" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>4.8</v>
       </c>
       <c r="AS19" t="n">
         <v>5.2</v>
       </c>
       <c r="AT19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV19" t="n">
         <v>4.2</v>
       </c>
-      <c r="AU19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AW19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB19" t="n">
         <v>4.9</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,28 +4240,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Aalesunds</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H20" t="n">
         <v>2.44</v>
       </c>
-      <c r="H20" t="n">
-        <v>3.05</v>
-      </c>
       <c r="I20" t="n">
-        <v>3.45</v>
+        <v>2.64</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K20" t="n">
         <v>4.1</v>
@@ -4270,156 +4270,156 @@
         <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="U20" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="V20" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="W20" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="X20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="Z20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE20" t="n">
         <v>28</v>
       </c>
-      <c r="AA20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>40</v>
-      </c>
       <c r="AF20" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AG20" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AH20" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI20" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AJ20" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AK20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="n">
         <v>27</v>
       </c>
-      <c r="AL20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AO20" t="n">
-        <v>32</v>
+        <v>19.5</v>
       </c>
       <c r="AP20" t="n">
         <v>14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BC20" t="n">
-        <v>17.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BG20" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="H21" t="n">
-        <v>2.82</v>
+        <v>3.45</v>
       </c>
       <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="n">
         <v>3.75</v>
       </c>
-      <c r="J21" t="n">
-        <v>3.55</v>
-      </c>
       <c r="K21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X21" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR21" t="n">
         <v>5.8</v>
       </c>
-      <c r="L21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
@@ -4628,127 +4628,127 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cottbus</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1860 Munich</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="G22" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="H22" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="I22" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K22" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>4.8</v>
+        <v>2.86</v>
       </c>
       <c r="O22" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.86</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="R22" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="S22" t="n">
-        <v>2.54</v>
+        <v>1.76</v>
       </c>
       <c r="T22" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="U22" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="X22" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
         <v>1.03</v>
@@ -4757,50 +4757,50 @@
         <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
         <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
         <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
         <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
@@ -4822,179 +4822,179 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Cottbus</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VfL Osnabruck</t>
+          <t>1860 Munich</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.92</v>
+        <v>1.9</v>
       </c>
       <c r="G23" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="H23" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="I23" t="n">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="K23" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="M23" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="P23" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.16</v>
+        <v>1.62</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>3.9</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="U23" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="V23" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="W23" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="X23" t="n">
-        <v>13.5</v>
+        <v>26</v>
       </c>
       <c r="Y23" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC23" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AD23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH23" t="n">
         <v>18.5</v>
       </c>
-      <c r="AA23" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>12</v>
       </c>
-      <c r="AC23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF23" t="n">
+      <c r="BA23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD23" t="n">
         <v>21</v>
       </c>
-      <c r="AG23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ23" t="n">
+      <c r="BE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF23" t="n">
         <v>7.8</v>
       </c>
-      <c r="AR23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>27</v>
-      </c>
       <c r="BG23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
@@ -5016,179 +5016,179 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>VfL Osnabruck</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU24" t="n">
         <v>5.9</v>
       </c>
-      <c r="G24" t="n">
-        <v>7</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V24" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X24" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="AV24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>14</v>
       </c>
-      <c r="Z24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA24" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.8</v>
+        <v>27</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.6</v>
+        <v>25</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
@@ -5210,103 +5210,103 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Erzgebirge</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.97</v>
+        <v>5.9</v>
       </c>
       <c r="G25" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>1.52</v>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>1.59</v>
       </c>
       <c r="J25" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="K25" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M25" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>2.04</v>
+        <v>5.7</v>
       </c>
       <c r="O25" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="P25" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="S25" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T25" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V25" t="n">
-        <v>1.32</v>
+        <v>2.68</v>
       </c>
       <c r="W25" t="n">
-        <v>1.66</v>
+        <v>1.17</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF25" t="n">
         <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ25" t="n">
         <v>1000</v>
@@ -5324,72 +5324,72 @@
         <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,31 +5404,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FC Nordsjaelland</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Erzgebirge</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G26" t="n">
         <v>2.26</v>
       </c>
-      <c r="G26" t="n">
-        <v>2.4</v>
-      </c>
       <c r="H26" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I26" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K26" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5443,147 +5443,147 @@
         <v>1.23</v>
       </c>
       <c r="P26" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="R26" t="n">
         <v>1.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="T26" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U26" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W26" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="X26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y26" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF26" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG26" t="n">
         <v>13.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK26" t="n">
         <v>26</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.7</v>
+        <v>19.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT26" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX26" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.8</v>
+        <v>19.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>4.6</v>
+        <v>15</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF26" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,36 +5593,36 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>14:00:59</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Vizela</t>
+          <t>FC Nordsjaelland</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="G27" t="n">
-        <v>120</v>
+        <v>2.4</v>
       </c>
       <c r="H27" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="I27" t="n">
-        <v>120</v>
+        <v>3.35</v>
       </c>
       <c r="J27" t="n">
-        <v>1.09</v>
+        <v>3.7</v>
       </c>
       <c r="K27" t="n">
-        <v>120</v>
+        <v>3.95</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -5631,40 +5631,40 @@
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>1.02</v>
+        <v>4.7</v>
       </c>
       <c r="O27" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P27" t="n">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="T27" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="U27" t="n">
-        <v>1.84</v>
+        <v>2.46</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z27" t="n">
         <v>1000</v>
@@ -5673,25 +5673,25 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
@@ -5700,7 +5700,7 @@
         <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL27" t="n">
         <v>1000</v>
@@ -5709,75 +5709,75 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L28" t="n">
         <v>1.3</v>
       </c>
-      <c r="G28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H28" t="n">
-        <v>10</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="M28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X28" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX28" t="n">
         <v>12.5</v>
       </c>
-      <c r="J28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X28" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="AY28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>12</v>
       </c>
-      <c r="AC28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
+      <c r="BA28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG28" t="n">
         <v>20</v>
       </c>
-      <c r="AQ28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:59</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FC Wil</t>
+          <t>Vizela</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Neuchatel Xamax</t>
+          <t>Benfica B</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.32</v>
+        <v>1.96</v>
       </c>
       <c r="G29" t="n">
-        <v>2.62</v>
+        <v>120</v>
       </c>
       <c r="H29" t="n">
-        <v>2.86</v>
+        <v>1.09</v>
       </c>
       <c r="I29" t="n">
-        <v>3.5</v>
+        <v>120</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2</v>
+        <v>1.09</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>120</v>
       </c>
       <c r="L29" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>1.02</v>
       </c>
       <c r="O29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P29" t="n">
         <v>1.25</v>
       </c>
-      <c r="P29" t="n">
-        <v>2.06</v>
-      </c>
       <c r="Q29" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="R29" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="S29" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="T29" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="U29" t="n">
-        <v>2.26</v>
+        <v>1.84</v>
       </c>
       <c r="V29" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,111 +6175,111 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="G30" t="n">
-        <v>6.2</v>
+        <v>1.37</v>
       </c>
       <c r="H30" t="n">
-        <v>1.67</v>
+        <v>10</v>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>12.5</v>
       </c>
       <c r="J30" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="K30" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="L30" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="O30" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="P30" t="n">
-        <v>1.97</v>
+        <v>2.52</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="S30" t="n">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="T30" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="U30" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="V30" t="n">
-        <v>2.24</v>
+        <v>1.09</v>
       </c>
       <c r="W30" t="n">
-        <v>1.19</v>
+        <v>3.7</v>
       </c>
       <c r="X30" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AC30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG30" t="n">
         <v>11</v>
       </c>
-      <c r="AD30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>26</v>
-      </c>
       <c r="AH30" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AI30" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AK30" t="n">
         <v>1000</v>
@@ -6291,75 +6291,75 @@
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="AO30" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="AQ30" t="n">
         <v>7.2</v>
       </c>
       <c r="AR30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT30" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AS30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AU30" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AV30" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AW30" t="n">
-        <v>15.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="AY30" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AZ30" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.8</v>
+        <v>25</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF30" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BG30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>FC Wil</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Neuchatel Xamax</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G31" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="H31" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="I31" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="J31" t="n">
         <v>3.2</v>
       </c>
       <c r="K31" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="L31" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="P31" t="n">
-        <v>1.63</v>
+        <v>2.06</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.28</v>
+        <v>1.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="S31" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="T31" t="n">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="U31" t="n">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W31" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="X31" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="Y31" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA31" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AB31" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AC31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH31" t="n">
         <v>18.5</v>
       </c>
-      <c r="AE31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>25</v>
-      </c>
       <c r="AI31" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="AJ31" t="n">
         <v>40</v>
       </c>
       <c r="AK31" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AL31" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO31" t="n">
         <v>30</v>
       </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP31" t="n">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AR31" t="n">
         <v>17</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="AU31" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX31" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AY31" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BC31" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE31" t="n">
         <v>5.1</v>
       </c>
-      <c r="BD31" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BF31" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,191 +6563,191 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cove Rangers</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="G32" t="n">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="H32" t="n">
-        <v>2.92</v>
+        <v>1.67</v>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K32" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L32" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M32" t="n">
         <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="O32" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="T32" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="U32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V32" t="n">
         <v>2.24</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.41</v>
-      </c>
       <c r="W32" t="n">
-        <v>1.66</v>
+        <v>1.19</v>
       </c>
       <c r="X32" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y32" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG32" t="n">
         <v>26</v>
       </c>
-      <c r="AA32" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC32" t="n">
+      <c r="AH32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR32" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD32" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH32" t="n">
+      <c r="AS32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ32" t="n">
         <v>17.5</v>
       </c>
-      <c r="AI32" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BA32" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF32" t="n">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="BG32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="G33" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="H33" t="n">
-        <v>2.24</v>
+        <v>3.25</v>
       </c>
       <c r="I33" t="n">
-        <v>2.26</v>
+        <v>3.7</v>
       </c>
       <c r="J33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S33" t="n">
         <v>4.3</v>
       </c>
-      <c r="K33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P33" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.18</v>
-      </c>
       <c r="T33" t="n">
-        <v>1.48</v>
+        <v>1.98</v>
       </c>
       <c r="U33" t="n">
-        <v>2.96</v>
+        <v>1.84</v>
       </c>
       <c r="V33" t="n">
-        <v>1.79</v>
+        <v>1.37</v>
       </c>
       <c r="W33" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="X33" t="n">
-        <v>32</v>
+        <v>12.5</v>
       </c>
       <c r="Y33" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD33" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z33" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>29</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC33" t="n">
+      <c r="AE33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX33" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>46</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>25</v>
-      </c>
       <c r="AY33" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ33" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA33" t="n">
-        <v>23</v>
+        <v>5.5</v>
       </c>
       <c r="BB33" t="n">
-        <v>44</v>
+        <v>5.2</v>
       </c>
       <c r="BC33" t="n">
-        <v>25</v>
+        <v>5.1</v>
       </c>
       <c r="BD33" t="n">
-        <v>27</v>
+        <v>5.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>40</v>
+        <v>5.7</v>
       </c>
       <c r="BF33" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="BG33" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,191 +6951,191 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Cove Rangers</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>5.1</v>
+        <v>2.34</v>
       </c>
       <c r="G34" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="H34" t="n">
-        <v>1.8</v>
+        <v>2.98</v>
       </c>
       <c r="I34" t="n">
-        <v>1.81</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K34" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L34" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="M34" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N34" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="O34" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="P34" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="R34" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>3.55</v>
+        <v>2.72</v>
       </c>
       <c r="T34" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="U34" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="V34" t="n">
-        <v>2.24</v>
+        <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="X34" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="Z34" t="n">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="AA34" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="AB34" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AE34" t="n">
-        <v>18.5</v>
+        <v>38</v>
       </c>
       <c r="AF34" t="n">
-        <v>38</v>
+        <v>16.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AH34" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI34" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL34" t="n">
         <v>36</v>
       </c>
-      <c r="AJ34" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>75</v>
-      </c>
       <c r="AM34" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AN34" t="n">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="AO34" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF34" t="n">
         <v>12</v>
       </c>
-      <c r="AP34" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>36</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>110</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>60</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>65</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>70</v>
-      </c>
       <c r="BG34" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,191 +7145,191 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="G35" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="H35" t="n">
-        <v>3.1</v>
+        <v>2.24</v>
       </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>2.26</v>
       </c>
       <c r="J35" t="n">
-        <v>2.94</v>
+        <v>4.3</v>
       </c>
       <c r="K35" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M35" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="N35" t="n">
-        <v>2.74</v>
+        <v>7.2</v>
       </c>
       <c r="O35" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="P35" t="n">
-        <v>1.58</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.52</v>
+        <v>1.48</v>
       </c>
       <c r="R35" t="n">
-        <v>1.2</v>
+        <v>1.81</v>
       </c>
       <c r="S35" t="n">
-        <v>4.9</v>
+        <v>2.18</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="U35" t="n">
-        <v>1.82</v>
+        <v>2.98</v>
       </c>
       <c r="V35" t="n">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="W35" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="X35" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV35" t="n">
         <v>11</v>
       </c>
-      <c r="Y35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z35" t="n">
+      <c r="AW35" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX35" t="n">
         <v>25</v>
       </c>
-      <c r="AA35" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC35" t="n">
+      <c r="AY35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG35" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD35" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,378 +7339,766 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="G36" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="H36" t="n">
-        <v>2.34</v>
+        <v>1.77</v>
       </c>
       <c r="I36" t="n">
-        <v>2.52</v>
+        <v>1.78</v>
       </c>
       <c r="J36" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="L36" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M36" t="n">
         <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="O36" t="n">
         <v>1.33</v>
       </c>
       <c r="P36" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T36" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q36" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.76</v>
-      </c>
       <c r="U36" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="V36" t="n">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="W36" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="X36" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO36" t="n">
         <v>12</v>
       </c>
-      <c r="Z36" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD36" t="n">
+      <c r="AP36" t="n">
         <v>13</v>
       </c>
-      <c r="AE36" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG36" t="n">
+      <c r="AQ36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT36" t="n">
         <v>16</v>
       </c>
-      <c r="AH36" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP36" t="n">
+      <c r="AU36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>95</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>60</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>70</v>
+      </c>
+      <c r="BG36" t="n">
         <v>11</v>
       </c>
-      <c r="AQ36" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Aguilas Doradas</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X37" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-04-06 11:50:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Queretaro</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-04-06 11:50:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Real Santander</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="H37" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I37" t="n">
-        <v>6</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K37" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L37" t="n">
+      <c r="F39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L39" t="n">
         <v>1.44</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG39" t="n">
         <v>1.01</v>
       </c>
-      <c r="N37" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH37" t="inlineStr">
-        <is>
-          <t>2026-04-06 09:33:34</t>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -775,34 +775,34 @@
         <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
         <v>4.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R2" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T2" t="n">
         <v>1.99</v>
       </c>
       <c r="U2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V2" t="n">
         <v>1.12</v>
@@ -823,7 +823,7 @@
         <v>320</v>
       </c>
       <c r="AB2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2" t="n">
         <v>11.5</v>
@@ -838,7 +838,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
         <v>26</v>
@@ -856,7 +856,7 @@
         <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
         <v>6.4</v>
@@ -871,13 +871,13 @@
         <v>26</v>
       </c>
       <c r="AR2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS2" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
@@ -886,41 +886,41 @@
         <v>27</v>
       </c>
       <c r="AW2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX2" t="n">
         <v>8</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BF2" t="n">
         <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -963,13 +963,13 @@
         <v>1.82</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
         <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
@@ -996,13 +996,13 @@
         <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V3" t="n">
         <v>2.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AR3" t="n">
         <v>4.1</v>
       </c>
       <c r="AS3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT3" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT3" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AU3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="AY3" t="n">
         <v>5.9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.75</v>
+        <v>6.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.46</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.44</v>
+        <v>7</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.44</v>
+        <v>7</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.46</v>
+        <v>7.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.46</v>
+        <v>7.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -1172,19 +1172,19 @@
         <v>1.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
         <v>1.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
         <v>3.75</v>
@@ -1369,10 +1369,10 @@
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R5" t="n">
         <v>1.3</v>
@@ -1387,10 +1387,10 @@
         <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="X5" t="n">
         <v>15.5</v>
@@ -1429,7 +1429,7 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1441,7 +1441,7 @@
         <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO5" t="n">
         <v>70</v>
@@ -1456,7 +1456,7 @@
         <v>19.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
         <v>6.6</v>
@@ -1489,20 +1489,20 @@
         <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF5" t="n">
         <v>14</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G6" t="n">
         <v>1.72</v>
@@ -1542,22 +1542,22 @@
         <v>5.7</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
         <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="O6" t="n">
         <v>1.42</v>
@@ -1569,19 +1569,19 @@
         <v>2.04</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T6" t="n">
         <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W6" t="n">
         <v>2.38</v>
@@ -1590,7 +1590,7 @@
         <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z6" t="n">
         <v>75</v>
@@ -1599,22 +1599,22 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
         <v>34</v>
@@ -1623,80 +1623,80 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV6" t="n">
         <v>20</v>
       </c>
-      <c r="AK6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4</v>
-      </c>
       <c r="AW6" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.65</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.85</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.55</v>
+        <v>10</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="J7" t="n">
         <v>3.6</v>
@@ -1745,28 +1745,28 @@
         <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="G8" t="n">
         <v>2.7</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="n">
         <v>3.8</v>
@@ -1936,7 +1936,7 @@
         <v>2.84</v>
       </c>
       <c r="K8" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="L8" t="n">
         <v>1.56</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J9" t="n">
         <v>4</v>
       </c>
-      <c r="G9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.2</v>
-      </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>5.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="R9" t="n">
         <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>2.58</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2271,14 +2271,14 @@
         <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -2309,40 +2309,40 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H10" t="n">
         <v>2.8</v>
       </c>
       <c r="I10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
         <v>2.92</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.39</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>2.54</v>
+        <v>2.76</v>
       </c>
       <c r="O10" t="n">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="P10" t="n">
         <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>1.26</v>
@@ -2351,16 +2351,16 @@
         <v>3.45</v>
       </c>
       <c r="T10" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
         <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
         <v>14</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G11" t="n">
         <v>6.6</v>
@@ -2518,13 +2518,13 @@
         <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
         <v>1.85</v>
@@ -2542,13 +2542,13 @@
         <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="T11" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="V11" t="n">
         <v>2.16</v>
@@ -2557,13 +2557,13 @@
         <v>1.17</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2572,10 +2572,10 @@
         <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
@@ -2608,7 +2608,7 @@
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AP11" t="n">
         <v>1.03</v>
@@ -2662,11 +2662,11 @@
         <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H12" t="n">
         <v>3.35</v>
@@ -2709,16 +2709,16 @@
         <v>3.95</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.3</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
         <v>4.3</v>
@@ -2730,19 +2730,19 @@
         <v>2.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V12" t="n">
         <v>1.33</v>
@@ -2751,7 +2751,7 @@
         <v>1.8</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y12" t="n">
         <v>19</v>
@@ -2769,16 +2769,16 @@
         <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE12" t="n">
         <v>46</v>
       </c>
       <c r="AF12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
         <v>19</v>
@@ -2814,7 +2814,7 @@
         <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
@@ -2826,10 +2826,10 @@
         <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
         <v>8.4</v>
@@ -2838,29 +2838,29 @@
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB12" t="n">
         <v>19.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF12" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="O13" t="n">
         <v>1.15</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -3094,49 +3094,49 @@
         <v>1.09</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09</v>
+        <v>4.7</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O14" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="R14" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S14" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="T14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V14" t="n">
         <v>1.07</v>
       </c>
       <c r="W14" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3187,7 +3187,7 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
@@ -3241,14 +3241,14 @@
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BG14" t="n">
         <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -3309,13 +3309,13 @@
         <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
         <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
         <v>3.05</v>
@@ -3324,7 +3324,7 @@
         <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V15" t="n">
         <v>1.38</v>
@@ -3336,7 +3336,7 @@
         <v>21</v>
       </c>
       <c r="Y15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z15" t="n">
         <v>32</v>
@@ -3348,7 +3348,7 @@
         <v>13</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15" t="n">
         <v>18</v>
@@ -3420,7 +3420,7 @@
         <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB15" t="n">
         <v>19.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -3473,61 +3473,61 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G16" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="H16" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
         <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>1.94</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V16" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
         <v>1000</v>
@@ -3539,10 +3539,10 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3554,19 +3554,19 @@
         <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
         <v>1000</v>
@@ -3575,13 +3575,13 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.03</v>
@@ -3593,13 +3593,13 @@
         <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AW16" t="n">
         <v>1.03</v>
@@ -3608,16 +3608,16 @@
         <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
         <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BC16" t="n">
         <v>1.03</v>
@@ -3629,14 +3629,14 @@
         <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>1.55</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="H17" t="n">
         <v>5.4</v>
@@ -3706,7 +3706,7 @@
         <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T17" t="n">
         <v>1.71</v>
@@ -3718,7 +3718,7 @@
         <v>1.15</v>
       </c>
       <c r="W17" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -3861,46 +3861,46 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G18" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="H18" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="I18" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J18" t="n">
         <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
         <v>1.69</v>
@@ -3909,10 +3909,10 @@
         <v>2.16</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W18" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="X18" t="n">
         <v>19.5</v>
@@ -3951,7 +3951,7 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK18" t="n">
         <v>28</v>
@@ -3981,7 +3981,7 @@
         <v>4.1</v>
       </c>
       <c r="AT18" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AU18" t="n">
         <v>7.2</v>
@@ -3996,10 +3996,10 @@
         <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA18" t="n">
         <v>4</v>
@@ -4008,7 +4008,7 @@
         <v>20</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.75</v>
+        <v>16.5</v>
       </c>
       <c r="BD18" t="n">
         <v>3.9</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G19" t="n">
         <v>2.56</v>
       </c>
       <c r="H19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I19" t="n">
         <v>3.6</v>
@@ -4073,7 +4073,7 @@
         <v>3.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
@@ -4100,7 +4100,7 @@
         <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
         <v>1.39</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G20" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="H20" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I20" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
         <v>1.3</v>
@@ -4273,40 +4273,40 @@
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
         <v>1.27</v>
       </c>
       <c r="P20" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q20" t="n">
         <v>1.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U20" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="V20" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W20" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="X20" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
         <v>18.5</v>
@@ -4315,22 +4315,22 @@
         <v>40</v>
       </c>
       <c r="AB20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AC20" t="n">
         <v>9</v>
       </c>
       <c r="AD20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
         <v>17</v>
@@ -4339,10 +4339,10 @@
         <v>38</v>
       </c>
       <c r="AJ20" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK20" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AL20" t="n">
         <v>42</v>
@@ -4351,34 +4351,34 @@
         <v>80</v>
       </c>
       <c r="AN20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.8</v>
+        <v>28</v>
       </c>
       <c r="AT20" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.5</v>
+        <v>17</v>
       </c>
       <c r="AX20" t="n">
         <v>17.5</v>
@@ -4387,22 +4387,22 @@
         <v>11</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.8</v>
+        <v>22</v>
       </c>
       <c r="BB20" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.6</v>
+        <v>19</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.9</v>
+        <v>30</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="BF20" t="n">
         <v>20</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -4443,46 +4443,46 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="G21" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="H21" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="J21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M21" t="n">
         <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O21" t="n">
         <v>1.21</v>
       </c>
       <c r="P21" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R21" t="n">
         <v>1.51</v>
       </c>
       <c r="S21" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="T21" t="n">
         <v>1.59</v>
@@ -4491,10 +4491,10 @@
         <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="X21" t="n">
         <v>25</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="I22" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K22" t="n">
         <v>4.6</v>
@@ -4661,10 +4661,10 @@
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>2.86</v>
+        <v>6.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P22" t="n">
         <v>2.86</v>
@@ -4673,109 +4673,109 @@
         <v>1.46</v>
       </c>
       <c r="R22" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="S22" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="T22" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AP22" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS22" t="n">
         <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA22" t="n">
         <v>1.03</v>
@@ -4784,23 +4784,23 @@
         <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BE22" t="n">
         <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G23" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H23" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="I23" t="n">
         <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K23" t="n">
         <v>4.4</v>
@@ -4870,19 +4870,19 @@
         <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U23" t="n">
         <v>2.34</v>
       </c>
       <c r="V23" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="X23" t="n">
         <v>26</v>
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO23" t="n">
         <v>38</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G24" t="n">
         <v>3.2</v>
       </c>
       <c r="H24" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="I24" t="n">
         <v>2.82</v>
@@ -5040,7 +5040,7 @@
         <v>3.15</v>
       </c>
       <c r="K24" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L24" t="n">
         <v>1.47</v>
@@ -5094,7 +5094,7 @@
         <v>12</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD24" t="n">
         <v>13</v>
@@ -5112,7 +5112,7 @@
         <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ24" t="n">
         <v>60</v>
@@ -5136,10 +5136,10 @@
         <v>9</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS24" t="n">
         <v>1.03</v>
@@ -5151,7 +5151,7 @@
         <v>5.9</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW24" t="n">
         <v>1.03</v>
@@ -5163,7 +5163,7 @@
         <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA24" t="n">
         <v>1.03</v>
@@ -5184,11 +5184,11 @@
         <v>27</v>
       </c>
       <c r="BG24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>7</v>
@@ -5267,7 +5267,7 @@
         <v>2.26</v>
       </c>
       <c r="V25" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="W25" t="n">
         <v>1.17</v>
@@ -5294,7 +5294,7 @@
         <v>12</v>
       </c>
       <c r="AE25" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF25" t="n">
         <v>1000</v>
@@ -5327,7 +5327,7 @@
         <v>6.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>9.199999999999999</v>
@@ -5351,7 +5351,7 @@
         <v>11.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY25" t="n">
         <v>18.5</v>
@@ -5363,16 +5363,16 @@
         <v>20</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF25" t="n">
         <v>4.9</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -5419,10 +5419,10 @@
         <v>2.26</v>
       </c>
       <c r="H26" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I26" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J26" t="n">
         <v>3.75</v>
@@ -5431,7 +5431,7 @@
         <v>4.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
@@ -5446,13 +5446,13 @@
         <v>2.26</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S26" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
         <v>1.61</v>
@@ -5461,7 +5461,7 @@
         <v>2.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W26" t="n">
         <v>1.79</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -5610,22 +5610,22 @@
         <v>2.26</v>
       </c>
       <c r="G27" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="H27" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I27" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J27" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K27" t="n">
         <v>3.95</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M27" t="n">
         <v>1.05</v>
@@ -5634,7 +5634,7 @@
         <v>4.7</v>
       </c>
       <c r="O27" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P27" t="n">
         <v>2.22</v>
@@ -5652,13 +5652,13 @@
         <v>1.62</v>
       </c>
       <c r="U27" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="V27" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X27" t="n">
         <v>23</v>
@@ -5688,7 +5688,7 @@
         <v>19.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH27" t="n">
         <v>17.5</v>
@@ -5709,22 +5709,22 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT27" t="n">
         <v>11</v>
@@ -5736,10 +5736,10 @@
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY27" t="n">
         <v>9.800000000000001</v>
@@ -5748,19 +5748,19 @@
         <v>12.5</v>
       </c>
       <c r="BA27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB27" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB27" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BC27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF27" t="n">
         <v>11</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -5825,13 +5825,13 @@
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
         <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q28" t="n">
         <v>1.73</v>
@@ -5840,13 +5840,13 @@
         <v>1.46</v>
       </c>
       <c r="S28" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="T28" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U28" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V28" t="n">
         <v>1.41</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G30" t="n">
         <v>1.37</v>
@@ -6204,10 +6204,10 @@
         <v>5.8</v>
       </c>
       <c r="K30" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M30" t="n">
         <v>1.03</v>
@@ -6222,7 +6222,7 @@
         <v>2.52</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R30" t="n">
         <v>1.6</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="G31" t="n">
         <v>2.62</v>
       </c>
       <c r="H31" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="I31" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
         <v>3.2</v>
       </c>
       <c r="K31" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L31" t="n">
         <v>1.31</v>
@@ -6428,13 +6428,13 @@
         <v>1.64</v>
       </c>
       <c r="U31" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V31" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W31" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X31" t="n">
         <v>21</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -6583,10 +6583,10 @@
         <v>6.2</v>
       </c>
       <c r="H32" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="J32" t="n">
         <v>3.8</v>
@@ -6625,7 +6625,7 @@
         <v>1.96</v>
       </c>
       <c r="V32" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="W32" t="n">
         <v>1.19</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G33" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H33" t="n">
         <v>3.25</v>
       </c>
       <c r="I33" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K33" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L33" t="n">
         <v>1.48</v>
@@ -6795,7 +6795,7 @@
         <v>1.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O33" t="n">
         <v>1.45</v>
@@ -6804,7 +6804,7 @@
         <v>1.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R33" t="n">
         <v>1.24</v>
@@ -6819,7 +6819,7 @@
         <v>1.84</v>
       </c>
       <c r="V33" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W33" t="n">
         <v>1.65</v>
@@ -6828,13 +6828,13 @@
         <v>12.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z33" t="n">
         <v>28</v>
       </c>
       <c r="AA33" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
         <v>8.4</v>
@@ -6855,16 +6855,16 @@
         <v>14.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI33" t="n">
         <v>80</v>
       </c>
       <c r="AJ33" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK33" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL33" t="n">
         <v>55</v>
@@ -6876,7 +6876,7 @@
         <v>30</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP33" t="n">
         <v>7.8</v>
@@ -6888,7 +6888,7 @@
         <v>17</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT33" t="n">
         <v>6.8</v>
@@ -6900,41 +6900,41 @@
         <v>11</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AX33" t="n">
         <v>10.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ33" t="n">
         <v>15</v>
       </c>
       <c r="BA33" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB33" t="n">
         <v>5.5</v>
       </c>
-      <c r="BB33" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BC33" t="n">
-        <v>5.1</v>
+        <v>25</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF33" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BG33" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -7159,16 +7159,16 @@
         </is>
       </c>
       <c r="F35" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" t="n">
         <v>3.05</v>
       </c>
-      <c r="G35" t="n">
-        <v>3.1</v>
-      </c>
       <c r="H35" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I35" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J35" t="n">
         <v>4.3</v>
@@ -7189,16 +7189,16 @@
         <v>1.15</v>
       </c>
       <c r="P35" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R35" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="S35" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="T35" t="n">
         <v>1.48</v>
@@ -7207,19 +7207,19 @@
         <v>2.98</v>
       </c>
       <c r="V35" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="W35" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X35" t="n">
         <v>32</v>
       </c>
       <c r="Y35" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z35" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA35" t="n">
         <v>29</v>
@@ -7228,13 +7228,13 @@
         <v>22</v>
       </c>
       <c r="AC35" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD35" t="n">
         <v>11.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF35" t="n">
         <v>27</v>
@@ -7243,25 +7243,25 @@
         <v>14</v>
       </c>
       <c r="AH35" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ35" t="n">
         <v>48</v>
       </c>
       <c r="AK35" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL35" t="n">
         <v>29</v>
       </c>
       <c r="AM35" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN35" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO35" t="n">
         <v>9</v>
@@ -7273,7 +7273,7 @@
         <v>17.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS35" t="n">
         <v>26</v>
@@ -7294,10 +7294,10 @@
         <v>25</v>
       </c>
       <c r="AY35" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ35" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA35" t="n">
         <v>23</v>
@@ -7309,7 +7309,7 @@
         <v>24</v>
       </c>
       <c r="BD35" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE35" t="n">
         <v>40</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -7359,10 +7359,10 @@
         <v>5.3</v>
       </c>
       <c r="H36" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I36" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="J36" t="n">
         <v>4</v>
@@ -7383,10 +7383,10 @@
         <v>1.33</v>
       </c>
       <c r="P36" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
         <v>1.37</v>
@@ -7395,13 +7395,13 @@
         <v>3.6</v>
       </c>
       <c r="T36" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U36" t="n">
         <v>2.02</v>
       </c>
       <c r="V36" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="W36" t="n">
         <v>1.23</v>
@@ -7410,16 +7410,16 @@
         <v>14.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AB36" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC36" t="n">
         <v>8.800000000000001</v>
@@ -7428,10 +7428,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE36" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF36" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG36" t="n">
         <v>19.5</v>
@@ -7440,13 +7440,13 @@
         <v>21</v>
       </c>
       <c r="AI36" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ36" t="n">
         <v>130</v>
       </c>
       <c r="AK36" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL36" t="n">
         <v>75</v>
@@ -7464,10 +7464,10 @@
         <v>13</v>
       </c>
       <c r="AQ36" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR36" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS36" t="n">
         <v>17</v>
@@ -7494,10 +7494,10 @@
         <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB36" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BC36" t="n">
         <v>60</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -7547,25 +7547,25 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G37" t="n">
         <v>2.82</v>
       </c>
       <c r="H37" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I37" t="n">
         <v>3.4</v>
       </c>
       <c r="J37" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K37" t="n">
         <v>3.2</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M37" t="n">
         <v>1.11</v>
@@ -7598,13 +7598,13 @@
         <v>1.41</v>
       </c>
       <c r="W37" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X37" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y37" t="n">
         <v>11</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>11.5</v>
       </c>
       <c r="Z37" t="n">
         <v>25</v>
@@ -7631,7 +7631,7 @@
         <v>16</v>
       </c>
       <c r="AH37" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
@@ -7643,7 +7643,7 @@
         <v>46</v>
       </c>
       <c r="AL37" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
@@ -7652,7 +7652,7 @@
         <v>50</v>
       </c>
       <c r="AO37" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
         <v>8.199999999999999</v>
@@ -7664,7 +7664,7 @@
         <v>15</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT37" t="n">
         <v>7.2</v>
@@ -7676,7 +7676,7 @@
         <v>10.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AX37" t="n">
         <v>11.5</v>
@@ -7688,29 +7688,29 @@
         <v>18</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB37" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BC37" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7747,7 @@
         <v>3.4</v>
       </c>
       <c r="H38" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I38" t="n">
         <v>2.52</v>
@@ -7780,7 +7780,7 @@
         <v>1.35</v>
       </c>
       <c r="S38" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T38" t="n">
         <v>1.76</v>
@@ -7804,22 +7804,22 @@
         <v>17.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC38" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE38" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF38" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AG38" t="n">
         <v>16</v>
@@ -7828,25 +7828,25 @@
         <v>20</v>
       </c>
       <c r="AI38" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK38" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL38" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM38" t="n">
         <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AO38" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP38" t="n">
         <v>11</v>
@@ -7858,10 +7858,10 @@
         <v>11.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU38" t="n">
         <v>7.2</v>
@@ -7873,38 +7873,38 @@
         <v>19</v>
       </c>
       <c r="AX38" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AY38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ38" t="n">
         <v>15</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB38" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.9</v>
+        <v>30</v>
       </c>
       <c r="BD38" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="BE38" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.9</v>
+        <v>29</v>
       </c>
       <c r="BG38" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="G39" t="n">
         <v>2.26</v>
@@ -7965,10 +7965,10 @@
         <v>1.44</v>
       </c>
       <c r="P39" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R39" t="n">
         <v>1.24</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -775,7 +775,7 @@
         <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -787,10 +787,10 @@
         <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R2" t="n">
         <v>1.51</v>
@@ -799,10 +799,10 @@
         <v>2.84</v>
       </c>
       <c r="T2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V2" t="n">
         <v>1.12</v>
@@ -820,16 +820,16 @@
         <v>80</v>
       </c>
       <c r="AA2" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC2" t="n">
         <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE2" t="n">
         <v>140</v>
@@ -862,7 +862,7 @@
         <v>6.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP2" t="n">
         <v>17.5</v>
@@ -871,13 +871,13 @@
         <v>26</v>
       </c>
       <c r="AR2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
         <v>27</v>
       </c>
       <c r="AW2" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
         <v>8</v>
@@ -898,10 +898,10 @@
         <v>22</v>
       </c>
       <c r="BA2" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
         <v>13.5</v>
@@ -910,17 +910,17 @@
         <v>25</v>
       </c>
       <c r="BE2" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF2" t="n">
         <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="I3" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.44</v>
@@ -975,13 +975,13 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
         <v>2.18</v>
@@ -990,7 +990,7 @@
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="T3" t="n">
         <v>2.16</v>
@@ -999,7 +999,7 @@
         <v>1.7</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="W3" t="n">
         <v>1.15</v>
@@ -1062,7 +1062,7 @@
         <v>4.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AR3" t="n">
         <v>4.1</v>
@@ -1071,7 +1071,7 @@
         <v>5.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.3</v>
+        <v>14</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
@@ -1101,7 +1101,7 @@
         <v>7</v>
       </c>
       <c r="BD3" t="n">
-        <v>7</v>
+        <v>2.16</v>
       </c>
       <c r="BE3" t="n">
         <v>7.2</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
@@ -1157,7 +1157,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1169,13 +1169,13 @@
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
         <v>1.61</v>
@@ -1184,7 +1184,7 @@
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H5" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
         <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
@@ -1387,10 +1387,10 @@
         <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X5" t="n">
         <v>15.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -1539,13 +1539,13 @@
         <v>1.72</v>
       </c>
       <c r="H6" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I6" t="n">
         <v>7.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
         <v>4.1</v>
@@ -1566,7 +1566,7 @@
         <v>1.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
@@ -1653,10 +1653,10 @@
         <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.65</v>
+        <v>5.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AV6" t="n">
         <v>20</v>
@@ -1665,7 +1665,7 @@
         <v>7.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY6" t="n">
         <v>7.6</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>3.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
         <v>1.92</v>
@@ -1739,10 +1739,10 @@
         <v>2.06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.32</v>
@@ -1766,19 +1766,19 @@
         <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.94</v>
       </c>
       <c r="W7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
         <v>2.96</v>
       </c>
       <c r="L8" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
         <v>1.15</v>
@@ -2032,13 +2032,13 @@
         <v>4.1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8" t="n">
         <v>4.2</v>
@@ -2050,25 +2050,25 @@
         <v>6</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY8" t="n">
         <v>5.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.4</v>
+        <v>3.55</v>
       </c>
       <c r="BB8" t="n">
         <v>7.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BD8" t="n">
         <v>8.199999999999999</v>
@@ -2080,11 +2080,11 @@
         <v>7.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="G9" t="n">
         <v>9.800000000000001</v>
@@ -2127,43 +2127,43 @@
         <v>1.57</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
         <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="R9" t="n">
         <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V9" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="W9" t="n">
         <v>1.12</v>
@@ -2220,65 +2220,65 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>2.82</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>2.72</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="G10" t="n">
         <v>2.8</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="J10" t="n">
         <v>2.92</v>
@@ -2333,19 +2333,19 @@
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
         <v>1.39</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
         <v>3.45</v>
@@ -2354,10 +2354,10 @@
         <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
         <v>1.55</v>
@@ -2381,10 +2381,10 @@
         <v>9</v>
       </c>
       <c r="AD10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
@@ -2396,7 +2396,7 @@
         <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
         <v>50</v>
@@ -2411,10 +2411,10 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP10" t="n">
         <v>1.03</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>1.85</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
         <v>4.1</v>
@@ -2527,7 +2527,7 @@
         <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="O11" t="n">
         <v>1.34</v>
@@ -2542,7 +2542,7 @@
         <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>1.87</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
         <v>1.9</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
         <v>3.95</v>
@@ -2736,19 +2736,19 @@
         <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
         <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X12" t="n">
         <v>23</v>
@@ -2757,7 +2757,7 @@
         <v>19</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA12" t="n">
         <v>75</v>
@@ -2769,7 +2769,7 @@
         <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
         <v>46</v>
@@ -2781,7 +2781,7 @@
         <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI12" t="n">
         <v>50</v>
@@ -2814,7 +2814,7 @@
         <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
@@ -2826,7 +2826,7 @@
         <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -2838,29 +2838,29 @@
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC12" t="n">
         <v>15.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K13" t="n">
         <v>950</v>
@@ -2912,19 +2912,19 @@
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O13" t="n">
         <v>1.15</v>
       </c>
       <c r="P13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
@@ -2933,16 +2933,16 @@
         <v>1.15</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2999,7 +2999,7 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.03</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -3094,10 +3094,10 @@
         <v>1.09</v>
       </c>
       <c r="I14" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -3106,10 +3106,10 @@
         <v>1.21</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.14</v>
@@ -3136,7 +3136,7 @@
         <v>1.07</v>
       </c>
       <c r="W14" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF14" t="n">
         <v>3.05</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -3309,13 +3309,13 @@
         <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
         <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
         <v>3.05</v>
@@ -3348,10 +3348,10 @@
         <v>13</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE15" t="n">
         <v>50</v>
@@ -3393,10 +3393,10 @@
         <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
         <v>9.800000000000001</v>
@@ -3408,7 +3408,7 @@
         <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AX15" t="n">
         <v>10.5</v>
@@ -3420,7 +3420,7 @@
         <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.8</v>
+        <v>32</v>
       </c>
       <c r="BB15" t="n">
         <v>19.5</v>
@@ -3429,20 +3429,20 @@
         <v>19.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF15" t="n">
         <v>11</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="G16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H16" t="n">
         <v>4.7</v>
@@ -3485,13 +3485,13 @@
         <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -3503,10 +3503,10 @@
         <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
         <v>1.43</v>
@@ -3524,7 +3524,7 @@
         <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X16" t="n">
         <v>22</v>
@@ -3539,7 +3539,7 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC16" t="n">
         <v>11</v>
@@ -3551,7 +3551,7 @@
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -3584,13 +3584,13 @@
         <v>14</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
         <v>7.8</v>
@@ -3599,13 +3599,13 @@
         <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>15</v>
+        <v>4.9</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY16" t="n">
         <v>7.8</v>
@@ -3614,29 +3614,29 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BB16" t="n">
         <v>14</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
         <v>7.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>50</v>
+        <v>5.9</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -3667,55 +3667,55 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G17" t="n">
         <v>1.62</v>
       </c>
       <c r="H17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P17" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R17" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S17" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="T17" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="U17" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W17" t="n">
         <v>2.62</v>
@@ -3733,10 +3733,10 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD17" t="n">
         <v>1000</v>
@@ -3745,7 +3745,7 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
@@ -3769,7 +3769,7 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -3778,59 +3778,59 @@
         <v>4.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AR17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW17" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AX17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ17" t="n">
         <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB17" t="n">
         <v>12</v>
       </c>
       <c r="BC17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -3861,25 +3861,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G18" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I18" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
@@ -3894,7 +3894,7 @@
         <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R18" t="n">
         <v>1.38</v>
@@ -3903,13 +3903,13 @@
         <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U18" t="n">
         <v>2.16</v>
       </c>
       <c r="V18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
         <v>1.73</v>
@@ -3921,13 +3921,13 @@
         <v>17.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
         <v>10</v>
@@ -3942,10 +3942,10 @@
         <v>18</v>
       </c>
       <c r="AG18" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
@@ -3963,7 +3963,7 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
@@ -3972,59 +3972,59 @@
         <v>13.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AU18" t="n">
         <v>7.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AX18" t="n">
         <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BB18" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>16.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF18" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.95</v>
+        <v>26</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J19" t="n">
         <v>3.2</v>
@@ -4073,7 +4073,7 @@
         <v>3.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
@@ -4169,16 +4169,16 @@
         <v>3.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS19" t="n">
         <v>5.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV19" t="n">
         <v>4.2</v>
@@ -4187,7 +4187,7 @@
         <v>5.1</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY19" t="n">
         <v>4</v>
@@ -4214,11 +4214,11 @@
         <v>4.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="H20" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="I20" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>3.75</v>
@@ -4279,28 +4279,28 @@
         <v>1.27</v>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R20" t="n">
         <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U20" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V20" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W20" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
         <v>18.5</v>
@@ -4309,28 +4309,28 @@
         <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AA20" t="n">
         <v>40</v>
       </c>
       <c r="AB20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD20" t="n">
         <v>12</v>
       </c>
       <c r="AE20" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AF20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>17</v>
@@ -4339,13 +4339,13 @@
         <v>38</v>
       </c>
       <c r="AJ20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM20" t="n">
         <v>80</v>
@@ -4354,31 +4354,31 @@
         <v>25</v>
       </c>
       <c r="AO20" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AP20" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR20" t="n">
         <v>15</v>
       </c>
       <c r="AS20" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AT20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV20" t="n">
         <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AX20" t="n">
         <v>17.5</v>
@@ -4396,13 +4396,13 @@
         <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BE20" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BF20" t="n">
         <v>20</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>2.14</v>
       </c>
       <c r="G21" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H21" t="n">
         <v>3.3</v>
@@ -4470,7 +4470,7 @@
         <v>4.7</v>
       </c>
       <c r="O21" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P21" t="n">
         <v>2.26</v>
@@ -4479,7 +4479,7 @@
         <v>1.64</v>
       </c>
       <c r="R21" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="n">
         <v>2.6</v>
@@ -4494,7 +4494,7 @@
         <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X21" t="n">
         <v>25</v>
@@ -4551,16 +4551,16 @@
         <v>32</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT21" t="n">
         <v>9.6</v>
@@ -4572,41 +4572,41 @@
         <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AY21" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BA21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG21" t="n">
         <v>6</v>
       </c>
-      <c r="BB21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -4643,13 +4643,13 @@
         <v>2.36</v>
       </c>
       <c r="H22" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I22" t="n">
         <v>3.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K22" t="n">
         <v>4.6</v>
@@ -4661,19 +4661,19 @@
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O22" t="n">
         <v>1.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q22" t="n">
         <v>1.46</v>
       </c>
       <c r="R22" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S22" t="n">
         <v>2.02</v>
@@ -4682,7 +4682,7 @@
         <v>1.46</v>
       </c>
       <c r="U22" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="V22" t="n">
         <v>1.46</v>
@@ -4700,7 +4700,7 @@
         <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB22" t="n">
         <v>21</v>
@@ -4712,7 +4712,7 @@
         <v>17</v>
       </c>
       <c r="AE22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF22" t="n">
         <v>23</v>
@@ -4721,10 +4721,10 @@
         <v>14.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ22" t="n">
         <v>36</v>
@@ -4742,10 +4742,10 @@
         <v>11</v>
       </c>
       <c r="AO22" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ22" t="n">
         <v>16</v>
@@ -4754,7 +4754,7 @@
         <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT22" t="n">
         <v>13.5</v>
@@ -4769,7 +4769,7 @@
         <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>15</v>
+        <v>4.6</v>
       </c>
       <c r="AY22" t="n">
         <v>9.4</v>
@@ -4778,10 +4778,10 @@
         <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC22" t="n">
         <v>15.5</v>
@@ -4790,7 +4790,7 @@
         <v>19</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF22" t="n">
         <v>7.4</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>1.91</v>
       </c>
       <c r="G23" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H23" t="n">
         <v>3.85</v>
@@ -4855,7 +4855,7 @@
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O23" t="n">
         <v>1.21</v>
@@ -4873,7 +4873,7 @@
         <v>2.54</v>
       </c>
       <c r="T23" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U23" t="n">
         <v>2.34</v>
@@ -4882,13 +4882,13 @@
         <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X23" t="n">
         <v>26</v>
       </c>
       <c r="Y23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="n">
         <v>36</v>
@@ -4900,19 +4900,19 @@
         <v>14.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE23" t="n">
         <v>48</v>
       </c>
       <c r="AF23" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
         <v>18.5</v>
@@ -4945,10 +4945,10 @@
         <v>14.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT23" t="n">
         <v>9.6</v>
@@ -4960,7 +4960,7 @@
         <v>12.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX23" t="n">
         <v>11</v>
@@ -4972,7 +4972,7 @@
         <v>12</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB23" t="n">
         <v>17.5</v>
@@ -4984,17 +4984,17 @@
         <v>21</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF23" t="n">
         <v>7.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>24</v>
+        <v>5.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="G24" t="n">
         <v>3.2</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="I24" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>3.15</v>
@@ -5142,7 +5142,7 @@
         <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT24" t="n">
         <v>8.4</v>
@@ -5154,7 +5154,7 @@
         <v>9.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AX24" t="n">
         <v>14.5</v>
@@ -5166,29 +5166,29 @@
         <v>13.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF24" t="n">
-        <v>27</v>
+        <v>6.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>23</v>
+        <v>6.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -5228,10 +5228,10 @@
         <v>1.52</v>
       </c>
       <c r="I25" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="J25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K25" t="n">
         <v>5.3</v>
@@ -5264,10 +5264,10 @@
         <v>1.68</v>
       </c>
       <c r="U25" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V25" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="W25" t="n">
         <v>1.17</v>
@@ -5363,13 +5363,13 @@
         <v>20</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC25" t="n">
         <v>5</v>
       </c>
       <c r="BD25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BE25" t="n">
         <v>5</v>
@@ -5378,11 +5378,11 @@
         <v>4.9</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -5416,10 +5416,10 @@
         <v>2.1</v>
       </c>
       <c r="G26" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="H26" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="I26" t="n">
         <v>3.65</v>
@@ -5428,7 +5428,7 @@
         <v>3.75</v>
       </c>
       <c r="K26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L26" t="n">
         <v>1.27</v>
@@ -5443,7 +5443,7 @@
         <v>1.23</v>
       </c>
       <c r="P26" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q26" t="n">
         <v>1.6</v>
@@ -5455,7 +5455,7 @@
         <v>2.7</v>
       </c>
       <c r="T26" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U26" t="n">
         <v>2.4</v>
@@ -5464,7 +5464,7 @@
         <v>1.38</v>
       </c>
       <c r="W26" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="X26" t="n">
         <v>25</v>
@@ -5482,7 +5482,7 @@
         <v>15.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD26" t="n">
         <v>18</v>
@@ -5497,10 +5497,10 @@
         <v>13.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ26" t="n">
         <v>34</v>
@@ -5521,19 +5521,19 @@
         <v>34</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>12</v>
+        <v>3.7</v>
       </c>
       <c r="AR26" t="n">
-        <v>19.5</v>
+        <v>4</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AU26" t="n">
         <v>6.8</v>
@@ -5542,7 +5542,7 @@
         <v>10.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="AX26" t="n">
         <v>11.5</v>
@@ -5551,32 +5551,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB26" t="n">
         <v>19.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="BD26" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -5625,22 +5625,22 @@
         <v>3.95</v>
       </c>
       <c r="L27" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M27" t="n">
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O27" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P27" t="n">
         <v>2.22</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R27" t="n">
         <v>1.5</v>
@@ -5649,10 +5649,10 @@
         <v>2.72</v>
       </c>
       <c r="T27" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U27" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="V27" t="n">
         <v>1.41</v>
@@ -5661,7 +5661,7 @@
         <v>1.74</v>
       </c>
       <c r="X27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y27" t="n">
         <v>18.5</v>
@@ -5673,10 +5673,10 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD27" t="n">
         <v>16.5</v>
@@ -5685,10 +5685,10 @@
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH27" t="n">
         <v>17.5</v>
@@ -5715,16 +5715,16 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AT27" t="n">
         <v>11</v>
@@ -5736,31 +5736,31 @@
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AX27" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ27" t="n">
         <v>12.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BD27" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.4</v>
+        <v>50</v>
       </c>
       <c r="BF27" t="n">
         <v>11</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -5837,16 +5837,16 @@
         <v>1.73</v>
       </c>
       <c r="R28" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="T28" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U28" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V28" t="n">
         <v>1.41</v>
@@ -5918,10 +5918,10 @@
         <v>18</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT28" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU28" t="n">
         <v>6.8</v>
@@ -5930,7 +5930,7 @@
         <v>10.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AX28" t="n">
         <v>12.5</v>
@@ -5942,19 +5942,19 @@
         <v>12</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BC28" t="n">
         <v>17.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF28" t="n">
         <v>11.5</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -6192,10 +6192,10 @@
         <v>1.31</v>
       </c>
       <c r="G30" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="H30" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I30" t="n">
         <v>12.5</v>
@@ -6204,7 +6204,7 @@
         <v>5.8</v>
       </c>
       <c r="K30" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L30" t="n">
         <v>1.24</v>
@@ -6219,19 +6219,19 @@
         <v>1.18</v>
       </c>
       <c r="P30" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R30" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S30" t="n">
         <v>2.36</v>
       </c>
       <c r="T30" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U30" t="n">
         <v>1.9</v>
@@ -6240,7 +6240,7 @@
         <v>1.09</v>
       </c>
       <c r="W30" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="X30" t="n">
         <v>32</v>
@@ -6255,7 +6255,7 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC30" t="n">
         <v>15.5</v>
@@ -6300,13 +6300,13 @@
         <v>20</v>
       </c>
       <c r="AQ30" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AS30" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT30" t="n">
         <v>8.800000000000001</v>
@@ -6315,10 +6315,10 @@
         <v>11</v>
       </c>
       <c r="AV30" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AW30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX30" t="n">
         <v>7.8</v>
@@ -6330,7 +6330,7 @@
         <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB30" t="n">
         <v>8.800000000000001</v>
@@ -6342,17 +6342,17 @@
         <v>25</v>
       </c>
       <c r="BE30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF30" t="n">
         <v>4.1</v>
       </c>
       <c r="BG30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="G31" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H31" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K31" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L31" t="n">
         <v>1.31</v>
@@ -6410,19 +6410,19 @@
         <v>4.1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P31" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R31" t="n">
         <v>1.43</v>
       </c>
       <c r="S31" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T31" t="n">
         <v>1.64</v>
@@ -6431,10 +6431,10 @@
         <v>2.28</v>
       </c>
       <c r="V31" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W31" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X31" t="n">
         <v>21</v>
@@ -6452,7 +6452,7 @@
         <v>14</v>
       </c>
       <c r="AC31" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD31" t="n">
         <v>15.5</v>
@@ -6500,7 +6500,7 @@
         <v>17</v>
       </c>
       <c r="AS31" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AT31" t="n">
         <v>9.4</v>
@@ -6512,7 +6512,7 @@
         <v>10</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX31" t="n">
         <v>13</v>
@@ -6524,19 +6524,19 @@
         <v>12</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BC31" t="n">
         <v>19</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF31" t="n">
         <v>13</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -6583,37 +6583,37 @@
         <v>6.2</v>
       </c>
       <c r="H32" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="I32" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="J32" t="n">
         <v>3.8</v>
       </c>
       <c r="K32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L32" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M32" t="n">
         <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O32" t="n">
         <v>1.31</v>
       </c>
       <c r="P32" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Q32" t="n">
         <v>1.89</v>
       </c>
       <c r="R32" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S32" t="n">
         <v>3.25</v>
@@ -6622,13 +6622,13 @@
         <v>1.86</v>
       </c>
       <c r="U32" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V32" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="W32" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X32" t="n">
         <v>18</v>
@@ -6637,19 +6637,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z32" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AA32" t="n">
         <v>21</v>
       </c>
       <c r="AB32" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AC32" t="n">
         <v>11</v>
       </c>
       <c r="AD32" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE32" t="n">
         <v>19.5</v>
@@ -6682,7 +6682,7 @@
         <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP32" t="n">
         <v>12.5</v>
@@ -6694,7 +6694,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT32" t="n">
         <v>15.5</v>
@@ -6703,44 +6703,44 @@
         <v>7.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW32" t="n">
         <v>15.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ32" t="n">
         <v>17.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB32" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BC32" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BG32" t="n">
         <v>8.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -6771,31 +6771,31 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G33" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H33" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I33" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J33" t="n">
         <v>3.15</v>
       </c>
       <c r="K33" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L33" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M33" t="n">
         <v>1.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O33" t="n">
         <v>1.45</v>
@@ -6810,7 +6810,7 @@
         <v>1.24</v>
       </c>
       <c r="S33" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T33" t="n">
         <v>1.98</v>
@@ -6819,10 +6819,10 @@
         <v>1.84</v>
       </c>
       <c r="V33" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W33" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X33" t="n">
         <v>12.5</v>
@@ -6831,10 +6831,10 @@
         <v>12.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB33" t="n">
         <v>8.4</v>
@@ -6858,7 +6858,7 @@
         <v>23</v>
       </c>
       <c r="AI33" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ33" t="n">
         <v>38</v>
@@ -6876,7 +6876,7 @@
         <v>30</v>
       </c>
       <c r="AO33" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
         <v>7.8</v>
@@ -6888,19 +6888,19 @@
         <v>17</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT33" t="n">
         <v>6.8</v>
       </c>
       <c r="AU33" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV33" t="n">
         <v>11</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX33" t="n">
         <v>10.5</v>
@@ -6912,29 +6912,29 @@
         <v>15</v>
       </c>
       <c r="BA33" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB33" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC33" t="n">
         <v>25</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF33" t="n">
         <v>6.2</v>
       </c>
-      <c r="BF33" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG33" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -6965,13 +6965,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G34" t="n">
         <v>2.5</v>
       </c>
       <c r="H34" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
         <v>3.3</v>
@@ -6998,7 +6998,7 @@
         <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R34" t="n">
         <v>1.4</v>
@@ -7016,7 +7016,7 @@
         <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X34" t="n">
         <v>20</v>
@@ -7073,62 +7073,62 @@
         <v>34</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF34" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -7159,79 +7159,79 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G35" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H35" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="I35" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="J35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K35" t="n">
         <v>4.3</v>
       </c>
-      <c r="K35" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L35" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M35" t="n">
         <v>1.03</v>
       </c>
       <c r="N35" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="O35" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="P35" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R35" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="S35" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="T35" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="U35" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="V35" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="W35" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X35" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA35" t="n">
         <v>32</v>
       </c>
-      <c r="Y35" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>29</v>
-      </c>
       <c r="AB35" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC35" t="n">
         <v>11</v>
       </c>
       <c r="AD35" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE35" t="n">
         <v>19.5</v>
@@ -7252,43 +7252,43 @@
         <v>48</v>
       </c>
       <c r="AK35" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL35" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM35" t="n">
         <v>44</v>
       </c>
       <c r="AN35" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO35" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP35" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AQ35" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AR35" t="n">
         <v>18.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT35" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU35" t="n">
         <v>10</v>
       </c>
       <c r="AV35" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX35" t="n">
         <v>25</v>
@@ -7303,26 +7303,26 @@
         <v>23</v>
       </c>
       <c r="BB35" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BC35" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD35" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE35" t="n">
         <v>40</v>
       </c>
       <c r="BF35" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="G36" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="H36" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="I36" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="J36" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K36" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L36" t="n">
         <v>1.42</v>
@@ -7377,34 +7377,34 @@
         <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O36" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P36" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R36" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
         <v>3.6</v>
       </c>
       <c r="T36" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U36" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V36" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="W36" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X36" t="n">
         <v>14.5</v>
@@ -7419,31 +7419,31 @@
         <v>19</v>
       </c>
       <c r="AB36" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE36" t="n">
         <v>19</v>
       </c>
       <c r="AF36" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG36" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI36" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ36" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK36" t="n">
         <v>70</v>
@@ -7452,13 +7452,13 @@
         <v>75</v>
       </c>
       <c r="AM36" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN36" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO36" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AP36" t="n">
         <v>13</v>
@@ -7470,40 +7470,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS36" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT36" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU36" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV36" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX36" t="n">
         <v>34</v>
       </c>
       <c r="AY36" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AZ36" t="n">
         <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB36" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BC36" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD36" t="n">
         <v>60</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>65</v>
       </c>
       <c r="BE36" t="n">
         <v>95</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>2.6</v>
       </c>
       <c r="G37" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H37" t="n">
         <v>3.15</v>
@@ -7610,7 +7610,7 @@
         <v>25</v>
       </c>
       <c r="AA37" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB37" t="n">
         <v>10</v>
@@ -7643,7 +7643,7 @@
         <v>46</v>
       </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
@@ -7652,7 +7652,7 @@
         <v>50</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP37" t="n">
         <v>8.199999999999999</v>
@@ -7664,7 +7664,7 @@
         <v>15</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.7</v>
+        <v>44</v>
       </c>
       <c r="AT37" t="n">
         <v>7.2</v>
@@ -7676,7 +7676,7 @@
         <v>10.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX37" t="n">
         <v>11.5</v>
@@ -7688,29 +7688,29 @@
         <v>18</v>
       </c>
       <c r="BA37" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB37" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB37" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BC37" t="n">
-        <v>4.5</v>
+        <v>27</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G38" t="n">
         <v>3.4</v>
@@ -7750,7 +7750,7 @@
         <v>2.38</v>
       </c>
       <c r="I38" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="J38" t="n">
         <v>3.35</v>
@@ -7789,7 +7789,7 @@
         <v>2.14</v>
       </c>
       <c r="V38" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W38" t="n">
         <v>1.41</v>
@@ -7798,7 +7798,7 @@
         <v>16.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z38" t="n">
         <v>17.5</v>
@@ -7822,7 +7822,7 @@
         <v>23</v>
       </c>
       <c r="AG38" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH38" t="n">
         <v>20</v>
@@ -7837,7 +7837,7 @@
         <v>1000</v>
       </c>
       <c r="AL38" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM38" t="n">
         <v>1000</v>
@@ -7846,7 +7846,7 @@
         <v>36</v>
       </c>
       <c r="AO38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP38" t="n">
         <v>11</v>
@@ -7858,7 +7858,7 @@
         <v>11.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT38" t="n">
         <v>11</v>
@@ -7882,29 +7882,29 @@
         <v>15</v>
       </c>
       <c r="BA38" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB38" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC38" t="n">
         <v>30</v>
       </c>
       <c r="BD38" t="n">
-        <v>40</v>
+        <v>7.8</v>
       </c>
       <c r="BE38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF38" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>29</v>
       </c>
       <c r="BG38" t="n">
         <v>18</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -7938,16 +7938,16 @@
         <v>1.87</v>
       </c>
       <c r="G39" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H39" t="n">
         <v>3.9</v>
       </c>
       <c r="I39" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J39" t="n">
-        <v>2.96</v>
+        <v>1.09</v>
       </c>
       <c r="K39" t="n">
         <v>4.1</v>
@@ -7968,7 +7968,7 @@
         <v>1.57</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R39" t="n">
         <v>1.24</v>
@@ -7986,7 +7986,7 @@
         <v>1.22</v>
       </c>
       <c r="W39" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8043,62 +8043,62 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF39" t="n">
-        <v>16</v>
+        <v>4.3</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="G2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>9.4</v>
       </c>
       <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
         <v>5.1</v>
       </c>
-      <c r="K2" t="n">
-        <v>5.2</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -790,28 +790,28 @@
         <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R2" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
         <v>2.84</v>
       </c>
       <c r="T2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U2" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="V2" t="n">
         <v>1.12</v>
       </c>
       <c r="W2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="n">
         <v>30</v>
@@ -820,7 +820,7 @@
         <v>80</v>
       </c>
       <c r="AA2" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AB2" t="n">
         <v>9</v>
@@ -841,10 +841,10 @@
         <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ2" t="n">
         <v>12</v>
@@ -853,28 +853,28 @@
         <v>14.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM2" t="n">
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO2" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
         <v>26</v>
       </c>
       <c r="AR2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AS2" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AT2" t="n">
         <v>8.4</v>
@@ -883,44 +883,44 @@
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AW2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
         <v>22</v>
       </c>
       <c r="BA2" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="BF2" t="n">
         <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.44</v>
@@ -975,49 +975,49 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O3" t="n">
         <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V3" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
         <v>5.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AW3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX3" t="n">
         <v>5.7</v>
       </c>
-      <c r="AX3" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AY3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA3" t="n">
         <v>5.9</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BB3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG3" t="n">
         <v>6</v>
       </c>
-      <c r="BA3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1184,19 +1184,19 @@
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="U4" t="n">
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -1345,16 +1345,16 @@
         <v>2.28</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
         <v>1.43</v>
@@ -1390,7 +1390,7 @@
         <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X5" t="n">
         <v>15.5</v>
@@ -1462,7 +1462,7 @@
         <v>6.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
         <v>11.5</v>
@@ -1498,11 +1498,11 @@
         <v>14</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="G6" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="H6" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="O6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="X6" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY6" t="n">
         <v>9</v>
       </c>
-      <c r="AD6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC6" t="n">
         <v>20</v>
       </c>
-      <c r="AW6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>15</v>
-      </c>
       <c r="BD6" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BG6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>1.92</v>
       </c>
       <c r="I7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J7" t="n">
         <v>3.65</v>
@@ -1748,7 +1748,7 @@
         <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
         <v>4</v>
@@ -1784,37 +1784,37 @@
         <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
@@ -1832,65 +1832,65 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.56</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H8" t="n">
         <v>3.6</v>
@@ -1933,7 +1933,7 @@
         <v>3.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="K8" t="n">
         <v>2.96</v>
@@ -1942,25 +1942,25 @@
         <v>1.65</v>
       </c>
       <c r="M8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.15</v>
       </c>
-      <c r="N8" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.16</v>
-      </c>
       <c r="S8" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="T8" t="n">
         <v>2.28</v>
@@ -1972,7 +1972,7 @@
         <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X8" t="n">
         <v>7.6</v>
@@ -1990,7 +1990,7 @@
         <v>7.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT8" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.2</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -2115,40 +2115,40 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G9" t="n">
         <v>6.6</v>
       </c>
-      <c r="G9" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="H9" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="I9" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R9" t="n">
         <v>1.41</v>
@@ -2157,16 +2157,16 @@
         <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="V9" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2220,25 +2220,25 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS9" t="n">
         <v>10.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="AV9" t="n">
         <v>7.8</v>
@@ -2247,38 +2247,38 @@
         <v>12.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>2.82</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>5.4</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BA9" t="n">
-        <v>2.72</v>
+        <v>6</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG9" t="n">
         <v>6.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -2315,16 +2315,16 @@
         <v>2.8</v>
       </c>
       <c r="H10" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I10" t="n">
         <v>3.35</v>
       </c>
       <c r="J10" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.39</v>
@@ -2333,7 +2333,7 @@
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.39</v>
@@ -2354,125 +2354,125 @@
         <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
         <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>500</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>500</v>
       </c>
       <c r="Z10" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>500</v>
       </c>
       <c r="AC10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY10" t="n">
         <v>9</v>
       </c>
-      <c r="AD10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>22</v>
+        <v>3.75</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I11" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
         <v>4.1</v>
@@ -2530,7 +2530,7 @@
         <v>2.7</v>
       </c>
       <c r="O11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P11" t="n">
         <v>1.74</v>
@@ -2539,7 +2539,7 @@
         <v>1.86</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
         <v>2.66</v>
@@ -2551,7 +2551,7 @@
         <v>1.94</v>
       </c>
       <c r="V11" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="W11" t="n">
         <v>1.17</v>
@@ -2587,7 +2587,7 @@
         <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>14.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
         <v>3.4</v>
@@ -2709,25 +2709,25 @@
         <v>3.95</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
         <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
         <v>1.71</v>
@@ -2736,7 +2736,7 @@
         <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T12" t="n">
         <v>1.64</v>
@@ -2748,10 +2748,10 @@
         <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
         <v>19</v>
@@ -2781,13 +2781,13 @@
         <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
         <v>50</v>
       </c>
       <c r="AJ12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK12" t="n">
         <v>24</v>
@@ -2799,7 +2799,7 @@
         <v>85</v>
       </c>
       <c r="AN12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
         <v>38</v>
@@ -2814,19 +2814,19 @@
         <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
         <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -2838,7 +2838,7 @@
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB12" t="n">
         <v>19</v>
@@ -2847,20 +2847,20 @@
         <v>15.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF12" t="n">
         <v>9.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -2915,13 +2915,13 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
         <v>1.15</v>
       </c>
       <c r="P13" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Q13" t="n">
         <v>1.14</v>
@@ -3002,49 +3002,49 @@
         <v>11</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -3091,16 +3091,16 @@
         <v>1.33</v>
       </c>
       <c r="H14" t="n">
-        <v>1.09</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J14" t="n">
         <v>5.5</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.21</v>
@@ -3109,13 +3109,13 @@
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="O14" t="n">
         <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="Q14" t="n">
         <v>1.38</v>
@@ -3127,10 +3127,10 @@
         <v>1.94</v>
       </c>
       <c r="T14" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U14" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V14" t="n">
         <v>1.07</v>
@@ -3202,7 +3202,7 @@
         <v>5.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT14" t="n">
         <v>3.95</v>
@@ -3214,16 +3214,16 @@
         <v>4.9</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA14" t="n">
         <v>5.2</v>
@@ -3244,11 +3244,11 @@
         <v>3.05</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H15" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
         <v>3.6</v>
@@ -3297,19 +3297,19 @@
         <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
         <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
         <v>1.83</v>
@@ -3324,7 +3324,7 @@
         <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V15" t="n">
         <v>1.38</v>
@@ -3342,7 +3342,7 @@
         <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AB15" t="n">
         <v>13</v>
@@ -3351,7 +3351,7 @@
         <v>8.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
         <v>50</v>
@@ -3393,7 +3393,7 @@
         <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.1</v>
+        <v>22</v>
       </c>
       <c r="AS15" t="n">
         <v>5</v>
@@ -3408,10 +3408,10 @@
         <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX15" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
         <v>9.800000000000001</v>
@@ -3423,7 +3423,7 @@
         <v>32</v>
       </c>
       <c r="BB15" t="n">
-        <v>19.5</v>
+        <v>5.2</v>
       </c>
       <c r="BC15" t="n">
         <v>19.5</v>
@@ -3432,7 +3432,7 @@
         <v>5</v>
       </c>
       <c r="BE15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF15" t="n">
         <v>11</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G16" t="n">
         <v>1.83</v>
@@ -3491,7 +3491,7 @@
         <v>4.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -3527,7 +3527,7 @@
         <v>2.2</v>
       </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="n">
         <v>1000</v>
@@ -3554,16 +3554,16 @@
         <v>12.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
         <v>21</v>
@@ -3575,7 +3575,7 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
@@ -3584,13 +3584,13 @@
         <v>14</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AT16" t="n">
         <v>7.8</v>
@@ -3599,10 +3599,10 @@
         <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AX16" t="n">
         <v>9.800000000000001</v>
@@ -3614,29 +3614,29 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BB16" t="n">
         <v>14</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BF16" t="n">
         <v>7.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -3670,10 +3670,10 @@
         <v>1.56</v>
       </c>
       <c r="G17" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H17" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I17" t="n">
         <v>7.2</v>
@@ -3703,10 +3703,10 @@
         <v>1.55</v>
       </c>
       <c r="R17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S17" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T17" t="n">
         <v>1.68</v>
@@ -3715,13 +3715,13 @@
         <v>2.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
         <v>2.62</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y17" t="n">
         <v>1000</v>
@@ -3751,16 +3751,16 @@
         <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL17" t="n">
         <v>1000</v>
@@ -3769,22 +3769,22 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT17" t="n">
         <v>8.800000000000001</v>
@@ -3793,10 +3793,10 @@
         <v>8.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX17" t="n">
         <v>8.800000000000001</v>
@@ -3808,7 +3808,7 @@
         <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB17" t="n">
         <v>12</v>
@@ -3817,20 +3817,20 @@
         <v>11.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BF17" t="n">
         <v>5.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
         <v>1.73</v>
       </c>
       <c r="X18" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Y18" t="n">
         <v>17.5</v>
@@ -3978,7 +3978,7 @@
         <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT18" t="n">
         <v>9</v>
@@ -3990,7 +3990,7 @@
         <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX18" t="n">
         <v>10.5</v>
@@ -4002,19 +4002,19 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.3</v>
+        <v>28</v>
       </c>
       <c r="BF18" t="n">
         <v>13.5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G19" t="n">
         <v>2.56</v>
@@ -4064,10 +4064,10 @@
         <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K19" t="n">
         <v>3.5</v>
@@ -4079,7 +4079,7 @@
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
         <v>1.4</v>
@@ -4091,7 +4091,7 @@
         <v>2.18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
         <v>4.1</v>
@@ -4103,22 +4103,22 @@
         <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
         <v>1.64</v>
       </c>
       <c r="X19" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="n">
         <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AA19" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AB19" t="n">
         <v>10.5</v>
@@ -4130,7 +4130,7 @@
         <v>17</v>
       </c>
       <c r="AE19" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF19" t="n">
         <v>17.5</v>
@@ -4139,86 +4139,86 @@
         <v>13.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AI19" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AJ19" t="n">
         <v>42</v>
       </c>
       <c r="AK19" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM19" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AN19" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AO19" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="AU19" t="n">
         <v>6.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB19" t="n">
         <v>5.1</v>
       </c>
-      <c r="AX19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA19" t="n">
+      <c r="BC19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD19" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BE19" t="n">
+        <v>26</v>
+      </c>
+      <c r="BF19" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G20" t="n">
         <v>2.9</v>
       </c>
       <c r="H20" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I20" t="n">
         <v>2.6</v>
@@ -4264,7 +4264,7 @@
         <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
         <v>1.3</v>
@@ -4273,7 +4273,7 @@
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
         <v>1.27</v>
@@ -4282,19 +4282,19 @@
         <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U20" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V20" t="n">
         <v>1.62</v>
@@ -4312,10 +4312,10 @@
         <v>22</v>
       </c>
       <c r="AA20" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC20" t="n">
         <v>8.6</v>
@@ -4324,7 +4324,7 @@
         <v>12</v>
       </c>
       <c r="AE20" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AF20" t="n">
         <v>21</v>
@@ -4336,7 +4336,7 @@
         <v>17</v>
       </c>
       <c r="AI20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ20" t="n">
         <v>46</v>
@@ -4357,7 +4357,7 @@
         <v>24</v>
       </c>
       <c r="AP20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ20" t="n">
         <v>11</v>
@@ -4390,7 +4390,7 @@
         <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
         <v>4.2</v>
@@ -4479,7 +4479,7 @@
         <v>1.64</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S21" t="n">
         <v>2.6</v>
@@ -4488,16 +4488,16 @@
         <v>1.59</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V21" t="n">
         <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="X21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y21" t="n">
         <v>1000</v>
@@ -4533,7 +4533,7 @@
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AK21" t="n">
         <v>21</v>
@@ -4551,10 +4551,10 @@
         <v>32</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AR21" t="n">
         <v>6</v>
@@ -4572,7 +4572,7 @@
         <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>29</v>
+        <v>6.2</v>
       </c>
       <c r="AX21" t="n">
         <v>5.1</v>
@@ -4581,7 +4581,7 @@
         <v>8.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BA21" t="n">
         <v>6.4</v>
@@ -4590,7 +4590,7 @@
         <v>20</v>
       </c>
       <c r="BC21" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BD21" t="n">
         <v>20</v>
@@ -4599,14 +4599,14 @@
         <v>6.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG21" t="n">
         <v>6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H22" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J22" t="n">
         <v>4.1</v>
@@ -4676,7 +4676,7 @@
         <v>1.77</v>
       </c>
       <c r="S22" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="T22" t="n">
         <v>1.46</v>
@@ -4688,10 +4688,10 @@
         <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y22" t="n">
         <v>25</v>
@@ -4745,7 +4745,7 @@
         <v>17.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AQ22" t="n">
         <v>16</v>
@@ -4754,7 +4754,7 @@
         <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT22" t="n">
         <v>13.5</v>
@@ -4769,7 +4769,7 @@
         <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY22" t="n">
         <v>9.4</v>
@@ -4781,7 +4781,7 @@
         <v>4.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC22" t="n">
         <v>15.5</v>
@@ -4790,7 +4790,7 @@
         <v>19</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF22" t="n">
         <v>7.4</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G23" t="n">
         <v>2.04</v>
@@ -4855,7 +4855,7 @@
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O23" t="n">
         <v>1.21</v>
@@ -4870,7 +4870,7 @@
         <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="T23" t="n">
         <v>1.6</v>
@@ -4885,13 +4885,13 @@
         <v>1.97</v>
       </c>
       <c r="X23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y23" t="n">
         <v>20</v>
       </c>
       <c r="Z23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
@@ -4915,19 +4915,19 @@
         <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
@@ -4936,7 +4936,7 @@
         <v>12</v>
       </c>
       <c r="AO23" t="n">
-        <v>38</v>
+        <v>230</v>
       </c>
       <c r="AP23" t="n">
         <v>16.5</v>
@@ -4945,10 +4945,10 @@
         <v>14.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AT23" t="n">
         <v>9.6</v>
@@ -4960,7 +4960,7 @@
         <v>12.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX23" t="n">
         <v>11</v>
@@ -4972,7 +4972,7 @@
         <v>12</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BB23" t="n">
         <v>17.5</v>
@@ -4984,17 +4984,17 @@
         <v>21</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF23" t="n">
         <v>7.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>3.2</v>
@@ -5046,13 +5046,13 @@
         <v>1.47</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P24" t="n">
         <v>1.76</v>
@@ -5070,7 +5070,7 @@
         <v>1.84</v>
       </c>
       <c r="U24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V24" t="n">
         <v>1.55</v>
@@ -5088,7 +5088,7 @@
         <v>18.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB24" t="n">
         <v>12</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
         <v>1.52</v>
       </c>
       <c r="I25" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="J25" t="n">
         <v>4.8</v>
@@ -5237,7 +5237,7 @@
         <v>5.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
@@ -5249,13 +5249,13 @@
         <v>1.18</v>
       </c>
       <c r="P25" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q25" t="n">
         <v>1.53</v>
       </c>
       <c r="R25" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S25" t="n">
         <v>2.32</v>
@@ -5327,7 +5327,7 @@
         <v>6.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="AQ25" t="n">
         <v>9.199999999999999</v>
@@ -5339,19 +5339,19 @@
         <v>11.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>21</v>
+        <v>5.1</v>
       </c>
       <c r="AU25" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AV25" t="n">
         <v>8</v>
       </c>
       <c r="AW25" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AY25" t="n">
         <v>18.5</v>
@@ -5363,26 +5363,26 @@
         <v>20</v>
       </c>
       <c r="BB25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC25" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC25" t="n">
-        <v>5</v>
-      </c>
       <c r="BD25" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE25" t="n">
         <v>5</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG25" t="n">
         <v>5.2</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G26" t="n">
         <v>2.18</v>
       </c>
       <c r="H26" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I26" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J26" t="n">
         <v>3.75</v>
@@ -5437,7 +5437,7 @@
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O26" t="n">
         <v>1.23</v>
@@ -5458,7 +5458,7 @@
         <v>1.62</v>
       </c>
       <c r="U26" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V26" t="n">
         <v>1.38</v>
@@ -5467,7 +5467,7 @@
         <v>1.84</v>
       </c>
       <c r="X26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y26" t="n">
         <v>21</v>
@@ -5494,7 +5494,7 @@
         <v>19</v>
       </c>
       <c r="AG26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH26" t="n">
         <v>19</v>
@@ -5503,34 +5503,34 @@
         <v>48</v>
       </c>
       <c r="AJ26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO26" t="n">
         <v>34</v>
       </c>
       <c r="AP26" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3.7</v>
+        <v>15</v>
       </c>
       <c r="AR26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT26" t="n">
         <v>11</v>
@@ -5542,31 +5542,31 @@
         <v>10.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>4.6</v>
       </c>
       <c r="AX26" t="n">
         <v>11.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB26" t="n">
         <v>19.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD26" t="n">
         <v>4</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF26" t="n">
         <v>10.5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -5607,37 +5607,37 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G27" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H27" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I27" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K27" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M27" t="n">
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O27" t="n">
         <v>1.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q27" t="n">
         <v>1.72</v>
@@ -5658,7 +5658,7 @@
         <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X27" t="n">
         <v>22</v>
@@ -5673,7 +5673,7 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AC27" t="n">
         <v>10</v>
@@ -5685,10 +5685,10 @@
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH27" t="n">
         <v>17.5</v>
@@ -5715,16 +5715,16 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AR27" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT27" t="n">
         <v>11</v>
@@ -5736,10 +5736,10 @@
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AY27" t="n">
         <v>10.5</v>
@@ -5748,16 +5748,16 @@
         <v>12.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE27" t="n">
         <v>50</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G28" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="H28" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="I28" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="J28" t="n">
         <v>3.65</v>
       </c>
       <c r="K28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
         <v>1.3</v>
@@ -5840,61 +5840,61 @@
         <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="T28" t="n">
         <v>1.63</v>
       </c>
       <c r="U28" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V28" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W28" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="X28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA28" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB28" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC28" t="n">
         <v>10.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG28" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH28" t="n">
         <v>18.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL28" t="n">
         <v>38</v>
@@ -5903,68 +5903,68 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO28" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV28" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AW28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX28" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC28" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.7</v>
+        <v>50</v>
       </c>
       <c r="BF28" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG28" t="n">
         <v>20</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -5998,43 +5998,43 @@
         <v>1.96</v>
       </c>
       <c r="G29" t="n">
-        <v>120</v>
+        <v>2.46</v>
       </c>
       <c r="H29" t="n">
-        <v>1.09</v>
+        <v>2.54</v>
       </c>
       <c r="I29" t="n">
-        <v>120</v>
+        <v>4.5</v>
       </c>
       <c r="J29" t="n">
-        <v>1.09</v>
+        <v>3.1</v>
       </c>
       <c r="K29" t="n">
-        <v>120</v>
+        <v>4.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="O29" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P29" t="n">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R29" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="T29" t="n">
         <v>1.82</v>
@@ -6043,10 +6043,10 @@
         <v>1.84</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6106,59 +6106,59 @@
         <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="O30" t="n">
         <v>1.18</v>
@@ -6240,7 +6240,7 @@
         <v>1.09</v>
       </c>
       <c r="W30" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="X30" t="n">
         <v>32</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>2.48</v>
       </c>
       <c r="G31" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H31" t="n">
         <v>2.92</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="G32" t="n">
         <v>6.2</v>
@@ -6607,7 +6607,7 @@
         <v>1.31</v>
       </c>
       <c r="P32" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q32" t="n">
         <v>1.89</v>
@@ -6619,10 +6619,10 @@
         <v>3.25</v>
       </c>
       <c r="T32" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U32" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="V32" t="n">
         <v>2.28</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -6777,16 +6777,16 @@
         <v>2.56</v>
       </c>
       <c r="H33" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I33" t="n">
         <v>3.5</v>
       </c>
       <c r="J33" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K33" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L33" t="n">
         <v>1.49</v>
@@ -6801,10 +6801,10 @@
         <v>1.45</v>
       </c>
       <c r="P33" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R33" t="n">
         <v>1.24</v>
@@ -6831,10 +6831,10 @@
         <v>12.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA33" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
         <v>8.4</v>
@@ -6846,13 +6846,13 @@
         <v>18.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
         <v>15</v>
       </c>
       <c r="AG33" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH33" t="n">
         <v>23</v>
@@ -6864,7 +6864,7 @@
         <v>38</v>
       </c>
       <c r="AK33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL33" t="n">
         <v>55</v>
@@ -6885,22 +6885,22 @@
         <v>9</v>
       </c>
       <c r="AR33" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT33" t="n">
         <v>6.8</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV33" t="n">
         <v>11</v>
       </c>
       <c r="AW33" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX33" t="n">
         <v>10.5</v>
@@ -6912,29 +6912,29 @@
         <v>15</v>
       </c>
       <c r="BA33" t="n">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="BB33" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC33" t="n">
         <v>25</v>
       </c>
       <c r="BD33" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="BE33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF33" t="n">
         <v>6.6</v>
       </c>
-      <c r="BF33" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG33" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -6965,16 +6965,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G34" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H34" t="n">
         <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J34" t="n">
         <v>3.5</v>
@@ -6989,19 +6989,19 @@
         <v>1.06</v>
       </c>
       <c r="N34" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="O34" t="n">
         <v>1.27</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S34" t="n">
         <v>2.72</v>
@@ -7013,22 +7013,22 @@
         <v>2.24</v>
       </c>
       <c r="V34" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W34" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X34" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Y34" t="n">
         <v>15</v>
       </c>
       <c r="Z34" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA34" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB34" t="n">
         <v>12</v>
@@ -7037,10 +7037,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF34" t="n">
         <v>16.5</v>
@@ -7049,13 +7049,13 @@
         <v>12</v>
       </c>
       <c r="AH34" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI34" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ34" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK34" t="n">
         <v>25</v>
@@ -7067,68 +7067,68 @@
         <v>95</v>
       </c>
       <c r="AN34" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AO34" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AP34" t="n">
-        <v>5.3</v>
+        <v>14</v>
       </c>
       <c r="AQ34" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>5.7</v>
+        <v>19</v>
       </c>
       <c r="AS34" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT34" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AY34" t="n">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ34" t="n">
-        <v>5.1</v>
+        <v>13.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB34" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BC34" t="n">
-        <v>5.6</v>
+        <v>20</v>
       </c>
       <c r="BD34" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="BE34" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BF34" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -7159,16 +7159,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="G35" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="H35" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="I35" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>4.2</v>
@@ -7177,7 +7177,7 @@
         <v>4.3</v>
       </c>
       <c r="L35" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M35" t="n">
         <v>1.03</v>
@@ -7195,37 +7195,37 @@
         <v>1.44</v>
       </c>
       <c r="R35" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S35" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T35" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="U35" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V35" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="W35" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X35" t="n">
         <v>36</v>
       </c>
       <c r="Y35" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z35" t="n">
         <v>21</v>
       </c>
       <c r="AA35" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB35" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC35" t="n">
         <v>11</v>
@@ -7246,37 +7246,37 @@
         <v>13.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ35" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AK35" t="n">
         <v>25</v>
       </c>
       <c r="AL35" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AM35" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AN35" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO35" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP35" t="n">
         <v>32</v>
       </c>
       <c r="AQ35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR35" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT35" t="n">
         <v>22</v>
@@ -7297,13 +7297,13 @@
         <v>13</v>
       </c>
       <c r="AZ35" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA35" t="n">
         <v>23</v>
       </c>
       <c r="BB35" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BC35" t="n">
         <v>23</v>
@@ -7315,14 +7315,14 @@
         <v>40</v>
       </c>
       <c r="BF35" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G36" t="n">
         <v>4.9</v>
       </c>
-      <c r="G36" t="n">
-        <v>5</v>
-      </c>
       <c r="H36" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="I36" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="J36" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K36" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L36" t="n">
         <v>1.42</v>
@@ -7377,46 +7377,46 @@
         <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O36" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P36" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="R36" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S36" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T36" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U36" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V36" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="W36" t="n">
         <v>1.25</v>
       </c>
       <c r="X36" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y36" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z36" t="n">
         <v>10.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AB36" t="n">
         <v>17</v>
@@ -7431,31 +7431,31 @@
         <v>19</v>
       </c>
       <c r="AF36" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG36" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ36" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK36" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL36" t="n">
         <v>70</v>
       </c>
-      <c r="AL36" t="n">
+      <c r="AM36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN36" t="n">
         <v>75</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>80</v>
       </c>
       <c r="AO36" t="n">
         <v>12.5</v>
@@ -7464,46 +7464,46 @@
         <v>13</v>
       </c>
       <c r="AQ36" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR36" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS36" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT36" t="n">
         <v>15.5</v>
       </c>
       <c r="AU36" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW36" t="n">
         <v>18</v>
       </c>
       <c r="AX36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AY36" t="n">
         <v>17.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BA36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB36" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BC36" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD36" t="n">
         <v>55</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>60</v>
       </c>
       <c r="BE36" t="n">
         <v>95</v>
@@ -7512,11 +7512,11 @@
         <v>70</v>
       </c>
       <c r="BG36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G37" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="H37" t="n">
         <v>3.15</v>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J37" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K37" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L37" t="n">
         <v>1.45</v>
@@ -7571,10 +7571,10 @@
         <v>1.11</v>
       </c>
       <c r="N37" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O37" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P37" t="n">
         <v>1.58</v>
@@ -7586,7 +7586,7 @@
         <v>1.2</v>
       </c>
       <c r="S37" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T37" t="n">
         <v>2</v>
@@ -7598,22 +7598,22 @@
         <v>1.41</v>
       </c>
       <c r="W37" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="X37" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="Y37" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z37" t="n">
         <v>25</v>
       </c>
       <c r="AA37" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC37" t="n">
         <v>8.4</v>
@@ -7625,10 +7625,10 @@
         <v>60</v>
       </c>
       <c r="AF37" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AG37" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AH37" t="n">
         <v>23</v>
@@ -7643,7 +7643,7 @@
         <v>46</v>
       </c>
       <c r="AL37" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
@@ -7652,37 +7652,37 @@
         <v>50</v>
       </c>
       <c r="AO37" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ37" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR37" t="n">
         <v>15</v>
       </c>
       <c r="AS37" t="n">
-        <v>44</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT37" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="AU37" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV37" t="n">
         <v>10.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.8</v>
+        <v>34</v>
       </c>
       <c r="AX37" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY37" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ37" t="n">
         <v>18</v>
@@ -7691,26 +7691,26 @@
         <v>48</v>
       </c>
       <c r="BB37" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC37" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.8</v>
+        <v>42</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -7741,67 +7741,67 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G38" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H38" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I38" t="n">
         <v>2.56</v>
       </c>
       <c r="J38" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K38" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L38" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M38" t="n">
         <v>1.07</v>
       </c>
       <c r="N38" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O38" t="n">
         <v>1.33</v>
       </c>
       <c r="P38" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R38" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T38" t="n">
         <v>1.76</v>
       </c>
       <c r="U38" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V38" t="n">
         <v>1.64</v>
       </c>
       <c r="W38" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X38" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y38" t="n">
         <v>11</v>
       </c>
       <c r="Z38" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AA38" t="n">
         <v>1000</v>
@@ -7810,7 +7810,7 @@
         <v>13</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD38" t="n">
         <v>12</v>
@@ -7849,16 +7849,16 @@
         <v>21</v>
       </c>
       <c r="AP38" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ38" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AS38" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT38" t="n">
         <v>11</v>
@@ -7867,7 +7867,7 @@
         <v>7.2</v>
       </c>
       <c r="AV38" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW38" t="n">
         <v>19</v>
@@ -7882,29 +7882,29 @@
         <v>15</v>
       </c>
       <c r="BA38" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB38" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC38" t="n">
         <v>30</v>
       </c>
       <c r="BD38" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE38" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF38" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>7.6</v>
       </c>
       <c r="BG38" t="n">
         <v>18</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -7935,58 +7935,58 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="G39" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H39" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J39" t="n">
-        <v>1.09</v>
+        <v>2.9</v>
       </c>
       <c r="K39" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="L39" t="n">
         <v>1.44</v>
       </c>
       <c r="M39" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N39" t="n">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="O39" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="P39" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R39" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="S39" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="T39" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
         <v>1.84</v>
       </c>
       <c r="V39" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W39" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8043,62 +8043,62 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AR39" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="AT39" t="n">
         <v>3.25</v>
       </c>
       <c r="AU39" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>3.3</v>
       </c>
-      <c r="AV39" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY39" t="n">
+      <c r="BA39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG39" t="n">
         <v>3.7</v>
       </c>
-      <c r="AZ39" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>5</v>
-      </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -766,7 +766,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
@@ -781,28 +781,28 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
         <v>1.71</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
         <v>1.12</v>
@@ -811,7 +811,7 @@
         <v>3.15</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y2" t="n">
         <v>30</v>
@@ -820,10 +820,10 @@
         <v>80</v>
       </c>
       <c r="AA2" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AB2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>11.5</v>
@@ -832,7 +832,7 @@
         <v>32</v>
       </c>
       <c r="AE2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF2" t="n">
         <v>8.800000000000001</v>
@@ -841,40 +841,40 @@
         <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
         <v>110</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK2" t="n">
         <v>14.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN2" t="n">
         <v>6.2</v>
       </c>
       <c r="AO2" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AP2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>26</v>
       </c>
       <c r="AR2" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="AS2" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>8.4</v>
@@ -883,10 +883,10 @@
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AX2" t="n">
         <v>8.199999999999999</v>
@@ -898,29 +898,29 @@
         <v>22</v>
       </c>
       <c r="BA2" t="n">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD2" t="n">
         <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="G3" t="n">
         <v>7.2</v>
@@ -960,82 +960,82 @@
         <v>1.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="T3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V3" t="n">
         <v>2.12</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.04</v>
       </c>
       <c r="W3" t="n">
         <v>1.16</v>
       </c>
       <c r="X3" t="n">
-        <v>90</v>
+        <v>10.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB3" t="n">
         <v>18.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1056,65 +1056,65 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AR3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU3" t="n">
         <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.7</v>
+        <v>34</v>
       </c>
       <c r="AY3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.9</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -1145,46 +1145,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>1.88</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>1.59</v>
       </c>
       <c r="O4" t="n">
         <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="T4" t="n">
         <v>1.87</v>
@@ -1193,13 +1193,13 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.02</v>
+        <v>1.93</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -1345,16 +1345,16 @@
         <v>2.28</v>
       </c>
       <c r="H5" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J5" t="n">
         <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
         <v>1.43</v>
@@ -1390,10 +1390,10 @@
         <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X5" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y5" t="n">
         <v>16</v>
@@ -1405,19 +1405,19 @@
         <v>95</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
         <v>19.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG5" t="n">
         <v>13.5</v>
@@ -1429,19 +1429,19 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AO5" t="n">
         <v>70</v>
@@ -1453,46 +1453,46 @@
         <v>9.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AU5" t="n">
         <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.1</v>
+        <v>34</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
         <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
         <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BF5" t="n">
         <v>14</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.88</v>
       </c>
       <c r="G6" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
         <v>4.4</v>
@@ -1545,7 +1545,7 @@
         <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
         <v>3.75</v>
@@ -1560,10 +1560,10 @@
         <v>2.78</v>
       </c>
       <c r="O6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q6" t="n">
         <v>2.28</v>
@@ -1578,22 +1578,22 @@
         <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V6" t="n">
         <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="X6" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="n">
         <v>14.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1608,10 +1608,10 @@
         <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
@@ -1620,7 +1620,7 @@
         <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
         <v>26</v>
@@ -1629,7 +1629,7 @@
         <v>27</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
@@ -1641,16 +1641,16 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ6" t="n">
         <v>11.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="AS6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AT6" t="n">
         <v>6</v>
@@ -1662,7 +1662,7 @@
         <v>16.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AX6" t="n">
         <v>9.4</v>
@@ -1674,29 +1674,29 @@
         <v>19.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC6" t="n">
         <v>20</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BF6" t="n">
         <v>14</v>
       </c>
       <c r="BG6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -1733,16 +1733,16 @@
         <v>4.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I7" t="n">
         <v>2.08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.32</v>
@@ -1796,7 +1796,7 @@
         <v>23</v>
       </c>
       <c r="AC7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
         <v>15</v>
@@ -1805,13 +1805,13 @@
         <v>29</v>
       </c>
       <c r="AF7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG7" t="n">
         <v>23</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>46</v>
@@ -1820,13 +1820,13 @@
         <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
         <v>1000</v>
@@ -1835,10 +1835,10 @@
         <v>17.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR7" t="n">
         <v>8.4</v>
@@ -1859,7 +1859,7 @@
         <v>13</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.52</v>
+        <v>14.5</v>
       </c>
       <c r="AY7" t="n">
         <v>11</v>
@@ -1868,29 +1868,29 @@
         <v>11</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.52</v>
+        <v>16</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.56</v>
+        <v>8.4</v>
       </c>
       <c r="BG7" t="n">
         <v>8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -1936,10 +1936,10 @@
         <v>2.8</v>
       </c>
       <c r="K8" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="M8" t="n">
         <v>1.16</v>
@@ -1948,10 +1948,10 @@
         <v>2.34</v>
       </c>
       <c r="O8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q8" t="n">
         <v>3</v>
@@ -1978,7 +1978,7 @@
         <v>7.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1987,7 +1987,7 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="AC8" t="n">
         <v>7</v>
@@ -2005,13 +2005,13 @@
         <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.8</v>
+        <v>3.75</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>2.82</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.8</v>
+        <v>2.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -2118,28 +2118,28 @@
         <v>5.1</v>
       </c>
       <c r="G9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="I9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.28</v>
@@ -2151,13 +2151,13 @@
         <v>1.85</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
         <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="U9" t="n">
         <v>1.94</v>
@@ -2172,25 +2172,25 @@
         <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF9" t="n">
         <v>1000</v>
@@ -2220,25 +2220,25 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AS9" t="n">
         <v>10.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AV9" t="n">
         <v>7.8</v>
@@ -2247,38 +2247,38 @@
         <v>12.5</v>
       </c>
       <c r="AX9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY9" t="n">
         <v>6</v>
       </c>
-      <c r="AY9" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BA9" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG9" t="n">
         <v>6.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -2363,25 +2363,25 @@
         <v>1.56</v>
       </c>
       <c r="X10" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
@@ -2390,16 +2390,16 @@
         <v>500</v>
       </c>
       <c r="AG10" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
         <v>500</v>
@@ -2423,10 +2423,10 @@
         <v>8</v>
       </c>
       <c r="AR10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS10" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
         <v>7.2</v>
@@ -2438,7 +2438,7 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
@@ -2447,32 +2447,32 @@
         <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BA10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BE10" t="n">
         <v>3.2</v>
       </c>
-      <c r="BB10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BF10" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>4.7</v>
       </c>
       <c r="G11" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
         <v>1.72</v>
       </c>
       <c r="I11" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="J11" t="n">
         <v>3.6</v>
@@ -2524,37 +2524,37 @@
         <v>1.42</v>
       </c>
       <c r="M11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="O11" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="P11" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
         <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U11" t="n">
         <v>1.94</v>
       </c>
       <c r="V11" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X11" t="n">
         <v>16</v>
@@ -2566,7 +2566,7 @@
         <v>12</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB11" t="n">
         <v>1000</v>
@@ -2578,19 +2578,19 @@
         <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AH11" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
         <v>1000</v>
@@ -2608,65 +2608,65 @@
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>14.5</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.65</v>
+        <v>7</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB11" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF11" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.99</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H12" t="n">
         <v>3.4</v>
@@ -2748,22 +2748,22 @@
         <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AA12" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
         <v>10.5</v>
@@ -2772,37 +2772,37 @@
         <v>18</v>
       </c>
       <c r="AE12" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AJ12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO12" t="n">
         <v>36</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>38</v>
       </c>
       <c r="AP12" t="n">
         <v>14.5</v>
@@ -2814,7 +2814,7 @@
         <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
@@ -2826,7 +2826,7 @@
         <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -2838,7 +2838,7 @@
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB12" t="n">
         <v>19</v>
@@ -2847,20 +2847,20 @@
         <v>15.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
         <v>9.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.06</v>
+        <v>1.76</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H13" t="n">
-        <v>1.06</v>
+        <v>3.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2918,143 +2918,143 @@
         <v>5.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>1.15</v>
+        <v>2.18</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.92</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -3088,16 +3088,16 @@
         <v>1.26</v>
       </c>
       <c r="G14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I14" t="n">
         <v>15</v>
       </c>
       <c r="J14" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="K14" t="n">
         <v>10.5</v>
@@ -3109,31 +3109,31 @@
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P14" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="R14" t="n">
         <v>1.68</v>
       </c>
       <c r="S14" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="T14" t="n">
         <v>1.84</v>
       </c>
       <c r="U14" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
         <v>3.95</v>
@@ -3175,7 +3175,7 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
@@ -3187,68 +3187,68 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>4.2</v>
       </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AR14" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="AU14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV14" t="n">
         <v>4.2</v>
       </c>
-      <c r="AV14" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AW14" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="AX14" t="n">
         <v>7.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.7</v>
+        <v>2.84</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="BF14" t="n">
         <v>3.05</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G15" t="n">
         <v>2.28</v>
@@ -3288,10 +3288,10 @@
         <v>3.4</v>
       </c>
       <c r="I15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J15" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
         <v>3.9</v>
@@ -3324,13 +3324,13 @@
         <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X15" t="n">
         <v>21</v>
@@ -3384,7 +3384,7 @@
         <v>17.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP15" t="n">
         <v>14.5</v>
@@ -3396,7 +3396,7 @@
         <v>22</v>
       </c>
       <c r="AS15" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT15" t="n">
         <v>9.800000000000001</v>
@@ -3408,7 +3408,7 @@
         <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AX15" t="n">
         <v>13</v>
@@ -3420,29 +3420,29 @@
         <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>32</v>
+        <v>5.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="BC15" t="n">
         <v>19.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF15" t="n">
         <v>11</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>4.7</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="n">
         <v>3.85</v>
@@ -3551,13 +3551,13 @@
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AG16" t="n">
         <v>10</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
@@ -3575,7 +3575,7 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
@@ -3584,13 +3584,13 @@
         <v>14</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
         <v>7.8</v>
@@ -3599,10 +3599,10 @@
         <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX16" t="n">
         <v>9.800000000000001</v>
@@ -3614,29 +3614,29 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB16" t="n">
         <v>14</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF16" t="n">
         <v>7.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -3697,10 +3697,10 @@
         <v>1.19</v>
       </c>
       <c r="P17" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R17" t="n">
         <v>1.58</v>
@@ -3721,7 +3721,7 @@
         <v>2.62</v>
       </c>
       <c r="X17" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
         <v>1000</v>
@@ -3733,10 +3733,10 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="AC17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD17" t="n">
         <v>1000</v>
@@ -3745,10 +3745,10 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH17" t="n">
         <v>500</v>
@@ -3757,10 +3757,10 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AL17" t="n">
         <v>1000</v>
@@ -3769,22 +3769,22 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="AT17" t="n">
         <v>8.800000000000001</v>
@@ -3796,7 +3796,7 @@
         <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX17" t="n">
         <v>8.800000000000001</v>
@@ -3805,10 +3805,10 @@
         <v>8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="BB17" t="n">
         <v>12</v>
@@ -3817,20 +3817,20 @@
         <v>11.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF17" t="n">
         <v>5.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
         <v>1.81</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
         <v>3.05</v>
@@ -3918,13 +3918,13 @@
         <v>17</v>
       </c>
       <c r="Y18" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
         <v>11.5</v>
@@ -3933,40 +3933,40 @@
         <v>10</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG18" t="n">
         <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ18" t="n">
         <v>34</v>
       </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP18" t="n">
         <v>13.5</v>
@@ -3978,7 +3978,7 @@
         <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AT18" t="n">
         <v>9</v>
@@ -3990,7 +3990,7 @@
         <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AX18" t="n">
         <v>10.5</v>
@@ -4002,16 +4002,16 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="BC18" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BE18" t="n">
         <v>28</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G19" t="n">
         <v>2.56</v>
@@ -4085,7 +4085,7 @@
         <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
         <v>2.18</v>
@@ -4097,7 +4097,7 @@
         <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U19" t="n">
         <v>2</v>
@@ -4109,13 +4109,13 @@
         <v>1.64</v>
       </c>
       <c r="X19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y19" t="n">
         <v>21</v>
       </c>
-      <c r="Y19" t="n">
-        <v>970</v>
-      </c>
       <c r="Z19" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AA19" t="n">
         <v>500</v>
@@ -4127,19 +4127,19 @@
         <v>8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AE19" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AF19" t="n">
         <v>17.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AI19" t="n">
         <v>500</v>
@@ -4148,13 +4148,13 @@
         <v>42</v>
       </c>
       <c r="AK19" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AL19" t="n">
         <v>500</v>
       </c>
       <c r="AM19" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
         <v>500</v>
@@ -4163,16 +4163,16 @@
         <v>500</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.95</v>
+        <v>8.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT19" t="n">
         <v>8</v>
@@ -4181,44 +4181,44 @@
         <v>6.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.6</v>
+        <v>12.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BE19" t="n">
         <v>26</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>2.9</v>
       </c>
       <c r="H20" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I20" t="n">
         <v>2.6</v>
@@ -4264,25 +4264,25 @@
         <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L20" t="n">
         <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
         <v>1.27</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R20" t="n">
         <v>1.46</v>
@@ -4291,10 +4291,10 @@
         <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U20" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V20" t="n">
         <v>1.62</v>
@@ -4309,7 +4309,7 @@
         <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA20" t="n">
         <v>70</v>
@@ -4330,46 +4330,46 @@
         <v>21</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="n">
-        <v>46</v>
+        <v>280</v>
       </c>
       <c r="AK20" t="n">
         <v>46</v>
       </c>
       <c r="AL20" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM20" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AN20" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AO20" t="n">
         <v>24</v>
       </c>
       <c r="AP20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS20" t="n">
         <v>22</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU20" t="n">
         <v>7.8</v>
@@ -4390,10 +4390,10 @@
         <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB20" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BC20" t="n">
         <v>24</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -4446,40 +4446,40 @@
         <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H21" t="n">
         <v>3.25</v>
       </c>
       <c r="I21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J21" t="n">
         <v>3.7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.65</v>
       </c>
       <c r="K21" t="n">
         <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="M21" t="n">
         <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O21" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P21" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R21" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S21" t="n">
         <v>2.6</v>
@@ -4488,19 +4488,19 @@
         <v>1.59</v>
       </c>
       <c r="U21" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W21" t="n">
         <v>1.79</v>
       </c>
       <c r="X21" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z21" t="n">
         <v>1000</v>
@@ -4509,58 +4509,58 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AC21" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="AK21" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="AL21" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO21" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="AR21" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT21" t="n">
         <v>9.6</v>
@@ -4572,41 +4572,41 @@
         <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX21" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AY21" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB21" t="n">
         <v>20</v>
       </c>
       <c r="BC21" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD21" t="n">
         <v>20</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         <v>1.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R22" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S22" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="T22" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U22" t="n">
         <v>2.84</v>
@@ -4700,7 +4700,7 @@
         <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AB22" t="n">
         <v>21</v>
@@ -4715,7 +4715,7 @@
         <v>32</v>
       </c>
       <c r="AF22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG22" t="n">
         <v>14.5</v>
@@ -4727,7 +4727,7 @@
         <v>34</v>
       </c>
       <c r="AJ22" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AK22" t="n">
         <v>24</v>
@@ -4745,7 +4745,7 @@
         <v>17.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AQ22" t="n">
         <v>16</v>
@@ -4754,7 +4754,7 @@
         <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT22" t="n">
         <v>13.5</v>
@@ -4769,7 +4769,7 @@
         <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AY22" t="n">
         <v>9.4</v>
@@ -4778,10 +4778,10 @@
         <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC22" t="n">
         <v>15.5</v>
@@ -4790,7 +4790,7 @@
         <v>19</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BF22" t="n">
         <v>7.4</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -4867,10 +4867,10 @@
         <v>1.62</v>
       </c>
       <c r="R23" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S23" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
         <v>1.6</v>
@@ -4885,7 +4885,7 @@
         <v>1.97</v>
       </c>
       <c r="X23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y23" t="n">
         <v>20</v>
@@ -4894,22 +4894,22 @@
         <v>34</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB23" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD23" t="n">
         <v>17</v>
       </c>
       <c r="AE23" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AF23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG23" t="n">
         <v>11.5</v>
@@ -4918,22 +4918,22 @@
         <v>17</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK23" t="n">
         <v>20</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO23" t="n">
         <v>230</v>
@@ -4945,10 +4945,10 @@
         <v>14.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AT23" t="n">
         <v>9.6</v>
@@ -4960,7 +4960,7 @@
         <v>12.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX23" t="n">
         <v>11</v>
@@ -4972,7 +4972,7 @@
         <v>12</v>
       </c>
       <c r="BA23" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BB23" t="n">
         <v>17.5</v>
@@ -4984,17 +4984,17 @@
         <v>21</v>
       </c>
       <c r="BE23" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BF23" t="n">
         <v>7.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -5031,16 +5031,16 @@
         <v>3.2</v>
       </c>
       <c r="H24" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J24" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L24" t="n">
         <v>1.47</v>
@@ -5049,16 +5049,16 @@
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O24" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P24" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R24" t="n">
         <v>1.29</v>
@@ -5067,13 +5067,13 @@
         <v>3.9</v>
       </c>
       <c r="T24" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="U24" t="n">
         <v>2.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W24" t="n">
         <v>1.45</v>
@@ -5085,7 +5085,7 @@
         <v>11.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA24" t="n">
         <v>48</v>
@@ -5097,7 +5097,7 @@
         <v>8.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE24" t="n">
         <v>38</v>
@@ -5121,7 +5121,7 @@
         <v>38</v>
       </c>
       <c r="AL24" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
@@ -5130,10 +5130,10 @@
         <v>42</v>
       </c>
       <c r="AO24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ24" t="n">
         <v>7.6</v>
@@ -5142,7 +5142,7 @@
         <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AT24" t="n">
         <v>8.4</v>
@@ -5154,7 +5154,7 @@
         <v>9.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AX24" t="n">
         <v>14.5</v>
@@ -5166,29 +5166,29 @@
         <v>13.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB24" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC24" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD24" t="n">
         <v>6.4</v>
       </c>
-      <c r="BD24" t="n">
-        <v>6</v>
-      </c>
       <c r="BE24" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF24" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H25" t="n">
         <v>1.52</v>
@@ -5234,7 +5234,7 @@
         <v>4.8</v>
       </c>
       <c r="K25" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L25" t="n">
         <v>1.23</v>
@@ -5249,16 +5249,16 @@
         <v>1.18</v>
       </c>
       <c r="P25" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q25" t="n">
         <v>1.53</v>
       </c>
       <c r="R25" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S25" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T25" t="n">
         <v>1.68</v>
@@ -5279,7 +5279,7 @@
         <v>14</v>
       </c>
       <c r="Z25" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AA25" t="n">
         <v>17.5</v>
@@ -5288,10 +5288,10 @@
         <v>34</v>
       </c>
       <c r="AC25" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE25" t="n">
         <v>17</v>
@@ -5327,7 +5327,7 @@
         <v>6.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AQ25" t="n">
         <v>9.199999999999999</v>
@@ -5339,22 +5339,22 @@
         <v>11.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="AU25" t="n">
         <v>6.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="AW25" t="n">
         <v>7.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AY25" t="n">
-        <v>18.5</v>
+        <v>6</v>
       </c>
       <c r="AZ25" t="n">
         <v>14.5</v>
@@ -5363,26 +5363,26 @@
         <v>20</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG25" t="n">
         <v>5</v>
       </c>
-      <c r="BF25" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -5422,10 +5422,10 @@
         <v>3.5</v>
       </c>
       <c r="I26" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K26" t="n">
         <v>4.1</v>
@@ -5443,7 +5443,7 @@
         <v>1.23</v>
       </c>
       <c r="P26" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q26" t="n">
         <v>1.6</v>
@@ -5476,7 +5476,7 @@
         <v>34</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB26" t="n">
         <v>15.5</v>
@@ -5512,7 +5512,7 @@
         <v>36</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
         <v>14.5</v>
@@ -5527,25 +5527,25 @@
         <v>15</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT26" t="n">
         <v>11</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AV26" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.6</v>
+        <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AY26" t="n">
         <v>9.800000000000001</v>
@@ -5554,16 +5554,16 @@
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB26" t="n">
         <v>19.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE26" t="n">
         <v>4.3</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -5607,19 +5607,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="G27" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J27" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K27" t="n">
         <v>3.8</v>
@@ -5634,13 +5634,13 @@
         <v>4.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P27" t="n">
         <v>2.32</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R27" t="n">
         <v>1.5</v>
@@ -5649,40 +5649,40 @@
         <v>2.72</v>
       </c>
       <c r="T27" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U27" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W27" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X27" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y27" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB27" t="n">
         <v>15</v>
       </c>
       <c r="AC27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD27" t="n">
         <v>16.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF27" t="n">
         <v>16.5</v>
@@ -5691,40 +5691,40 @@
         <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.4</v>
+        <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.3</v>
+        <v>13.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT27" t="n">
         <v>11</v>
@@ -5736,10 +5736,10 @@
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX27" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="AY27" t="n">
         <v>10.5</v>
@@ -5748,16 +5748,16 @@
         <v>12.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BB27" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BE27" t="n">
         <v>50</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G28" t="n">
         <v>2.5</v>
       </c>
       <c r="H28" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I28" t="n">
         <v>3.2</v>
@@ -5831,22 +5831,22 @@
         <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
         <v>1.73</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S28" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T28" t="n">
         <v>1.63</v>
       </c>
       <c r="U28" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V28" t="n">
         <v>1.45</v>
@@ -5855,58 +5855,58 @@
         <v>1.66</v>
       </c>
       <c r="X28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y28" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA28" t="n">
         <v>60</v>
       </c>
       <c r="AB28" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC28" t="n">
         <v>10.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF28" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG28" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AK28" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL28" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN28" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP28" t="n">
         <v>16</v>
@@ -5918,7 +5918,7 @@
         <v>20</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AT28" t="n">
         <v>10.5</v>
@@ -5930,7 +5930,7 @@
         <v>11.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="AX28" t="n">
         <v>14.5</v>
@@ -5942,16 +5942,16 @@
         <v>13.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="BB28" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="BC28" t="n">
         <v>20</v>
       </c>
       <c r="BD28" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BE28" t="n">
         <v>50</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="G29" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="H29" t="n">
-        <v>2.54</v>
+        <v>3.6</v>
       </c>
       <c r="I29" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J29" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K29" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="L29" t="n">
         <v>1.31</v>
@@ -6022,13 +6022,13 @@
         <v>3.2</v>
       </c>
       <c r="O29" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="R29" t="n">
         <v>1.27</v>
@@ -6040,13 +6040,13 @@
         <v>1.82</v>
       </c>
       <c r="U29" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="V29" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W29" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6064,7 +6064,7 @@
         <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD29" t="n">
         <v>1000</v>
@@ -6079,16 +6079,16 @@
         <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI29" t="n">
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL29" t="n">
         <v>1000</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.02</v>
+        <v>1.95</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.02</v>
+        <v>1.77</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.02</v>
+        <v>1.95</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.02</v>
+        <v>2.08</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.02</v>
+        <v>1.95</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.02</v>
+        <v>1.87</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.02</v>
+        <v>1.95</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.02</v>
+        <v>1.99</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="G30" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="H30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J30" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="K30" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="L30" t="n">
         <v>1.24</v>
@@ -6219,37 +6219,37 @@
         <v>1.18</v>
       </c>
       <c r="P30" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="Q30" t="n">
         <v>1.53</v>
       </c>
       <c r="R30" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S30" t="n">
         <v>2.36</v>
       </c>
       <c r="T30" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U30" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V30" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W30" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="X30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
@@ -6261,13 +6261,13 @@
         <v>15.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF30" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG30" t="n">
         <v>11</v>
@@ -6276,83 +6276,83 @@
         <v>32</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>220</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW30" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AX30" t="n">
         <v>7.8</v>
       </c>
       <c r="AY30" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ30" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BA30" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BB30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE30" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BG30" t="n">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
         <v>2.92</v>
       </c>
       <c r="T31" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U31" t="n">
         <v>2.28</v>
@@ -6458,7 +6458,7 @@
         <v>15.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF31" t="n">
         <v>20</v>
@@ -6470,16 +6470,16 @@
         <v>18.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ31" t="n">
         <v>40</v>
       </c>
       <c r="AK31" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM31" t="n">
         <v>85</v>
@@ -6500,7 +6500,7 @@
         <v>17</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT31" t="n">
         <v>9.4</v>
@@ -6512,7 +6512,7 @@
         <v>10</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX31" t="n">
         <v>13</v>
@@ -6524,19 +6524,19 @@
         <v>12</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC31" t="n">
         <v>19</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF31" t="n">
         <v>13</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
         <v>1.68</v>
       </c>
       <c r="I32" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="J32" t="n">
         <v>3.8</v>
@@ -6610,7 +6610,7 @@
         <v>1.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="R32" t="n">
         <v>1.37</v>
@@ -6619,13 +6619,13 @@
         <v>3.25</v>
       </c>
       <c r="T32" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="U32" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V32" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="W32" t="n">
         <v>1.2</v>
@@ -6664,22 +6664,22 @@
         <v>25</v>
       </c>
       <c r="AI32" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AJ32" t="n">
         <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AO32" t="n">
         <v>11.5</v>
@@ -6709,7 +6709,7 @@
         <v>15.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AY32" t="n">
         <v>18</v>
@@ -6718,29 +6718,29 @@
         <v>17.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BB32" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE32" t="n">
         <v>5.9</v>
       </c>
-      <c r="BC32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BF32" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG32" t="n">
         <v>8.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -6792,10 +6792,10 @@
         <v>1.49</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="O33" t="n">
         <v>1.45</v>
@@ -6807,7 +6807,7 @@
         <v>2.28</v>
       </c>
       <c r="R33" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
         <v>4.5</v>
@@ -6816,7 +6816,7 @@
         <v>1.98</v>
       </c>
       <c r="U33" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V33" t="n">
         <v>1.4</v>
@@ -6825,16 +6825,16 @@
         <v>1.64</v>
       </c>
       <c r="X33" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z33" t="n">
         <v>23</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB33" t="n">
         <v>8.4</v>
@@ -6843,22 +6843,22 @@
         <v>8</v>
       </c>
       <c r="AD33" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF33" t="n">
         <v>15</v>
       </c>
       <c r="AG33" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH33" t="n">
         <v>23</v>
       </c>
       <c r="AI33" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ33" t="n">
         <v>38</v>
@@ -6870,16 +6870,16 @@
         <v>55</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN33" t="n">
         <v>30</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP33" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ33" t="n">
         <v>9</v>
@@ -6888,7 +6888,7 @@
         <v>18.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AT33" t="n">
         <v>6.8</v>
@@ -6900,22 +6900,22 @@
         <v>11</v>
       </c>
       <c r="AW33" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AX33" t="n">
         <v>10.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ33" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA33" t="n">
         <v>50</v>
       </c>
       <c r="BB33" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BC33" t="n">
         <v>25</v>
@@ -6924,17 +6924,17 @@
         <v>42</v>
       </c>
       <c r="BE33" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BF33" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -6968,13 +6968,13 @@
         <v>2.3</v>
       </c>
       <c r="G34" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H34" t="n">
         <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
         <v>3.5</v>
@@ -7016,7 +7016,7 @@
         <v>1.43</v>
       </c>
       <c r="W34" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X34" t="n">
         <v>17.5</v>
@@ -7082,7 +7082,7 @@
         <v>19</v>
       </c>
       <c r="AS34" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT34" t="n">
         <v>8.6</v>
@@ -7106,7 +7106,7 @@
         <v>13.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB34" t="n">
         <v>7.8</v>
@@ -7124,11 +7124,11 @@
         <v>14.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
         <v>2.9</v>
       </c>
       <c r="G35" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H35" t="n">
         <v>2.38</v>
@@ -7204,25 +7204,25 @@
         <v>1.43</v>
       </c>
       <c r="U35" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V35" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W35" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X35" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y35" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z35" t="n">
         <v>21</v>
       </c>
       <c r="AA35" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AB35" t="n">
         <v>23</v>
@@ -7231,7 +7231,7 @@
         <v>11</v>
       </c>
       <c r="AD35" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE35" t="n">
         <v>19.5</v>
@@ -7249,10 +7249,10 @@
         <v>25</v>
       </c>
       <c r="AJ35" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AK35" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL35" t="n">
         <v>26</v>
@@ -7261,22 +7261,22 @@
         <v>42</v>
       </c>
       <c r="AN35" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO35" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP35" t="n">
         <v>32</v>
       </c>
       <c r="AQ35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR35" t="n">
         <v>19.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT35" t="n">
         <v>22</v>
@@ -7318,11 +7318,11 @@
         <v>11.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -7362,13 +7362,13 @@
         <v>1.87</v>
       </c>
       <c r="I36" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K36" t="n">
         <v>3.8</v>
-      </c>
-      <c r="K36" t="n">
-        <v>3.85</v>
       </c>
       <c r="L36" t="n">
         <v>1.42</v>
@@ -7386,19 +7386,19 @@
         <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R36" t="n">
         <v>1.38</v>
       </c>
       <c r="S36" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T36" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U36" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V36" t="n">
         <v>2.12</v>
@@ -7419,7 +7419,7 @@
         <v>19.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC36" t="n">
         <v>8.6</v>
@@ -7434,7 +7434,7 @@
         <v>36</v>
       </c>
       <c r="AG36" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH36" t="n">
         <v>19.5</v>
@@ -7446,10 +7446,10 @@
         <v>110</v>
       </c>
       <c r="AK36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL36" t="n">
         <v>65</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>70</v>
       </c>
       <c r="AM36" t="n">
         <v>100</v>
@@ -7464,19 +7464,19 @@
         <v>13</v>
       </c>
       <c r="AQ36" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR36" t="n">
         <v>10</v>
       </c>
       <c r="AS36" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AT36" t="n">
         <v>15.5</v>
       </c>
       <c r="AU36" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV36" t="n">
         <v>9.6</v>
@@ -7506,7 +7506,7 @@
         <v>55</v>
       </c>
       <c r="BE36" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BF36" t="n">
         <v>70</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="G37" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H37" t="n">
         <v>3.15</v>
@@ -7559,10 +7559,10 @@
         <v>3.45</v>
       </c>
       <c r="J37" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L37" t="n">
         <v>1.45</v>
@@ -7595,22 +7595,22 @@
         <v>1.82</v>
       </c>
       <c r="V37" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W37" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="X37" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y37" t="n">
         <v>10.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA37" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB37" t="n">
         <v>8.199999999999999</v>
@@ -7619,13 +7619,13 @@
         <v>8.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE37" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF37" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AG37" t="n">
         <v>12.5</v>
@@ -7634,7 +7634,7 @@
         <v>23</v>
       </c>
       <c r="AI37" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AJ37" t="n">
         <v>55</v>
@@ -7643,7 +7643,7 @@
         <v>46</v>
       </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
@@ -7652,22 +7652,22 @@
         <v>50</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP37" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ37" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR37" t="n">
         <v>15</v>
       </c>
       <c r="AS37" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT37" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AU37" t="n">
         <v>6.2</v>
@@ -7679,7 +7679,7 @@
         <v>34</v>
       </c>
       <c r="AX37" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY37" t="n">
         <v>10</v>
@@ -7691,26 +7691,26 @@
         <v>48</v>
       </c>
       <c r="BB37" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BC37" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD37" t="n">
         <v>28</v>
       </c>
-      <c r="BD37" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE37" t="n">
-        <v>9.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BF37" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BG37" t="n">
         <v>42</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
         <v>3.7</v>
       </c>
       <c r="L38" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M38" t="n">
         <v>1.07</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -7935,34 +7935,34 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="G39" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I39" t="n">
         <v>5.7</v>
       </c>
       <c r="J39" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K39" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="L39" t="n">
         <v>1.44</v>
       </c>
       <c r="M39" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N39" t="n">
         <v>2.36</v>
       </c>
       <c r="O39" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P39" t="n">
         <v>1.53</v>
@@ -7986,7 +7986,7 @@
         <v>1.21</v>
       </c>
       <c r="W39" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8055,7 +8055,7 @@
         <v>3.7</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AU39" t="n">
         <v>2.74</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -775,34 +775,34 @@
         <v>5.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R2" t="n">
         <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
         <v>1.12</v>
@@ -814,7 +814,7 @@
         <v>21</v>
       </c>
       <c r="Y2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z2" t="n">
         <v>80</v>
@@ -823,7 +823,7 @@
         <v>280</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC2" t="n">
         <v>11.5</v>
@@ -835,10 +835,10 @@
         <v>130</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
         <v>24</v>
@@ -859,28 +859,28 @@
         <v>130</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
         <v>160</v>
       </c>
       <c r="AP2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AR2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV2" t="n">
         <v>28</v>
@@ -889,7 +889,7 @@
         <v>36</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY2" t="n">
         <v>9.199999999999999</v>
@@ -898,29 +898,29 @@
         <v>22</v>
       </c>
       <c r="BA2" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC2" t="n">
         <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE2" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="BF2" t="n">
         <v>5.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -1101,10 +1101,10 @@
         <v>7.6</v>
       </c>
       <c r="BD3" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE3" t="n">
         <v>8</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
         <v>7.8</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G4" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="H4" t="n">
         <v>3.15</v>
       </c>
       <c r="I4" t="n">
-        <v>240</v>
+        <v>24</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.2</v>
@@ -1169,13 +1169,13 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="Q4" t="n">
         <v>1.5</v>
@@ -1193,10 +1193,10 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X4" t="n">
         <v>65</v>
@@ -1244,61 +1244,61 @@
         <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="BF4" t="n">
         <v>1.93</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H5" t="n">
         <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
         <v>3.65</v>
@@ -1378,19 +1378,19 @@
         <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
         <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X5" t="n">
         <v>13.5</v>
@@ -1399,7 +1399,7 @@
         <v>16</v>
       </c>
       <c r="Z5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="n">
         <v>95</v>
@@ -1411,28 +1411,28 @@
         <v>9</v>
       </c>
       <c r="AD5" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE5" t="n">
         <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL5" t="n">
         <v>44</v>
@@ -1447,62 +1447,62 @@
         <v>70</v>
       </c>
       <c r="AP5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY5" t="n">
         <v>9.4</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR5" t="n">
+      <c r="AZ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC5" t="n">
         <v>20</v>
       </c>
-      <c r="AS5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC5" t="n">
+      <c r="BD5" t="n">
         <v>18.5</v>
       </c>
-      <c r="BD5" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BE5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BF5" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BG5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="G6" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.49</v>
@@ -1560,19 +1560,19 @@
         <v>2.78</v>
       </c>
       <c r="O6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R6" t="n">
         <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T6" t="n">
         <v>2</v>
@@ -1581,16 +1581,16 @@
         <v>1.78</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W6" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="X6" t="n">
         <v>11</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
         <v>85</v>
@@ -1599,13 +1599,13 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>230</v>
@@ -1614,7 +1614,7 @@
         <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>25</v>
@@ -1629,7 +1629,7 @@
         <v>27</v>
       </c>
       <c r="AL6" t="n">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
@@ -1641,28 +1641,28 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT6" t="n">
         <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX6" t="n">
         <v>9.4</v>
@@ -1671,10 +1671,10 @@
         <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.5</v>
+        <v>36</v>
       </c>
       <c r="BB6" t="n">
         <v>19.5</v>
@@ -1683,20 +1683,20 @@
         <v>20</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>1.93</v>
       </c>
       <c r="I7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J7" t="n">
         <v>3.6</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -1939,19 +1939,19 @@
         <v>2.98</v>
       </c>
       <c r="L8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M8" t="n">
         <v>1.16</v>
       </c>
       <c r="N8" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="P8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q8" t="n">
         <v>3</v>
@@ -1963,10 +1963,10 @@
         <v>6.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="V8" t="n">
         <v>1.35</v>
@@ -1978,7 +1978,7 @@
         <v>7.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -2029,19 +2029,19 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
@@ -2050,41 +2050,41 @@
         <v>3.75</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY8" t="n">
         <v>6.6</v>
       </c>
-      <c r="AY8" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="BB8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="BE8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.35</v>
+        <v>2.76</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -2115,31 +2115,31 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="I9" t="n">
         <v>1.72</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
         <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.28</v>
@@ -2166,7 +2166,7 @@
         <v>2.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2181,7 +2181,7 @@
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC9" t="n">
         <v>14</v>
@@ -2223,22 +2223,22 @@
         <v>29</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS9" t="n">
         <v>10.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AV9" t="n">
         <v>7.8</v>
@@ -2247,38 +2247,38 @@
         <v>12.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF9" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>7.4</v>
       </c>
       <c r="BG9" t="n">
         <v>6.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
         <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
         <v>1.39</v>
@@ -2342,13 +2342,13 @@
         <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="R10" t="n">
         <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
         <v>1.84</v>
@@ -2423,10 +2423,10 @@
         <v>8</v>
       </c>
       <c r="AR10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT10" t="n">
         <v>7.2</v>
@@ -2438,7 +2438,7 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
@@ -2447,32 +2447,32 @@
         <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA10" t="n">
         <v>3.15</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BE10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BF10" t="n">
         <v>3.2</v>
       </c>
-      <c r="BF10" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BG10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="J11" t="n">
         <v>3.6</v>
@@ -2521,7 +2521,7 @@
         <v>4.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
@@ -2551,16 +2551,16 @@
         <v>1.94</v>
       </c>
       <c r="V11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="W11" t="n">
         <v>1.2</v>
       </c>
       <c r="X11" t="n">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
         <v>12</v>
@@ -2569,28 +2569,28 @@
         <v>50</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
         <v>500</v>
       </c>
-      <c r="AG11" t="n">
-        <v>42</v>
-      </c>
       <c r="AH11" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AI11" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
         <v>1000</v>
@@ -2620,10 +2620,10 @@
         <v>5.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AU11" t="n">
         <v>5.1</v>
@@ -2632,41 +2632,41 @@
         <v>7</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>2.16</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I12" t="n">
         <v>3.95</v>
@@ -2766,7 +2766,7 @@
         <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
         <v>18</v>
@@ -2814,19 +2814,19 @@
         <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
         <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -2838,7 +2838,7 @@
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB12" t="n">
         <v>19</v>
@@ -2847,20 +2847,20 @@
         <v>15.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.2</v>
+        <v>25</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
         <v>4.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AW13" t="n">
         <v>5.6</v>
@@ -3047,14 +3047,14 @@
         <v>5.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BG13" t="n">
         <v>5.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -3097,19 +3097,19 @@
         <v>15</v>
       </c>
       <c r="J14" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="K14" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.12</v>
@@ -3136,7 +3136,7 @@
         <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3193,7 +3193,7 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AQ14" t="n">
         <v>4.2</v>
@@ -3205,10 +3205,10 @@
         <v>4.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AV14" t="n">
         <v>4.2</v>
@@ -3220,35 +3220,35 @@
         <v>7.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BA14" t="n">
         <v>4.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
         <v>22</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT15" t="n">
         <v>9.800000000000001</v>
@@ -3432,7 +3432,7 @@
         <v>16</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF15" t="n">
         <v>11</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>1.83</v>
       </c>
       <c r="H16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I16" t="n">
         <v>5.6</v>
@@ -3575,7 +3575,7 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
         <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L18" t="n">
         <v>1.31</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G19" t="n">
         <v>2.56</v>
@@ -4067,13 +4067,13 @@
         <v>3.45</v>
       </c>
       <c r="J19" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K19" t="n">
         <v>3.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
@@ -4085,7 +4085,7 @@
         <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
         <v>2.18</v>
@@ -4145,7 +4145,7 @@
         <v>500</v>
       </c>
       <c r="AJ19" t="n">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="AK19" t="n">
         <v>90</v>
@@ -4175,10 +4175,10 @@
         <v>6</v>
       </c>
       <c r="AT19" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AV19" t="n">
         <v>8.4</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
         <v>2.9</v>
       </c>
       <c r="H20" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J20" t="n">
         <v>3.75</v>
@@ -4276,13 +4276,13 @@
         <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P20" t="n">
         <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R20" t="n">
         <v>1.46</v>
@@ -4330,7 +4330,7 @@
         <v>21</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
         <v>16.5</v>
@@ -4393,7 +4393,7 @@
         <v>22</v>
       </c>
       <c r="BB20" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BC20" t="n">
         <v>24</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -4446,40 +4446,40 @@
         <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="H21" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="I21" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K21" t="n">
         <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M21" t="n">
         <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O21" t="n">
         <v>1.21</v>
       </c>
       <c r="P21" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R21" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
         <v>2.6</v>
@@ -4488,19 +4488,19 @@
         <v>1.59</v>
       </c>
       <c r="U21" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V21" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W21" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="X21" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="Y21" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z21" t="n">
         <v>1000</v>
@@ -4515,7 +4515,7 @@
         <v>12.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
@@ -4524,7 +4524,7 @@
         <v>34</v>
       </c>
       <c r="AG21" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="n">
         <v>25</v>
@@ -4533,7 +4533,7 @@
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AK21" t="n">
         <v>65</v>
@@ -4557,10 +4557,10 @@
         <v>9</v>
       </c>
       <c r="AR21" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT21" t="n">
         <v>9.6</v>
@@ -4572,7 +4572,7 @@
         <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX21" t="n">
         <v>7.6</v>
@@ -4584,7 +4584,7 @@
         <v>9</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BB21" t="n">
         <v>20</v>
@@ -4596,17 +4596,17 @@
         <v>20</v>
       </c>
       <c r="BE21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG21" t="n">
         <v>8.4</v>
       </c>
-      <c r="BF21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G22" t="n">
         <v>2.34</v>
@@ -4646,7 +4646,7 @@
         <v>2.92</v>
       </c>
       <c r="I22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
         <v>4.1</v>
@@ -4670,10 +4670,10 @@
         <v>2.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R22" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="S22" t="n">
         <v>2.08</v>
@@ -4715,7 +4715,7 @@
         <v>32</v>
       </c>
       <c r="AF22" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AG22" t="n">
         <v>14.5</v>
@@ -4745,7 +4745,7 @@
         <v>17.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ22" t="n">
         <v>16</v>
@@ -4754,7 +4754,7 @@
         <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT22" t="n">
         <v>13.5</v>
@@ -4763,7 +4763,7 @@
         <v>8.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW22" t="n">
         <v>21</v>
@@ -4772,13 +4772,13 @@
         <v>10.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
         <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB22" t="n">
         <v>14.5</v>
@@ -4790,7 +4790,7 @@
         <v>19</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF22" t="n">
         <v>7.4</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
         <v>3.85</v>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J23" t="n">
         <v>3.85</v>
@@ -4933,7 +4933,7 @@
         <v>500</v>
       </c>
       <c r="AN23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO23" t="n">
         <v>230</v>
@@ -4948,7 +4948,7 @@
         <v>14.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT23" t="n">
         <v>9.6</v>
@@ -4960,19 +4960,19 @@
         <v>12.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX23" t="n">
         <v>11</v>
       </c>
       <c r="AY23" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
         <v>12</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB23" t="n">
         <v>17.5</v>
@@ -4984,17 +4984,17 @@
         <v>21</v>
       </c>
       <c r="BE23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF23" t="n">
         <v>7.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -5025,25 +5025,25 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="G24" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="H24" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="I24" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K24" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
@@ -5061,22 +5061,22 @@
         <v>2.12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="T24" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U24" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V24" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="W24" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="X24" t="n">
         <v>13.5</v>
@@ -5085,110 +5085,110 @@
         <v>11.5</v>
       </c>
       <c r="Z24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH24" t="n">
         <v>17.5</v>
       </c>
-      <c r="AA24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC24" t="n">
+      <c r="AI24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>340</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>7.6</v>
       </c>
       <c r="AR24" t="n">
         <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW24" t="n">
         <v>14.5</v>
       </c>
       <c r="AX24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>14.5</v>
       </c>
-      <c r="AY24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BA24" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BB24" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="G25" t="n">
         <v>6.8</v>
       </c>
       <c r="H25" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I25" t="n">
         <v>1.58</v>
@@ -5234,10 +5234,10 @@
         <v>4.8</v>
       </c>
       <c r="K25" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
@@ -5252,7 +5252,7 @@
         <v>2.68</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R25" t="n">
         <v>1.68</v>
@@ -5264,7 +5264,7 @@
         <v>1.68</v>
       </c>
       <c r="U25" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V25" t="n">
         <v>2.72</v>
@@ -5291,7 +5291,7 @@
         <v>12.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE25" t="n">
         <v>17</v>
@@ -5327,31 +5327,31 @@
         <v>6.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="AQ25" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR25" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AT25" t="n">
         <v>14.5</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AW25" t="n">
         <v>7.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY25" t="n">
         <v>6</v>
@@ -5363,16 +5363,16 @@
         <v>20</v>
       </c>
       <c r="BB25" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF25" t="n">
         <v>8.4</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         <v>3.5</v>
       </c>
       <c r="I26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J26" t="n">
         <v>3.7</v>
@@ -5443,25 +5443,25 @@
         <v>1.23</v>
       </c>
       <c r="P26" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q26" t="n">
         <v>1.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S26" t="n">
         <v>2.7</v>
       </c>
       <c r="T26" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U26" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V26" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W26" t="n">
         <v>1.84</v>
@@ -5476,7 +5476,7 @@
         <v>34</v>
       </c>
       <c r="AA26" t="n">
-        <v>160</v>
+        <v>440</v>
       </c>
       <c r="AB26" t="n">
         <v>15.5</v>
@@ -5530,7 +5530,7 @@
         <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT26" t="n">
         <v>11</v>
@@ -5563,20 +5563,20 @@
         <v>10.5</v>
       </c>
       <c r="BD26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE26" t="n">
         <v>4.4</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>4.3</v>
       </c>
       <c r="BF26" t="n">
         <v>10.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -5607,19 +5607,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G27" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H27" t="n">
         <v>3.25</v>
       </c>
       <c r="I27" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K27" t="n">
         <v>3.8</v>
@@ -5631,7 +5631,7 @@
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O27" t="n">
         <v>1.23</v>
@@ -5640,25 +5640,25 @@
         <v>2.32</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S27" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T27" t="n">
         <v>1.62</v>
       </c>
       <c r="U27" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V27" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X27" t="n">
         <v>19</v>
@@ -5718,7 +5718,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AR27" t="n">
         <v>11.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -5998,19 +5998,19 @@
         <v>2.06</v>
       </c>
       <c r="G29" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H29" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>3.4</v>
       </c>
       <c r="K29" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L29" t="n">
         <v>1.31</v>
@@ -6025,10 +6025,10 @@
         <v>1.26</v>
       </c>
       <c r="P29" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="R29" t="n">
         <v>1.27</v>
@@ -6043,10 +6043,10 @@
         <v>2.1</v>
       </c>
       <c r="V29" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6061,7 +6061,7 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC29" t="n">
         <v>950</v>
@@ -6103,37 +6103,37 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AS29" t="n">
         <v>2.1</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AY29" t="n">
         <v>1.87</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BA29" t="n">
         <v>2.1</v>
@@ -6142,23 +6142,23 @@
         <v>2.06</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BD29" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BE29" t="n">
         <v>2.1</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="BG29" t="n">
         <v>2.1</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH30" t="n">
         <v>32</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
         <v>2.56</v>
       </c>
       <c r="H31" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I31" t="n">
         <v>3.1</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -6583,16 +6583,16 @@
         <v>6.2</v>
       </c>
       <c r="H32" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I32" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="J32" t="n">
         <v>3.8</v>
       </c>
       <c r="K32" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L32" t="n">
         <v>1.33</v>
@@ -6625,13 +6625,13 @@
         <v>1.94</v>
       </c>
       <c r="V32" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="W32" t="n">
         <v>1.2</v>
       </c>
       <c r="X32" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y32" t="n">
         <v>8.800000000000001</v>
@@ -6643,7 +6643,7 @@
         <v>21</v>
       </c>
       <c r="AB32" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC32" t="n">
         <v>11</v>
@@ -6655,13 +6655,13 @@
         <v>19.5</v>
       </c>
       <c r="AF32" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AG32" t="n">
         <v>26</v>
       </c>
       <c r="AH32" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI32" t="n">
         <v>85</v>
@@ -6709,7 +6709,7 @@
         <v>15.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AY32" t="n">
         <v>18</v>
@@ -6718,29 +6718,29 @@
         <v>17.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC32" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF32" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BG32" t="n">
         <v>8.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -6795,28 +6795,28 @@
         <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O33" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P33" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R33" t="n">
         <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T33" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U33" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V33" t="n">
         <v>1.4</v>
@@ -6825,7 +6825,7 @@
         <v>1.64</v>
       </c>
       <c r="X33" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y33" t="n">
         <v>11</v>
@@ -6837,16 +6837,16 @@
         <v>160</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC33" t="n">
         <v>8</v>
       </c>
       <c r="AD33" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF33" t="n">
         <v>15</v>
@@ -6855,10 +6855,10 @@
         <v>13</v>
       </c>
       <c r="AH33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI33" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ33" t="n">
         <v>38</v>
@@ -6888,7 +6888,7 @@
         <v>18.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT33" t="n">
         <v>6.8</v>
@@ -6900,7 +6900,7 @@
         <v>11</v>
       </c>
       <c r="AW33" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX33" t="n">
         <v>10.5</v>
@@ -6912,7 +6912,7 @@
         <v>18</v>
       </c>
       <c r="BA33" t="n">
-        <v>50</v>
+        <v>8.6</v>
       </c>
       <c r="BB33" t="n">
         <v>16</v>
@@ -6921,20 +6921,20 @@
         <v>25</v>
       </c>
       <c r="BD33" t="n">
-        <v>42</v>
+        <v>8.4</v>
       </c>
       <c r="BE33" t="n">
         <v>29</v>
       </c>
       <c r="BF33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG33" t="n">
         <v>8.4</v>
       </c>
-      <c r="BG33" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
         <v>2.5</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I34" t="n">
         <v>3.3</v>
@@ -7022,7 +7022,7 @@
         <v>17.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z34" t="n">
         <v>24</v>
@@ -7064,7 +7064,7 @@
         <v>36</v>
       </c>
       <c r="AM34" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN34" t="n">
         <v>17.5</v>
@@ -7106,10 +7106,10 @@
         <v>13.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB34" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC34" t="n">
         <v>20</v>
@@ -7124,11 +7124,11 @@
         <v>14.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -7162,10 +7162,10 @@
         <v>2.9</v>
       </c>
       <c r="G35" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H35" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I35" t="n">
         <v>2.4</v>
@@ -7177,40 +7177,40 @@
         <v>4.3</v>
       </c>
       <c r="L35" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M35" t="n">
         <v>1.03</v>
       </c>
       <c r="N35" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O35" t="n">
         <v>1.13</v>
       </c>
       <c r="P35" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R35" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S35" t="n">
         <v>2.06</v>
       </c>
       <c r="T35" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="U35" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V35" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W35" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X35" t="n">
         <v>34</v>
@@ -7225,7 +7225,7 @@
         <v>32</v>
       </c>
       <c r="AB35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC35" t="n">
         <v>11</v>
@@ -7243,7 +7243,7 @@
         <v>14</v>
       </c>
       <c r="AH35" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AI35" t="n">
         <v>25</v>
@@ -7252,7 +7252,7 @@
         <v>48</v>
       </c>
       <c r="AK35" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL35" t="n">
         <v>26</v>
@@ -7276,7 +7276,7 @@
         <v>19.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT35" t="n">
         <v>22</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -7365,10 +7365,10 @@
         <v>1.88</v>
       </c>
       <c r="J36" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K36" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L36" t="n">
         <v>1.42</v>
@@ -7386,7 +7386,7 @@
         <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R36" t="n">
         <v>1.38</v>
@@ -7425,7 +7425,7 @@
         <v>8.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE36" t="n">
         <v>19</v>
@@ -7434,7 +7434,7 @@
         <v>36</v>
       </c>
       <c r="AG36" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH36" t="n">
         <v>19.5</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -7565,19 +7565,19 @@
         <v>3.25</v>
       </c>
       <c r="L37" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="M37" t="n">
         <v>1.11</v>
       </c>
       <c r="N37" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O37" t="n">
         <v>1.51</v>
       </c>
       <c r="P37" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="Q37" t="n">
         <v>2.52</v>
@@ -7586,7 +7586,7 @@
         <v>1.2</v>
       </c>
       <c r="S37" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T37" t="n">
         <v>2</v>
@@ -7595,7 +7595,7 @@
         <v>1.82</v>
       </c>
       <c r="V37" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W37" t="n">
         <v>1.57</v>
@@ -7619,7 +7619,7 @@
         <v>8.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE37" t="n">
         <v>55</v>
@@ -7664,7 +7664,7 @@
         <v>15</v>
       </c>
       <c r="AS37" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT37" t="n">
         <v>7.2</v>
@@ -7703,14 +7703,14 @@
         <v>38</v>
       </c>
       <c r="BF37" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG37" t="n">
         <v>42</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -7741,22 +7741,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G38" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H38" t="n">
         <v>2.4</v>
       </c>
       <c r="I38" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J38" t="n">
         <v>3.4</v>
       </c>
       <c r="K38" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L38" t="n">
         <v>1.41</v>
@@ -7768,7 +7768,7 @@
         <v>3.7</v>
       </c>
       <c r="O38" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P38" t="n">
         <v>1.93</v>
@@ -7792,7 +7792,7 @@
         <v>1.64</v>
       </c>
       <c r="W38" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X38" t="n">
         <v>14.5</v>
@@ -7801,13 +7801,13 @@
         <v>11</v>
       </c>
       <c r="Z38" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA38" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB38" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC38" t="n">
         <v>8</v>
@@ -7825,7 +7825,7 @@
         <v>14</v>
       </c>
       <c r="AH38" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI38" t="n">
         <v>1000</v>
@@ -7846,7 +7846,7 @@
         <v>36</v>
       </c>
       <c r="AO38" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AP38" t="n">
         <v>12.5</v>
@@ -7858,7 +7858,7 @@
         <v>14</v>
       </c>
       <c r="AS38" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT38" t="n">
         <v>11</v>
@@ -7873,7 +7873,7 @@
         <v>19</v>
       </c>
       <c r="AX38" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY38" t="n">
         <v>12</v>
@@ -7882,29 +7882,29 @@
         <v>15</v>
       </c>
       <c r="BA38" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BB38" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC38" t="n">
         <v>30</v>
       </c>
       <c r="BD38" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BE38" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF38" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BG38" t="n">
         <v>18</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -7938,16 +7938,16 @@
         <v>1.81</v>
       </c>
       <c r="G39" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H39" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J39" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
@@ -7959,19 +7959,19 @@
         <v>1.06</v>
       </c>
       <c r="N39" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O39" t="n">
         <v>1.07</v>
       </c>
       <c r="P39" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q39" t="n">
         <v>2.08</v>
       </c>
       <c r="R39" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S39" t="n">
         <v>3.05</v>
@@ -7986,7 +7986,7 @@
         <v>1.21</v>
       </c>
       <c r="W39" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8043,62 +8043,62 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="AQ39" t="n">
         <v>3.95</v>
       </c>
       <c r="AR39" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY39" t="n">
         <v>3.7</v>
       </c>
-      <c r="AT39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>3</v>
-      </c>
       <c r="AZ39" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="BA39" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="BB39" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="BC39" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="BF39" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="BG39" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="G2" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="H2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I2" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K2" t="n">
         <v>5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.33</v>
@@ -781,146 +781,146 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W2" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
         <v>32</v>
       </c>
       <c r="Z2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AA2" t="n">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE2" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK2" t="n">
         <v>14.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AO2" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AP2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AR2" t="n">
         <v>60</v>
       </c>
       <c r="AS2" t="n">
-        <v>36</v>
+        <v>18.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AW2" t="n">
         <v>36</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BB2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BE2" t="n">
         <v>110</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -951,64 +951,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G3" t="n">
         <v>7.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="I3" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="O3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="U3" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="V3" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="W3" t="n">
         <v>1.16</v>
       </c>
       <c r="X3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Z3" t="n">
         <v>9.800000000000001</v>
@@ -1023,22 +1023,22 @@
         <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AF3" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AG3" t="n">
         <v>55</v>
       </c>
       <c r="AH3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
@@ -1056,25 +1056,25 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
         <v>9.199999999999999</v>
@@ -1083,13 +1083,13 @@
         <v>12</v>
       </c>
       <c r="AX3" t="n">
-        <v>34</v>
+        <v>14.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BA3" t="n">
         <v>28</v>
@@ -1101,20 +1101,20 @@
         <v>7.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>29</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF3" t="n">
         <v>7.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1148,10 @@
         <v>1.36</v>
       </c>
       <c r="G4" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="H4" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="I4" t="n">
         <v>24</v>
@@ -1160,34 +1160,34 @@
         <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="L4" t="n">
         <v>1.2</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>1.62</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="P4" t="n">
-        <v>1.61</v>
+        <v>2.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
         <v>1.11</v>
@@ -1196,7 +1196,7 @@
         <v>1.14</v>
       </c>
       <c r="W4" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="X4" t="n">
         <v>65</v>
@@ -1253,52 +1253,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.32</v>
+        <v>4.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.32</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU4" t="n">
         <v>1.33</v>
       </c>
-      <c r="AT4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AV4" t="n">
-        <v>1.32</v>
+        <v>4.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.33</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.29</v>
+        <v>4.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.28</v>
+        <v>4.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.33</v>
+        <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.31</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BF4" t="n">
         <v>1.93</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -1354,49 +1354,49 @@
         <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
         <v>2.04</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="T5" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V5" t="n">
         <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Z5" t="n">
         <v>32</v>
@@ -1408,67 +1408,67 @@
         <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE5" t="n">
         <v>55</v>
       </c>
       <c r="AF5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH5" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>22</v>
       </c>
       <c r="AI5" t="n">
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AK5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>580</v>
+        <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO5" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR5" t="n">
         <v>23</v>
       </c>
       <c r="AS5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AX5" t="n">
         <v>11.5</v>
@@ -1477,32 +1477,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.8</v>
+        <v>27</v>
       </c>
       <c r="BB5" t="n">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="BC5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD5" t="n">
         <v>20</v>
       </c>
-      <c r="BD5" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BE5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BF5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -1533,49 +1533,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="G6" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O6" t="n">
         <v>1.49</v>
       </c>
-      <c r="M6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.45</v>
-      </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
         <v>1.78</v>
@@ -1587,10 +1587,10 @@
         <v>1.89</v>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
         <v>85</v>
@@ -1599,34 +1599,34 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AE6" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
         <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
         <v>450</v>
@@ -1635,25 +1635,25 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR6" t="n">
         <v>23</v>
       </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AS6" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU6" t="n">
         <v>6.4</v>
@@ -1662,41 +1662,41 @@
         <v>16</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY6" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BC6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BF6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BG6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>2.06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
         <v>4.2</v>
@@ -1751,7 +1751,7 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.27</v>
@@ -1760,137 +1760,137 @@
         <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V7" t="n">
         <v>1.94</v>
       </c>
       <c r="W7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH7" t="n">
         <v>18</v>
       </c>
-      <c r="AA7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="AI7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP7" t="n">
         <v>15</v>
       </c>
-      <c r="AE7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2.66</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AX7" t="n">
         <v>14.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BA7" t="n">
         <v>16</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.94</v>
+        <v>8.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.84</v>
+        <v>8</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.92</v>
+        <v>8.6</v>
       </c>
       <c r="BF7" t="n">
         <v>8.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>3.6</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J8" t="n">
         <v>2.8</v>
@@ -1939,19 +1939,19 @@
         <v>2.98</v>
       </c>
       <c r="L8" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="M8" t="n">
         <v>1.16</v>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O8" t="n">
         <v>1.68</v>
       </c>
       <c r="P8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q8" t="n">
         <v>3</v>
@@ -1960,13 +1960,13 @@
         <v>1.15</v>
       </c>
       <c r="S8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T8" t="n">
         <v>2.3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="V8" t="n">
         <v>1.35</v>
@@ -1990,7 +1990,7 @@
         <v>13</v>
       </c>
       <c r="AC8" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -2011,7 +2011,7 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AT8" t="n">
         <v>4.8</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5.7</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY8" t="n">
         <v>6.8</v>
       </c>
-      <c r="AY8" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>8.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.72</v>
+        <v>5.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF8" t="n">
-        <v>10.5</v>
+        <v>2.48</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -2115,40 +2115,40 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G9" t="n">
         <v>6.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="I9" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R9" t="n">
         <v>1.45</v>
@@ -2157,31 +2157,31 @@
         <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="W9" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y9" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="Z9" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AC9" t="n">
         <v>14</v>
@@ -2190,19 +2190,19 @@
         <v>36</v>
       </c>
       <c r="AE9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ9" t="n">
         <v>1000</v>
@@ -2220,65 +2220,65 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS9" t="n">
         <v>4.5</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AT9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV9" t="n">
         <v>5.2</v>
       </c>
-      <c r="AS9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AW9" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="AX9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>6.6</v>
       </c>
-      <c r="AY9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BA9" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="BB9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE9" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BF9" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="H10" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I10" t="n">
         <v>3.35</v>
@@ -2324,7 +2324,7 @@
         <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.39</v>
@@ -2333,7 +2333,7 @@
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
         <v>1.39</v>
@@ -2342,10 +2342,10 @@
         <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
         <v>3.9</v>
@@ -2375,10 +2375,10 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
@@ -2387,7 +2387,7 @@
         <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
         <v>970</v>
@@ -2411,68 +2411,68 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AY10" t="n">
         <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.5</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.4</v>
+        <v>32</v>
       </c>
       <c r="BE10" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="G11" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="H11" t="n">
         <v>1.73</v>
       </c>
       <c r="I11" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
         <v>4.1</v>
@@ -2548,28 +2548,28 @@
         <v>1.91</v>
       </c>
       <c r="U11" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V11" t="n">
         <v>2.16</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X11" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
         <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AC11" t="n">
         <v>14</v>
@@ -2611,62 +2611,62 @@
         <v>55</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ11" t="n">
         <v>4.9</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AV11" t="n">
         <v>7</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.4</v>
+        <v>3.65</v>
       </c>
       <c r="BC11" t="n">
         <v>7</v>
       </c>
       <c r="BD11" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BF11" t="n">
         <v>3.1</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H12" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I12" t="n">
         <v>3.95</v>
@@ -2715,43 +2715,43 @@
         <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R12" t="n">
         <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U12" t="n">
         <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y12" t="n">
         <v>17.5</v>
@@ -2763,10 +2763,10 @@
         <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
         <v>18</v>
@@ -2775,19 +2775,19 @@
         <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
         <v>150</v>
       </c>
       <c r="AJ12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2796,71 +2796,71 @@
         <v>80</v>
       </c>
       <c r="AM12" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN12" t="n">
         <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>36</v>
+        <v>220</v>
       </c>
       <c r="AP12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BB12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BD12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="BE12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG12" t="n">
         <v>7.2</v>
       </c>
-      <c r="BF12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>25</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>1.76</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="I13" t="n">
         <v>4.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
@@ -2942,7 +2942,7 @@
         <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X13" t="n">
         <v>29</v>
@@ -2993,7 +2993,7 @@
         <v>70</v>
       </c>
       <c r="AN13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO13" t="n">
         <v>34</v>
@@ -3002,10 +3002,10 @@
         <v>10</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS13" t="n">
         <v>6</v>
@@ -3014,47 +3014,47 @@
         <v>4.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY13" t="n">
         <v>4.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF13" t="n">
         <v>3.85</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="G14" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="H14" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>15</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3115,28 +3115,28 @@
         <v>1.12</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
         <v>1.31</v>
       </c>
       <c r="R14" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W14" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3187,13 +3187,13 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="AQ14" t="n">
         <v>4.2</v>
@@ -3208,7 +3208,7 @@
         <v>4.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV14" t="n">
         <v>4.2</v>
@@ -3220,7 +3220,7 @@
         <v>7.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AZ14" t="n">
         <v>2.84</v>
@@ -3229,26 +3229,26 @@
         <v>4.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC14" t="n">
         <v>5.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="BF14" t="n">
         <v>3.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G15" t="n">
         <v>2.28</v>
@@ -3288,7 +3288,7 @@
         <v>3.4</v>
       </c>
       <c r="I15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J15" t="n">
         <v>3.7</v>
@@ -3297,13 +3297,13 @@
         <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.28</v>
@@ -3312,79 +3312,79 @@
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R15" t="n">
         <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U15" t="n">
         <v>2.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
         <v>1.78</v>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA15" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AB15" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG15" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI15" t="n">
         <v>60</v>
       </c>
       <c r="AJ15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM15" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
         <v>17.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP15" t="n">
         <v>14.5</v>
@@ -3396,53 +3396,53 @@
         <v>22</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.2</v>
+        <v>34</v>
       </c>
       <c r="AT15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.5</v>
+        <v>23</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.4</v>
+        <v>29</v>
       </c>
       <c r="BB15" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="BC15" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.4</v>
+        <v>40</v>
       </c>
       <c r="BF15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O16" t="n">
         <v>1.25</v>
@@ -3509,7 +3509,7 @@
         <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
         <v>2.84</v>
@@ -3542,7 +3542,7 @@
         <v>10.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3557,7 +3557,7 @@
         <v>10</v>
       </c>
       <c r="AH16" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
@@ -3566,7 +3566,7 @@
         <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="AL16" t="n">
         <v>1000</v>
@@ -3575,7 +3575,7 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
@@ -3584,13 +3584,13 @@
         <v>14</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
         <v>7.8</v>
@@ -3599,10 +3599,10 @@
         <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX16" t="n">
         <v>9.800000000000001</v>
@@ -3614,29 +3614,29 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB16" t="n">
         <v>14</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF16" t="n">
         <v>7.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G17" t="n">
         <v>1.61</v>
@@ -3778,7 +3778,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR17" t="n">
         <v>8.199999999999999</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
         <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
         <v>1.39</v>
@@ -3906,7 +3906,7 @@
         <v>1.71</v>
       </c>
       <c r="U18" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V18" t="n">
         <v>1.36</v>
@@ -3978,7 +3978,7 @@
         <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
         <v>9</v>
@@ -3990,7 +3990,7 @@
         <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX18" t="n">
         <v>10.5</v>
@@ -4002,7 +4002,7 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB18" t="n">
         <v>13</v>
@@ -4011,7 +4011,7 @@
         <v>11.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE18" t="n">
         <v>28</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
         <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X19" t="n">
         <v>19.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="G20" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H20" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I20" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="J20" t="n">
         <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -4279,10 +4279,10 @@
         <v>1.26</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R20" t="n">
         <v>1.46</v>
@@ -4291,31 +4291,31 @@
         <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U20" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V20" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W20" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X20" t="n">
         <v>18.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z20" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC20" t="n">
         <v>8.6</v>
@@ -4324,13 +4324,13 @@
         <v>12</v>
       </c>
       <c r="AE20" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AF20" t="n">
         <v>21</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
         <v>16.5</v>
@@ -4339,22 +4339,22 @@
         <v>80</v>
       </c>
       <c r="AJ20" t="n">
-        <v>280</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AL20" t="n">
         <v>85</v>
       </c>
       <c r="AM20" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AO20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>16</v>
@@ -4363,13 +4363,13 @@
         <v>11.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS20" t="n">
         <v>22</v>
       </c>
       <c r="AT20" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU20" t="n">
         <v>7.8</v>
@@ -4384,35 +4384,35 @@
         <v>17.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BA20" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD20" t="n">
         <v>22</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>23</v>
       </c>
       <c r="BE20" t="n">
         <v>55</v>
       </c>
       <c r="BF20" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
         <v>3.45</v>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J21" t="n">
         <v>3.8</v>
@@ -4473,7 +4473,7 @@
         <v>1.21</v>
       </c>
       <c r="P21" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q21" t="n">
         <v>1.63</v>
@@ -4515,7 +4515,7 @@
         <v>12.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
@@ -4560,7 +4560,7 @@
         <v>8.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AT21" t="n">
         <v>9.6</v>
@@ -4572,7 +4572,7 @@
         <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX21" t="n">
         <v>7.6</v>
@@ -4584,7 +4584,7 @@
         <v>9</v>
       </c>
       <c r="BA21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB21" t="n">
         <v>20</v>
@@ -4599,14 +4599,14 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG21" t="n">
         <v>8.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>2.34</v>
       </c>
       <c r="H22" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I22" t="n">
         <v>3.2</v>
@@ -4673,10 +4673,10 @@
         <v>1.46</v>
       </c>
       <c r="R22" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S22" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="T22" t="n">
         <v>1.47</v>
@@ -4691,7 +4691,7 @@
         <v>1.74</v>
       </c>
       <c r="X22" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="Y22" t="n">
         <v>25</v>
@@ -4730,7 +4730,7 @@
         <v>75</v>
       </c>
       <c r="AK22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="n">
         <v>29</v>
@@ -4745,7 +4745,7 @@
         <v>17.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>16</v>
@@ -4754,7 +4754,7 @@
         <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT22" t="n">
         <v>13.5</v>
@@ -4763,7 +4763,7 @@
         <v>8.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW22" t="n">
         <v>21</v>
@@ -4778,7 +4778,7 @@
         <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB22" t="n">
         <v>14.5</v>
@@ -4790,7 +4790,7 @@
         <v>19</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF22" t="n">
         <v>7.4</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
         <v>4.3</v>
       </c>
       <c r="J23" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K23" t="n">
         <v>4.4</v>
@@ -4855,7 +4855,7 @@
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="O23" t="n">
         <v>1.21</v>
@@ -4864,10 +4864,10 @@
         <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R23" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S23" t="n">
         <v>2.56</v>
@@ -4936,7 +4936,7 @@
         <v>10.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
         <v>16.5</v>
@@ -4948,7 +4948,7 @@
         <v>14.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT23" t="n">
         <v>9.6</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -5034,10 +5034,10 @@
         <v>2.44</v>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J24" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K24" t="n">
         <v>3.3</v>
@@ -5049,22 +5049,22 @@
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P24" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R24" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="T24" t="n">
         <v>1.81</v>
@@ -5097,7 +5097,7 @@
         <v>7.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -5106,22 +5106,22 @@
         <v>25</v>
       </c>
       <c r="AG24" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AH24" t="n">
         <v>17.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>44</v>
+        <v>290</v>
       </c>
       <c r="AJ24" t="n">
-        <v>340</v>
+        <v>900</v>
       </c>
       <c r="AK24" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
         <v>580</v>
@@ -5130,7 +5130,7 @@
         <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP24" t="n">
         <v>10.5</v>
@@ -5142,7 +5142,7 @@
         <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT24" t="n">
         <v>11</v>
@@ -5163,32 +5163,32 @@
         <v>14</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD24" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG24" t="n">
         <v>21</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G25" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H25" t="n">
         <v>1.53</v>
@@ -5258,13 +5258,13 @@
         <v>1.68</v>
       </c>
       <c r="S25" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T25" t="n">
         <v>1.68</v>
       </c>
       <c r="U25" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V25" t="n">
         <v>2.72</v>
@@ -5273,40 +5273,40 @@
         <v>1.17</v>
       </c>
       <c r="X25" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="Y25" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z25" t="n">
         <v>12</v>
       </c>
       <c r="AA25" t="n">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="AB25" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="AC25" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AD25" t="n">
         <v>10.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
         <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AJ25" t="n">
         <v>1000</v>
@@ -5324,19 +5324,19 @@
         <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AP25" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AQ25" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AT25" t="n">
         <v>14.5</v>
@@ -5345,16 +5345,16 @@
         <v>10.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AX25" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ25" t="n">
         <v>14.5</v>
@@ -5363,26 +5363,26 @@
         <v>20</v>
       </c>
       <c r="BB25" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BG25" t="n">
         <v>5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G26" t="n">
         <v>2.18</v>
@@ -5422,10 +5422,10 @@
         <v>3.5</v>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J26" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K26" t="n">
         <v>4.1</v>
@@ -5440,82 +5440,82 @@
         <v>4.8</v>
       </c>
       <c r="O26" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P26" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="R26" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S26" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T26" t="n">
         <v>1.61</v>
       </c>
       <c r="U26" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W26" t="n">
         <v>1.84</v>
       </c>
       <c r="X26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK26" t="n">
         <v>21</v>
       </c>
-      <c r="Z26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>440</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>25</v>
-      </c>
       <c r="AL26" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM26" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN26" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AO26" t="n">
         <v>34</v>
@@ -5527,10 +5527,10 @@
         <v>15</v>
       </c>
       <c r="AR26" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="AT26" t="n">
         <v>11</v>
@@ -5539,13 +5539,13 @@
         <v>8</v>
       </c>
       <c r="AV26" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX26" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
         <v>9.800000000000001</v>
@@ -5554,19 +5554,19 @@
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.7</v>
+        <v>29</v>
       </c>
       <c r="BB26" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="BC26" t="n">
         <v>10.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF26" t="n">
         <v>10.5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G27" t="n">
         <v>2.38</v>
@@ -5616,16 +5616,16 @@
         <v>3.25</v>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K27" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L27" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
         <v>1.05</v>
@@ -5646,28 +5646,28 @@
         <v>1.51</v>
       </c>
       <c r="S27" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
         <v>1.62</v>
       </c>
       <c r="U27" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W27" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X27" t="n">
         <v>19</v>
       </c>
       <c r="Y27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AA27" t="n">
         <v>500</v>
@@ -5676,22 +5676,22 @@
         <v>15</v>
       </c>
       <c r="AC27" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AE27" t="n">
         <v>85</v>
       </c>
       <c r="AF27" t="n">
-        <v>16.5</v>
+        <v>38</v>
       </c>
       <c r="AG27" t="n">
         <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI27" t="n">
         <v>500</v>
@@ -5706,10 +5706,10 @@
         <v>60</v>
       </c>
       <c r="AM27" t="n">
-        <v>580</v>
+        <v>250</v>
       </c>
       <c r="AN27" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
@@ -5724,31 +5724,31 @@
         <v>11.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AT27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV27" t="n">
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX27" t="n">
         <v>9</v>
       </c>
       <c r="AY27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA27" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>18</v>
       </c>
       <c r="BB27" t="n">
         <v>14.5</v>
@@ -5757,20 +5757,20 @@
         <v>11.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="BE27" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BF27" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>18</v>
+        <v>9.4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G28" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H28" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="I28" t="n">
         <v>3.2</v>
@@ -5837,7 +5837,7 @@
         <v>1.73</v>
       </c>
       <c r="R28" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S28" t="n">
         <v>2.84</v>
@@ -5855,7 +5855,7 @@
         <v>1.66</v>
       </c>
       <c r="X28" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y28" t="n">
         <v>15.5</v>
@@ -5873,7 +5873,7 @@
         <v>10.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
         <v>34</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G29" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H29" t="n">
         <v>3.7</v>
@@ -6007,7 +6007,7 @@
         <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K29" t="n">
         <v>3.8</v>
@@ -6016,149 +6016,149 @@
         <v>1.31</v>
       </c>
       <c r="M29" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="O29" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="P29" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="R29" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
         <v>1.82</v>
       </c>
       <c r="U29" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V29" t="n">
         <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB29" t="n">
-        <v>500</v>
+        <v>9.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AJ29" t="n">
-        <v>900</v>
+        <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.92</v>
+        <v>12</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.96</v>
+        <v>12</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.06</v>
+        <v>13</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.1</v>
+        <v>11</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.87</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.78</v>
+        <v>7</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.96</v>
+        <v>13.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.1</v>
+        <v>10</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.96</v>
+        <v>11.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.87</v>
+        <v>9.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.96</v>
+        <v>15.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.1</v>
+        <v>23</v>
       </c>
       <c r="BB29" t="n">
-        <v>2.06</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.04</v>
+        <v>20</v>
       </c>
       <c r="BD29" t="n">
-        <v>2.08</v>
+        <v>9.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.1</v>
+        <v>11.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>2</v>
+        <v>14.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.1</v>
+        <v>10.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -6192,22 +6192,22 @@
         <v>1.29</v>
       </c>
       <c r="G30" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="H30" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="I30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J30" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="K30" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
         <v>1.03</v>
@@ -6219,10 +6219,10 @@
         <v>1.18</v>
       </c>
       <c r="P30" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R30" t="n">
         <v>1.62</v>
@@ -6231,52 +6231,52 @@
         <v>2.36</v>
       </c>
       <c r="T30" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U30" t="n">
         <v>1.87</v>
       </c>
       <c r="V30" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W30" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="X30" t="n">
         <v>30</v>
       </c>
       <c r="Y30" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Z30" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>720</v>
       </c>
       <c r="AB30" t="n">
         <v>10.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AE30" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AF30" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH30" t="n">
         <v>32</v>
       </c>
       <c r="AI30" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AJ30" t="n">
         <v>11</v>
@@ -6285,52 +6285,52 @@
         <v>14</v>
       </c>
       <c r="AL30" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AO30" t="n">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="AP30" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="AQ30" t="n">
         <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT30" t="n">
         <v>9</v>
       </c>
       <c r="AU30" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV30" t="n">
         <v>18</v>
       </c>
       <c r="AW30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX30" t="n">
         <v>7.8</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
         <v>24</v>
       </c>
       <c r="BA30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB30" t="n">
         <v>9.199999999999999</v>
@@ -6339,20 +6339,20 @@
         <v>12</v>
       </c>
       <c r="BD30" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BE30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF30" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="BG30" t="n">
         <v>15</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>2.48</v>
       </c>
       <c r="G31" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H31" t="n">
         <v>2.94</v>
@@ -6419,10 +6419,10 @@
         <v>1.76</v>
       </c>
       <c r="R31" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T31" t="n">
         <v>1.65</v>
@@ -6434,10 +6434,10 @@
         <v>1.47</v>
       </c>
       <c r="W31" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y31" t="n">
         <v>16.5</v>
@@ -6500,7 +6500,7 @@
         <v>17</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT31" t="n">
         <v>9.4</v>
@@ -6524,7 +6524,7 @@
         <v>12</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB31" t="n">
         <v>4.9</v>
@@ -6533,10 +6533,10 @@
         <v>19</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF31" t="n">
         <v>13</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G32" t="n">
         <v>6.2</v>
       </c>
       <c r="H32" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I32" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="J32" t="n">
         <v>3.8</v>
@@ -6595,7 +6595,7 @@
         <v>4.2</v>
       </c>
       <c r="L32" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M32" t="n">
         <v>1.06</v>
@@ -6610,10 +6610,10 @@
         <v>1.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="R32" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
         <v>3.25</v>
@@ -6622,7 +6622,7 @@
         <v>1.88</v>
       </c>
       <c r="U32" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V32" t="n">
         <v>2.28</v>
@@ -6631,10 +6631,10 @@
         <v>1.2</v>
       </c>
       <c r="X32" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z32" t="n">
         <v>11</v>
@@ -6685,7 +6685,7 @@
         <v>11.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ32" t="n">
         <v>7.2</v>
@@ -6709,7 +6709,7 @@
         <v>15.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY32" t="n">
         <v>18</v>
@@ -6718,29 +6718,29 @@
         <v>17.5</v>
       </c>
       <c r="BA32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC32" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BD32" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE32" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF32" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG32" t="n">
         <v>8.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -6771,25 +6771,25 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="G33" t="n">
         <v>2.56</v>
       </c>
       <c r="H33" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I33" t="n">
         <v>3.5</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K33" t="n">
         <v>3.6</v>
       </c>
       <c r="L33" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
         <v>1.09</v>
@@ -6858,7 +6858,7 @@
         <v>22</v>
       </c>
       <c r="AI33" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AJ33" t="n">
         <v>38</v>
@@ -6927,14 +6927,14 @@
         <v>29</v>
       </c>
       <c r="BF33" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BG33" t="n">
         <v>8.4</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -6965,13 +6965,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G34" t="n">
         <v>2.5</v>
       </c>
       <c r="H34" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I34" t="n">
         <v>3.3</v>
@@ -6980,7 +6980,7 @@
         <v>3.5</v>
       </c>
       <c r="K34" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L34" t="n">
         <v>1.37</v>
@@ -6989,7 +6989,7 @@
         <v>1.06</v>
       </c>
       <c r="N34" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
         <v>1.27</v>
@@ -6998,7 +6998,7 @@
         <v>2.06</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="R34" t="n">
         <v>1.42</v>
@@ -7016,7 +7016,7 @@
         <v>1.43</v>
       </c>
       <c r="W34" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X34" t="n">
         <v>17.5</v>
@@ -7067,7 +7067,7 @@
         <v>90</v>
       </c>
       <c r="AN34" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AO34" t="n">
         <v>29</v>
@@ -7082,7 +7082,7 @@
         <v>19</v>
       </c>
       <c r="AS34" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT34" t="n">
         <v>8.6</v>
@@ -7106,10 +7106,10 @@
         <v>13.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB34" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BC34" t="n">
         <v>20</v>
@@ -7124,11 +7124,11 @@
         <v>14.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -7159,13 +7159,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="G35" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="H35" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I35" t="n">
         <v>2.4</v>
@@ -7198,25 +7198,25 @@
         <v>1.93</v>
       </c>
       <c r="S35" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T35" t="n">
         <v>1.42</v>
       </c>
       <c r="U35" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V35" t="n">
         <v>1.71</v>
       </c>
       <c r="W35" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X35" t="n">
         <v>34</v>
       </c>
       <c r="Y35" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z35" t="n">
         <v>21</v>
@@ -7225,7 +7225,7 @@
         <v>32</v>
       </c>
       <c r="AB35" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC35" t="n">
         <v>11</v>
@@ -7246,10 +7246,10 @@
         <v>13</v>
       </c>
       <c r="AI35" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ35" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK35" t="n">
         <v>25</v>
@@ -7267,10 +7267,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AP35" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR35" t="n">
         <v>19.5</v>
@@ -7285,19 +7285,19 @@
         <v>10</v>
       </c>
       <c r="AV35" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW35" t="n">
         <v>18.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY35" t="n">
         <v>13</v>
       </c>
       <c r="AZ35" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA35" t="n">
         <v>23</v>
@@ -7309,7 +7309,7 @@
         <v>23</v>
       </c>
       <c r="BD35" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE35" t="n">
         <v>40</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
         <v>1.87</v>
       </c>
       <c r="I36" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J36" t="n">
         <v>3.8</v>
@@ -7392,7 +7392,7 @@
         <v>1.38</v>
       </c>
       <c r="S36" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T36" t="n">
         <v>1.88</v>
@@ -7413,19 +7413,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z36" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA36" t="n">
         <v>19.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE36" t="n">
         <v>19</v>
@@ -7434,13 +7434,13 @@
         <v>36</v>
       </c>
       <c r="AG36" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH36" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI36" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ36" t="n">
         <v>110</v>
@@ -7470,13 +7470,13 @@
         <v>10</v>
       </c>
       <c r="AS36" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AT36" t="n">
         <v>15.5</v>
       </c>
       <c r="AU36" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV36" t="n">
         <v>9.6</v>
@@ -7491,22 +7491,22 @@
         <v>17.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA36" t="n">
         <v>32</v>
       </c>
       <c r="BB36" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BC36" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BD36" t="n">
         <v>55</v>
       </c>
       <c r="BE36" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="BF36" t="n">
         <v>70</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -7547,16 +7547,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G37" t="n">
         <v>2.74</v>
       </c>
       <c r="H37" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I37" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>3</v>
@@ -7565,19 +7565,19 @@
         <v>3.25</v>
       </c>
       <c r="L37" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M37" t="n">
         <v>1.11</v>
       </c>
       <c r="N37" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O37" t="n">
         <v>1.51</v>
       </c>
       <c r="P37" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q37" t="n">
         <v>2.52</v>
@@ -7595,7 +7595,7 @@
         <v>1.82</v>
       </c>
       <c r="V37" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W37" t="n">
         <v>1.57</v>
@@ -7625,7 +7625,7 @@
         <v>55</v>
       </c>
       <c r="AF37" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG37" t="n">
         <v>12.5</v>
@@ -7649,7 +7649,7 @@
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AO37" t="n">
         <v>65</v>
@@ -7664,7 +7664,7 @@
         <v>15</v>
       </c>
       <c r="AS37" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT37" t="n">
         <v>7.2</v>
@@ -7697,20 +7697,20 @@
         <v>16</v>
       </c>
       <c r="BD37" t="n">
-        <v>28</v>
+        <v>7.8</v>
       </c>
       <c r="BE37" t="n">
         <v>38</v>
       </c>
       <c r="BF37" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG37" t="n">
-        <v>42</v>
+        <v>9.4</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -7747,10 +7747,10 @@
         <v>3.25</v>
       </c>
       <c r="H38" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="I38" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J38" t="n">
         <v>3.4</v>
@@ -7759,7 +7759,7 @@
         <v>3.65</v>
       </c>
       <c r="L38" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
         <v>1.07</v>
@@ -7789,10 +7789,10 @@
         <v>2.16</v>
       </c>
       <c r="V38" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W38" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X38" t="n">
         <v>14.5</v>
@@ -7822,7 +7822,7 @@
         <v>23</v>
       </c>
       <c r="AG38" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH38" t="n">
         <v>19.5</v>
@@ -7858,7 +7858,7 @@
         <v>14</v>
       </c>
       <c r="AS38" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT38" t="n">
         <v>11</v>
@@ -7882,29 +7882,29 @@
         <v>15</v>
       </c>
       <c r="BA38" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD38" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC38" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD38" t="n">
+      <c r="BE38" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF38" t="n">
         <v>8</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>7.8</v>
       </c>
       <c r="BG38" t="n">
         <v>18</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
         <v>2.38</v>
       </c>
       <c r="O39" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="P39" t="n">
         <v>1.52</v>
@@ -8043,10 +8043,10 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.95</v>
+        <v>10.5</v>
       </c>
       <c r="AR39" t="n">
         <v>4.6</v>
@@ -8058,7 +8058,7 @@
         <v>5.8</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AV39" t="n">
         <v>4.2</v>
@@ -8067,7 +8067,7 @@
         <v>4.9</v>
       </c>
       <c r="AX39" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AY39" t="n">
         <v>3.7</v>
@@ -8076,7 +8076,7 @@
         <v>4.3</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB39" t="n">
         <v>4.4</v>
@@ -8088,17 +8088,17 @@
         <v>4.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF39" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG39" t="n">
         <v>5</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-07.xlsx
@@ -757,94 +757,94 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="H2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K2" t="n">
         <v>4.9</v>
       </c>
-      <c r="K2" t="n">
-        <v>5</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P2" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="R2" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="S2" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z2" t="n">
         <v>70</v>
       </c>
       <c r="AA2" t="n">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="AB2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
         <v>11</v>
       </c>
       <c r="AD2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
         <v>13.5</v>
@@ -853,74 +853,74 @@
         <v>14.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM2" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AS2" t="n">
-        <v>18.5</v>
+        <v>42</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW2" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AX2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY2" t="n">
         <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BB2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE2" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG2" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -951,88 +951,88 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="G3" t="n">
         <v>7.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="I3" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="P3" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V3" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AF3" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AG3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
         <v>60</v>
@@ -1056,19 +1056,19 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>36</v>
+        <v>18.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AR3" t="n">
         <v>7.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="AT3" t="n">
         <v>13</v>
@@ -1077,44 +1077,44 @@
         <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AX3" t="n">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BD3" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BE3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BG3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G4" t="n">
         <v>1.55</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I4" t="n">
         <v>24</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.2</v>
@@ -1172,19 +1172,19 @@
         <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P4" t="n">
         <v>2.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="R4" t="n">
         <v>1.68</v>
       </c>
       <c r="S4" t="n">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1244,7 +1244,7 @@
         <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
         <v>29</v>
@@ -1253,7 +1253,7 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AQ4" t="n">
         <v>4.2</v>
@@ -1268,7 +1268,7 @@
         <v>6.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AV4" t="n">
         <v>4.2</v>
@@ -1283,7 +1283,7 @@
         <v>4.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BA4" t="n">
         <v>4.2</v>
@@ -1295,20 +1295,20 @@
         <v>6</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="J5" t="n">
         <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.33</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.32</v>
-      </c>
       <c r="S5" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="U5" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AA5" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AB5" t="n">
         <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF5" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AM5" t="n">
         <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AP5" t="n">
         <v>11</v>
       </c>
       <c r="AQ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX5" t="n">
         <v>13</v>
       </c>
-      <c r="AR5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB5" t="n">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
         <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BG5" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -1533,64 +1533,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="G6" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="M6" t="n">
         <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="X6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z6" t="n">
         <v>85</v>
@@ -1599,104 +1599,104 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
         <v>11.5</v>
       </c>
       <c r="AH6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK6" t="n">
         <v>42</v>
       </c>
-      <c r="AI6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>34</v>
-      </c>
       <c r="AL6" t="n">
-        <v>450</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AS6" t="n">
         <v>10.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BD6" t="n">
         <v>29</v>
       </c>
       <c r="BE6" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF6" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BG6" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -1727,70 +1727,70 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="I7" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
         <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U7" t="n">
         <v>2.18</v>
       </c>
       <c r="V7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB7" t="n">
         <v>17.5</v>
@@ -1817,7 +1817,7 @@
         <v>34</v>
       </c>
       <c r="AJ7" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AK7" t="n">
         <v>50</v>
@@ -1826,13 +1826,13 @@
         <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN7" t="n">
-        <v>46</v>
+        <v>250</v>
       </c>
       <c r="AO7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP7" t="n">
         <v>15</v>
@@ -1871,26 +1871,26 @@
         <v>16</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7" t="n">
         <v>10.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -1921,64 +1921,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="G8" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I8" t="n">
         <v>3.85</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="K8" t="n">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="L8" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="M8" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="N8" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="O8" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="P8" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="R8" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="U8" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="V8" t="n">
         <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X8" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1987,7 +1987,7 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="AC8" t="n">
         <v>14</v>
@@ -2002,19 +2002,19 @@
         <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH8" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.52</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
         <v>7</v>
       </c>
       <c r="AY8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.56</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.44</v>
+        <v>7.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.48</v>
+        <v>4.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.5</v>
+        <v>9.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -2115,94 +2115,94 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="I9" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
         <v>1.84</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
         <v>90</v>
       </c>
       <c r="Y9" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>19.5</v>
+        <v>40</v>
       </c>
       <c r="AC9" t="n">
         <v>14</v>
       </c>
       <c r="AD9" t="n">
-        <v>36</v>
+        <v>16.5</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
         <v>1000</v>
@@ -2220,65 +2220,65 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ9" t="n">
         <v>8</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.6</v>
+        <v>17.5</v>
       </c>
       <c r="AY9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD9" t="n">
         <v>7</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC9" t="n">
+      <c r="BE9" t="n">
         <v>4.8</v>
       </c>
-      <c r="BD9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BF9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -2309,25 +2309,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G10" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H10" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>3.35</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
@@ -2342,13 +2342,13 @@
         <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
         <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
         <v>1.84</v>
@@ -2357,10 +2357,10 @@
         <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
         <v>970</v>
@@ -2375,7 +2375,7 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AC10" t="n">
         <v>7.8</v>
@@ -2387,7 +2387,7 @@
         <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="AG10" t="n">
         <v>970</v>
@@ -2423,10 +2423,10 @@
         <v>8.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AT10" t="n">
         <v>7.4</v>
@@ -2438,41 +2438,41 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="AZ10" t="n">
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BC10" t="n">
         <v>23</v>
       </c>
       <c r="BD10" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -2506,73 +2506,73 @@
         <v>5.1</v>
       </c>
       <c r="G11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I11" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="J11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N11" t="n">
         <v>3.65</v>
       </c>
-      <c r="K11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.58</v>
-      </c>
       <c r="O11" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="P11" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.66</v>
+        <v>3.55</v>
       </c>
       <c r="T11" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U11" t="n">
         <v>1.96</v>
       </c>
       <c r="V11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Z11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB11" t="n">
         <v>34</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="AD11" t="n">
         <v>11.5</v>
@@ -2590,19 +2590,19 @@
         <v>60</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ11" t="n">
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>55</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
         <v>4.9</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS11" t="n">
         <v>7.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB11" t="n">
         <v>5.2</v>
       </c>
-      <c r="AV11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW11" t="n">
+      <c r="BC11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE11" t="n">
         <v>7.6</v>
       </c>
-      <c r="AX11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BF11" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="BG11" t="n">
         <v>6.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -2697,64 +2697,64 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K12" t="n">
         <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U12" t="n">
         <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X12" t="n">
         <v>19.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z12" t="n">
         <v>70</v>
@@ -2763,25 +2763,25 @@
         <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AE12" t="n">
         <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>150</v>
@@ -2790,13 +2790,13 @@
         <v>26</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
         <v>80</v>
       </c>
       <c r="AM12" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
         <v>13</v>
@@ -2805,22 +2805,22 @@
         <v>220</v>
       </c>
       <c r="AP12" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>14.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="AT12" t="n">
         <v>9.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
         <v>13</v>
@@ -2835,7 +2835,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA12" t="n">
         <v>20</v>
@@ -2844,23 +2844,23 @@
         <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BD12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="BE12" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="BF12" t="n">
         <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -2891,170 +2891,170 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="G13" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="H13" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="I13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="T13" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="U13" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="X13" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
         <v>85</v>
       </c>
-      <c r="AB13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>9</v>
-      </c>
       <c r="AO13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
         <v>10</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.1</v>
+        <v>1.68</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.6</v>
+        <v>19</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>1.74</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.2</v>
+        <v>1.56</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.7</v>
+        <v>1.73</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.7</v>
+        <v>22</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.1</v>
+        <v>1.68</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.9</v>
+        <v>12</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>6</v>
+        <v>1.74</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.5</v>
+        <v>19</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -3085,64 +3085,64 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="G14" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="H14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I14" t="n">
-        <v>15</v>
-      </c>
-      <c r="J14" t="n">
-        <v>6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>15</v>
-      </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M14" t="n">
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>7.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="R14" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="S14" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3187,13 +3187,13 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.58</v>
+        <v>26</v>
       </c>
       <c r="AQ14" t="n">
         <v>4.2</v>
@@ -3202,53 +3202,53 @@
         <v>4.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.6</v>
+        <v>13.5</v>
       </c>
       <c r="AV14" t="n">
         <v>4.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>2.84</v>
       </c>
       <c r="BA14" t="n">
         <v>4.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.56</v>
+        <v>24</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.48</v>
+        <v>5.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I15" t="n">
         <v>3.4</v>
       </c>
-      <c r="I15" t="n">
-        <v>3.5</v>
-      </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
         <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="T15" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="U15" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z15" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AA15" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AF15" t="n">
         <v>16</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AJ15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN15" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AP15" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
       </c>
       <c r="AS15" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV15" t="n">
         <v>12.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AX15" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY15" t="n">
         <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BB15" t="n">
         <v>26</v>
       </c>
       <c r="BC15" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="BD15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE15" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BF15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BG15" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -3473,64 +3473,64 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="G16" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="J16" t="n">
         <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="T16" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U16" t="n">
         <v>2.12</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3539,10 +3539,10 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3551,92 +3551,92 @@
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AG16" t="n">
         <v>10</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK16" t="n">
         <v>65</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP16" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="AR16" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU16" t="n">
         <v>7.8</v>
       </c>
-      <c r="AU16" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AV16" t="n">
-        <v>6.6</v>
+        <v>15.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY16" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -3667,49 +3667,49 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G17" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="H17" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I17" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M17" t="n">
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O17" t="n">
         <v>1.19</v>
       </c>
       <c r="P17" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="R17" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="S17" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="T17" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U17" t="n">
         <v>2.2</v>
@@ -3718,7 +3718,7 @@
         <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3733,31 +3733,31 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AC17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AH17" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK17" t="n">
         <v>500</v>
@@ -3769,68 +3769,68 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP17" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="AQ17" t="n">
         <v>12.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD17" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AU17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE17" t="n">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.6</v>
+        <v>27</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -3861,79 +3861,79 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="G18" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="H18" t="n">
         <v>3.25</v>
       </c>
       <c r="I18" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="J18" t="n">
         <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L18" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="T18" t="n">
         <v>1.71</v>
       </c>
       <c r="U18" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
         <v>75</v>
       </c>
       <c r="AA18" t="n">
-        <v>900</v>
+        <v>440</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE18" t="n">
         <v>120</v>
@@ -3945,28 +3945,28 @@
         <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AJ18" t="n">
         <v>34</v>
       </c>
       <c r="AK18" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AM18" t="n">
-        <v>580</v>
+        <v>85</v>
       </c>
       <c r="AN18" t="n">
         <v>16.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP18" t="n">
         <v>13.5</v>
@@ -3978,7 +3978,7 @@
         <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="AT18" t="n">
         <v>9</v>
@@ -3990,41 +3990,41 @@
         <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="AX18" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AY18" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BC18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BF18" t="n">
         <v>13.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>26</v>
+        <v>8.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G19" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="n">
         <v>3.3</v>
@@ -4067,37 +4067,37 @@
         <v>3.45</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L19" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P19" t="n">
         <v>1.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U19" t="n">
         <v>2</v>
@@ -4106,7 +4106,7 @@
         <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X19" t="n">
         <v>19.5</v>
@@ -4115,110 +4115,110 @@
         <v>21</v>
       </c>
       <c r="Z19" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AA19" t="n">
         <v>500</v>
       </c>
       <c r="AB19" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD19" t="n">
         <v>27</v>
       </c>
       <c r="AE19" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AF19" t="n">
-        <v>17.5</v>
+        <v>36</v>
       </c>
       <c r="AG19" t="n">
         <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AI19" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ19" t="n">
         <v>130</v>
       </c>
       <c r="AK19" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AL19" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO19" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV19" t="n">
         <v>8.6</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AW19" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AY19" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BB19" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.9</v>
+        <v>38</v>
       </c>
       <c r="BE19" t="n">
         <v>26</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="G20" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="I20" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="J20" t="n">
         <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -4276,127 +4276,127 @@
         <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P20" t="n">
         <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U20" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V20" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="W20" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="X20" t="n">
         <v>18.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC20" t="n">
         <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AF20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG20" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH20" t="n">
         <v>16.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ20" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AK20" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL20" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AM20" t="n">
         <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP20" t="n">
         <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS20" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AT20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
         <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AX20" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AY20" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB20" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BC20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BD20" t="n">
         <v>22</v>
@@ -4405,14 +4405,14 @@
         <v>55</v>
       </c>
       <c r="BF20" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -4446,16 +4446,16 @@
         <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="H21" t="n">
         <v>3.45</v>
       </c>
       <c r="I21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J21" t="n">
         <v>3.75</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.8</v>
       </c>
       <c r="K21" t="n">
         <v>4.2</v>
@@ -4476,7 +4476,7 @@
         <v>2.44</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R21" t="n">
         <v>1.56</v>
@@ -4488,22 +4488,22 @@
         <v>1.59</v>
       </c>
       <c r="U21" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="X21" t="n">
         <v>950</v>
       </c>
       <c r="Y21" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
@@ -4515,7 +4515,7 @@
         <v>12.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
@@ -4548,46 +4548,46 @@
         <v>55</v>
       </c>
       <c r="AO21" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP21" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AT21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW21" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="BB21" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BC21" t="n">
         <v>10.5</v>
@@ -4596,17 +4596,17 @@
         <v>20</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G22" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H22" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J22" t="n">
         <v>4.1</v>
       </c>
       <c r="K22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O22" t="n">
         <v>1.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="Q22" t="n">
         <v>1.46</v>
       </c>
       <c r="R22" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="S22" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="T22" t="n">
         <v>1.47</v>
       </c>
       <c r="U22" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
         <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X22" t="n">
         <v>80</v>
@@ -4700,7 +4700,7 @@
         <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AB22" t="n">
         <v>21</v>
@@ -4727,7 +4727,7 @@
         <v>34</v>
       </c>
       <c r="AJ22" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AK22" t="n">
         <v>21</v>
@@ -4745,31 +4745,31 @@
         <v>17.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AR22" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AV22" t="n">
         <v>13</v>
       </c>
       <c r="AW22" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AX22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
@@ -4778,29 +4778,29 @@
         <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC22" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="BD22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -4831,61 +4831,61 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G23" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
         <v>3.85</v>
       </c>
       <c r="I23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K23" t="n">
         <v>4.3</v>
       </c>
-      <c r="J23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L23" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M23" t="n">
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
         <v>1.21</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T23" t="n">
         <v>1.63</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.6</v>
-      </c>
       <c r="U23" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V23" t="n">
         <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y23" t="n">
         <v>20</v>
@@ -4897,13 +4897,13 @@
         <v>900</v>
       </c>
       <c r="AB23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC23" t="n">
         <v>10</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE23" t="n">
         <v>100</v>
@@ -4936,65 +4936,65 @@
         <v>10.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP23" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AR23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV23" t="n">
         <v>12.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB23" t="n">
         <v>12</v>
       </c>
-      <c r="BA23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BC23" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BD23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG23" t="n">
-        <v>9.4</v>
+        <v>24</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -5025,55 +5025,55 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G24" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H24" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I24" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="J24" t="n">
         <v>3.15</v>
       </c>
       <c r="K24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L24" t="n">
         <v>1.46</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4</v>
+      </c>
+      <c r="T24" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.81</v>
-      </c>
       <c r="U24" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V24" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W24" t="n">
         <v>1.39</v>
@@ -5097,16 +5097,16 @@
         <v>7.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
       </c>
       <c r="AF24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG24" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH24" t="n">
         <v>17.5</v>
@@ -5118,7 +5118,7 @@
         <v>900</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL24" t="n">
         <v>1000</v>
@@ -5130,22 +5130,22 @@
         <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR24" t="n">
         <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU24" t="n">
         <v>6.2</v>
@@ -5154,41 +5154,41 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX24" t="n">
         <v>14.5</v>
       </c>
-      <c r="AX24" t="n">
-        <v>9</v>
-      </c>
       <c r="AY24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ24" t="n">
         <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BD24" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG24" t="n">
         <v>21</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -5219,55 +5219,55 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="G25" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
         <v>1.53</v>
       </c>
       <c r="I25" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="J25" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
         <v>5.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R25" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="T25" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U25" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="V25" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="W25" t="n">
         <v>1.17</v>
@@ -5279,28 +5279,28 @@
         <v>12.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>29</v>
+        <v>14.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AC25" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AD25" t="n">
         <v>10.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AH25" t="n">
         <v>19.5</v>
@@ -5315,74 +5315,74 @@
         <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AO25" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AP25" t="n">
         <v>13</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS25" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AU25" t="n">
         <v>10.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF25" t="n">
         <v>13</v>
       </c>
-      <c r="AX25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BG25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>2.1</v>
       </c>
       <c r="G26" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H26" t="n">
         <v>3.5</v>
@@ -5431,28 +5431,28 @@
         <v>4.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
         <v>1.22</v>
       </c>
       <c r="P26" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R26" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S26" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="T26" t="n">
         <v>1.61</v>
@@ -5464,7 +5464,7 @@
         <v>1.37</v>
       </c>
       <c r="W26" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X26" t="n">
         <v>21</v>
@@ -5476,19 +5476,19 @@
         <v>70</v>
       </c>
       <c r="AA26" t="n">
-        <v>900</v>
+        <v>440</v>
       </c>
       <c r="AB26" t="n">
         <v>13</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
         <v>15</v>
       </c>
       <c r="AE26" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AF26" t="n">
         <v>16</v>
@@ -5503,10 +5503,10 @@
         <v>110</v>
       </c>
       <c r="AJ26" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="AL26" t="n">
         <v>80</v>
@@ -5515,22 +5515,22 @@
         <v>320</v>
       </c>
       <c r="AN26" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP26" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR26" t="n">
         <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="AT26" t="n">
         <v>11</v>
@@ -5542,7 +5542,7 @@
         <v>13</v>
       </c>
       <c r="AW26" t="n">
-        <v>9.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="AX26" t="n">
         <v>14</v>
@@ -5554,29 +5554,29 @@
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BF26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG26" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -5616,34 +5616,34 @@
         <v>3.25</v>
       </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J27" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K27" t="n">
         <v>3.75</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M27" t="n">
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
         <v>1.23</v>
       </c>
       <c r="P27" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q27" t="n">
         <v>1.72</v>
       </c>
       <c r="R27" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S27" t="n">
         <v>2.8</v>
@@ -5652,22 +5652,22 @@
         <v>1.62</v>
       </c>
       <c r="U27" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V27" t="n">
         <v>1.43</v>
       </c>
       <c r="W27" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y27" t="n">
         <v>16.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AA27" t="n">
         <v>500</v>
@@ -5679,13 +5679,13 @@
         <v>8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE27" t="n">
         <v>85</v>
       </c>
       <c r="AF27" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="AG27" t="n">
         <v>11.5</v>
@@ -5694,83 +5694,83 @@
         <v>15</v>
       </c>
       <c r="AI27" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AJ27" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AK27" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AL27" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AM27" t="n">
-        <v>250</v>
+        <v>65</v>
       </c>
       <c r="AN27" t="n">
-        <v>55</v>
+        <v>14.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP27" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AS27" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AT27" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV27" t="n">
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AY27" t="n">
         <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BA27" t="n">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="BB27" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="BC27" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BD27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BE27" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BG27" t="n">
-        <v>9.4</v>
+        <v>22</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -5801,58 +5801,58 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G28" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H28" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J28" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L28" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R28" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S28" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="T28" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U28" t="n">
         <v>2.38</v>
       </c>
       <c r="V28" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W28" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X28" t="n">
         <v>19.5</v>
@@ -5864,13 +5864,13 @@
         <v>24</v>
       </c>
       <c r="AA28" t="n">
-        <v>60</v>
+        <v>440</v>
       </c>
       <c r="AB28" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC28" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD28" t="n">
         <v>14</v>
@@ -5879,10 +5879,10 @@
         <v>34</v>
       </c>
       <c r="AF28" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
         <v>16.5</v>
@@ -5915,10 +5915,10 @@
         <v>12.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT28" t="n">
         <v>10.5</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G29" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H29" t="n">
         <v>3.7</v>
@@ -6007,46 +6007,46 @@
         <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K29" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L29" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S29" t="n">
         <v>3.55</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.5</v>
       </c>
       <c r="T29" t="n">
         <v>1.82</v>
       </c>
       <c r="U29" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V29" t="n">
         <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X29" t="n">
         <v>14.5</v>
@@ -6082,22 +6082,22 @@
         <v>18</v>
       </c>
       <c r="AI29" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="AJ29" t="n">
         <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL29" t="n">
         <v>95</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO29" t="n">
         <v>55</v>
@@ -6109,13 +6109,13 @@
         <v>12</v>
       </c>
       <c r="AR29" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AS29" t="n">
         <v>11</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU29" t="n">
         <v>7</v>
@@ -6124,13 +6124,13 @@
         <v>13.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AX29" t="n">
         <v>11.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ29" t="n">
         <v>15.5</v>
@@ -6139,13 +6139,13 @@
         <v>23</v>
       </c>
       <c r="BB29" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BC29" t="n">
         <v>20</v>
       </c>
       <c r="BD29" t="n">
-        <v>9.6</v>
+        <v>21</v>
       </c>
       <c r="BE29" t="n">
         <v>11.5</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -6189,170 +6189,170 @@
         </is>
       </c>
       <c r="F30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H30" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" t="n">
+        <v>12</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L30" t="n">
         <v>1.29</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="H30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I30" t="n">
-        <v>15</v>
-      </c>
-      <c r="J30" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K30" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.01</v>
       </c>
       <c r="M30" t="n">
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P30" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S30" t="n">
         <v>2.56</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.36</v>
       </c>
       <c r="T30" t="n">
         <v>1.96</v>
       </c>
       <c r="U30" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="V30" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W30" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="X30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Y30" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Z30" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AA30" t="n">
-        <v>720</v>
+        <v>500</v>
       </c>
       <c r="AB30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG30" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>250</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>11</v>
-      </c>
       <c r="AH30" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI30" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AJ30" t="n">
         <v>11</v>
       </c>
       <c r="AK30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL30" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AO30" t="n">
-        <v>270</v>
+        <v>190</v>
       </c>
       <c r="AP30" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="AR30" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AS30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU30" t="n">
         <v>11.5</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AW30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX30" t="n">
         <v>7.8</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA30" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BB30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD30" t="n">
         <v>29</v>
       </c>
       <c r="BE30" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BF30" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="BG30" t="n">
         <v>15</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>2.48</v>
       </c>
       <c r="G31" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H31" t="n">
         <v>2.94</v>
@@ -6398,82 +6398,82 @@
         <v>3.55</v>
       </c>
       <c r="K31" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L31" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O31" t="n">
         <v>1.26</v>
       </c>
       <c r="P31" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="R31" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S31" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="T31" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U31" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V31" t="n">
         <v>1.47</v>
       </c>
       <c r="W31" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X31" t="n">
         <v>20</v>
       </c>
       <c r="Y31" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA31" t="n">
         <v>60</v>
       </c>
       <c r="AB31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF31" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG31" t="n">
         <v>13.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI31" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ31" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK31" t="n">
         <v>26</v>
@@ -6482,71 +6482,71 @@
         <v>36</v>
       </c>
       <c r="AM31" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN31" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP31" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT31" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AU31" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV31" t="n">
         <v>10</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX31" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BC31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BF31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BG31" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -6580,79 +6580,79 @@
         <v>5.5</v>
       </c>
       <c r="G32" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="I32" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="J32" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K32" t="n">
         <v>4.2</v>
       </c>
       <c r="L32" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="M32" t="n">
         <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O32" t="n">
         <v>1.31</v>
       </c>
       <c r="P32" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q32" t="n">
-        <v>1.89</v>
-      </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T32" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="U32" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V32" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="W32" t="n">
         <v>1.2</v>
       </c>
       <c r="X32" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z32" t="n">
         <v>11</v>
       </c>
       <c r="AA32" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AB32" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC32" t="n">
         <v>11</v>
       </c>
       <c r="AD32" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>19.5</v>
+        <v>34</v>
       </c>
       <c r="AF32" t="n">
         <v>120</v>
@@ -6670,22 +6670,22 @@
         <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>700</v>
+        <v>190</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
         <v>11.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ32" t="n">
         <v>7.2</v>
@@ -6697,50 +6697,50 @@
         <v>15</v>
       </c>
       <c r="AT32" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV32" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW32" t="n">
         <v>15.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="AY32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ32" t="n">
         <v>18</v>
       </c>
-      <c r="AZ32" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BA32" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB32" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BD32" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF32" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG32" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -6771,40 +6771,40 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="G33" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="H33" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J33" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K33" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="n">
         <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="O33" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P33" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R33" t="n">
         <v>1.25</v>
@@ -6816,22 +6816,22 @@
         <v>1.96</v>
       </c>
       <c r="U33" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V33" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W33" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X33" t="n">
         <v>12</v>
       </c>
       <c r="Y33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA33" t="n">
         <v>160</v>
@@ -6840,16 +6840,16 @@
         <v>8.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE33" t="n">
         <v>48</v>
       </c>
       <c r="AF33" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG33" t="n">
         <v>13</v>
@@ -6864,46 +6864,46 @@
         <v>38</v>
       </c>
       <c r="AK33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL33" t="n">
         <v>55</v>
       </c>
       <c r="AM33" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO33" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AP33" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR33" t="n">
         <v>18.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="AT33" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU33" t="n">
         <v>6.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW33" t="n">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AX33" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY33" t="n">
         <v>10</v>
@@ -6912,7 +6912,7 @@
         <v>18</v>
       </c>
       <c r="BA33" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB33" t="n">
         <v>16</v>
@@ -6921,20 +6921,20 @@
         <v>25</v>
       </c>
       <c r="BD33" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="BE33" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BF33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG33" t="n">
         <v>8.6</v>
       </c>
-      <c r="BG33" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -6965,64 +6965,64 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G34" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H34" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="I34" t="n">
         <v>3.3</v>
       </c>
       <c r="J34" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K34" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M34" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O34" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="P34" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R34" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S34" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="T34" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="U34" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="V34" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X34" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Z34" t="n">
         <v>24</v>
@@ -7031,7 +7031,7 @@
         <v>55</v>
       </c>
       <c r="AB34" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AC34" t="n">
         <v>8.800000000000001</v>
@@ -7040,19 +7040,19 @@
         <v>14.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF34" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AG34" t="n">
         <v>12</v>
       </c>
       <c r="AH34" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ34" t="n">
         <v>34</v>
@@ -7061,31 +7061,31 @@
         <v>25</v>
       </c>
       <c r="AL34" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM34" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN34" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AO34" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP34" t="n">
         <v>14</v>
       </c>
       <c r="AQ34" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR34" t="n">
         <v>19</v>
       </c>
       <c r="AS34" t="n">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AT34" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU34" t="n">
         <v>7.2</v>
@@ -7094,7 +7094,7 @@
         <v>11.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX34" t="n">
         <v>14</v>
@@ -7106,29 +7106,29 @@
         <v>13.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BB34" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC34" t="n">
         <v>20</v>
       </c>
       <c r="BD34" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE34" t="n">
         <v>21</v>
       </c>
       <c r="BF34" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BG34" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -7165,10 +7165,10 @@
         <v>2.88</v>
       </c>
       <c r="H35" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I35" t="n">
         <v>2.38</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>4.2</v>
@@ -7177,124 +7177,124 @@
         <v>4.3</v>
       </c>
       <c r="L35" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N35" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="P35" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="R35" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="S35" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="T35" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="U35" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="V35" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W35" t="n">
         <v>1.53</v>
       </c>
       <c r="X35" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA35" t="n">
         <v>34</v>
       </c>
-      <c r="Y35" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>32</v>
-      </c>
       <c r="AB35" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AC35" t="n">
         <v>11</v>
       </c>
       <c r="AD35" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE35" t="n">
         <v>19.5</v>
       </c>
       <c r="AF35" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AG35" t="n">
         <v>14</v>
       </c>
       <c r="AH35" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AI35" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT35" t="n">
         <v>26</v>
       </c>
-      <c r="AJ35" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>42</v>
-      </c>
-      <c r="AN35" t="n">
+      <c r="AU35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV35" t="n">
         <v>12.5</v>
       </c>
-      <c r="AO35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>22</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>12</v>
-      </c>
       <c r="AW35" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX35" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AY35" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ35" t="n">
         <v>12</v>
@@ -7303,26 +7303,26 @@
         <v>23</v>
       </c>
       <c r="BB35" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BC35" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD35" t="n">
         <v>23</v>
       </c>
-      <c r="BD35" t="n">
-        <v>24</v>
-      </c>
       <c r="BE35" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BF35" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -7359,16 +7359,16 @@
         <v>4.9</v>
       </c>
       <c r="H36" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I36" t="n">
         <v>1.89</v>
       </c>
       <c r="J36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K36" t="n">
         <v>3.8</v>
-      </c>
-      <c r="K36" t="n">
-        <v>3.85</v>
       </c>
       <c r="L36" t="n">
         <v>1.42</v>
@@ -7377,28 +7377,28 @@
         <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O36" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P36" t="n">
         <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R36" t="n">
         <v>1.38</v>
       </c>
       <c r="S36" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T36" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U36" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V36" t="n">
         <v>2.12</v>
@@ -7410,7 +7410,7 @@
         <v>14</v>
       </c>
       <c r="Y36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z36" t="n">
         <v>11</v>
@@ -7422,7 +7422,7 @@
         <v>16</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD36" t="n">
         <v>10</v>
@@ -7434,7 +7434,7 @@
         <v>36</v>
       </c>
       <c r="AG36" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH36" t="n">
         <v>19</v>
@@ -7443,7 +7443,7 @@
         <v>34</v>
       </c>
       <c r="AJ36" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="n">
         <v>60</v>
@@ -7458,7 +7458,7 @@
         <v>75</v>
       </c>
       <c r="AO36" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AP36" t="n">
         <v>13</v>
@@ -7470,7 +7470,7 @@
         <v>10</v>
       </c>
       <c r="AS36" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AT36" t="n">
         <v>15.5</v>
@@ -7479,25 +7